--- a/tame_output/ON/bt/strategyON_20240705.xlsx
+++ b/tame_output/ON/bt/strategyON_20240705.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.3%</t>
+          <t>-69.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>450.0%</t>
+          <t>452.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-36.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.5%</t>
+          <t>-160.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.7%</t>
+          <t>-177.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-219.0%</t>
+          <t>-225.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-83.8%</t>
         </is>
       </c>
     </row>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.41134014318502</v>
+        <v>-10.30744938049405</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.00293847844415</v>
+        <v>-0.9613821733677614</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.712262189196578</v>
+        <v>-2.66928454656672</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.534596689625658</v>
+        <v>1.560383275203574</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.53737693655331</v>
+        <v>-10.43348617386234</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.050659467162351</v>
+        <v>-1.009103162085963</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.687010566386836</v>
+        <v>-2.644032923756977</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.552441391940618</v>
+        <v>1.578227977518534</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.48536142258449</v>
+        <v>-10.38147065989352</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.025862925888425</v>
+        <v>-0.9843066208120357</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.687010566386836</v>
+        <v>-2.644032923756977</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.556431727627019</v>
+        <v>1.582218313204935</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.62703326430861</v>
+        <v>-10.52314250161764</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.084006889476814</v>
+        <v>-1.042450584400425</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.687010566386836</v>
+        <v>-2.644032923756977</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.554956500728278</v>
+        <v>1.580743086306193</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.57744241988378</v>
+        <v>-10.47355165719281</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.049117141542009</v>
+        <v>-1.00756083646562</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.637419721962002</v>
+        <v>-2.594442079332143</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.59976441754805</v>
+        <v>1.625551003125965</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.56463502687901</v>
+        <v>-10.46074426418804</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.057045317986782</v>
+        <v>-1.015489012910393</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.686275496970903</v>
+        <v>-2.643297854341044</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.557399818896027</v>
+        <v>1.583186404473942</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.33878987415959</v>
+        <v>-10.23489911146862</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9571281838628081</v>
+        <v>-0.9155718787864209</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.64434882138374</v>
+        <v>-2.60137117875388</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.592134897284533</v>
+        <v>1.617921482862449</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.214211217822</v>
+        <v>-10.11032045513103</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9061575767717129</v>
+        <v>-0.8646012716953249</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.64434882138374</v>
+        <v>-2.60137117875388</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.593274041840592</v>
+        <v>1.619060627418508</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.26710650586629</v>
+        <v>-10.16321574317532</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9246819178273196</v>
+        <v>-0.8831256127509315</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.639393475295293</v>
+        <v>-2.596415832665434</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.598881023655768</v>
+        <v>1.624667609233683</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.19497333057841</v>
+        <v>-10.09108256788744</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8900949434735308</v>
+        <v>-0.8485386383971427</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.639393475295293</v>
+        <v>-2.596415832665434</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.604614727894404</v>
+        <v>1.63040131347232</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.12360693796876</v>
+        <v>-10.01971617527779</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8712856488235374</v>
+        <v>-0.8297293437471494</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.568027082685645</v>
+        <v>-2.525049440055786</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.637697301066328</v>
+        <v>1.663483886644243</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.03014790398354</v>
+        <v>-9.926257141292567</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8437855165423547</v>
+        <v>-0.802229211465967</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.568027082685645</v>
+        <v>-2.525049440055786</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.62781381975342</v>
+        <v>1.653600405331336</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.762906103115139</v>
+        <v>-9.659015340424169</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7387233566943694</v>
+        <v>-0.6971670516179818</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.568027082685645</v>
+        <v>-2.525049440055786</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.625979259254047</v>
+        <v>1.651765844831962</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.664999064438648</v>
+        <v>-9.561108301747678</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6998608561972341</v>
+        <v>-0.6583045511208461</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.500041332825089</v>
+        <v>-2.45706369019523</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.66647039419692</v>
+        <v>1.692256979774835</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.64104552346269</v>
+        <v>-9.53715476077172</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6896109336613572</v>
+        <v>-0.6480546285849695</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.476087791849131</v>
+        <v>-2.433110149219272</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.681511024927988</v>
+        <v>1.707297610505903</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.376985585139893</v>
+        <v>-9.273094822448924</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5972472744939905</v>
+        <v>-0.5556909694176029</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.212027853526335</v>
+        <v>-2.169050210896476</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.826686671759913</v>
+        <v>1.852473257337829</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.669905961635056</v>
+        <v>-8.566015198944086</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3172024587523565</v>
+        <v>-0.2756461536759689</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.212027853526335</v>
+        <v>-2.169050210896476</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.823899638099612</v>
+        <v>1.849686223677528</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.629721663268866</v>
+        <v>-8.525830900577896</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.300785115518039</v>
+        <v>-0.2592288104416514</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.171843555160144</v>
+        <v>-2.128865912530285</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.848353841007168</v>
+        <v>1.874140426585084</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.466321792329502</v>
+        <v>-8.362431029638532</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2360583459215366</v>
+        <v>-0.194502040845149</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.008443684220782</v>
+        <v>-1.965466041590923</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.945760584791542</v>
+        <v>1.971547170369458</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.232840570099903</v>
+        <v>-8.128949807408933</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1347414281918446</v>
+        <v>-0.09318512311545657</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.774962461991183</v>
+        <v>-1.731984819361324</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.093773746967154</v>
+        <v>2.11956033254507</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.083174179092389</v>
+        <v>-7.979283416401418</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07776708210179795</v>
+        <v>-0.03621077702540987</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.682058970748648</v>
+        <v>-1.639081328118788</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.146623631399716</v>
+        <v>2.172410216977632</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.950898705461502</v>
+        <v>-7.847007942770531</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02948940590241644</v>
+        <v>0.01206689917397163</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.549783497117761</v>
+        <v>-1.506805854487902</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.221356402325275</v>
+        <v>2.247142987903191</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.79516037290176</v>
+        <v>-7.69126961021079</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.03562098780911693</v>
+        <v>0.07717729288550501</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.394045164558019</v>
+        <v>-1.35106752192816</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.317614462548757</v>
+        <v>2.343401048126672</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.546160574218179</v>
+        <v>-7.442269811527209</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1481272485062082</v>
+        <v>0.1896835535825963</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.394045164558019</v>
+        <v>-1.35106752192816</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.330520803772416</v>
+        <v>2.356307389350331</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.651750563991284</v>
+        <v>-7.547859801300313</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.02208467700225247</v>
+        <v>0.01947162807413605</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.499635154331124</v>
+        <v>-1.456657511701265</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.139190880309334</v>
+        <v>2.16497746588725</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.670485466109881</v>
+        <v>-7.56659470341891</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.01896570402739517</v>
+        <v>0.06052200910378325</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.505231163991255</v>
+        <v>-1.462253521361396</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.184377616390342</v>
+        <v>2.210164201968257</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.522545424702281</v>
+        <v>-7.418654662011311</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.04173720209773268</v>
+        <v>-0.0001808970213446059</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.484910248082697</v>
+        <v>-1.441932605452838</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.076691243247309</v>
+        <v>2.102477828825224</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.469575902448293</v>
+        <v>-7.365685139757322</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02926337944961555</v>
+        <v>0.01229292562677298</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.38896308319885</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.099758970346224</v>
+        <v>2.125545555924139</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.426027495677602</v>
+        <v>-7.322136732986632</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01880462883643252</v>
+        <v>0.022751676239956</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.38896308319885</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.092798358251131</v>
+        <v>2.118584943829046</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.183879102223744</v>
+        <v>-7.079988339532774</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09251708292625382</v>
+        <v>0.1340733880026423</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.38896308319885</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.107260712632274</v>
+        <v>2.133047298210189</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.075619965101223</v>
+        <v>-6.971729202410252</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1303528582344575</v>
+        <v>0.171909163310846</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.431940725828709</v>
+        <v>-1.38896308319885</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.101792833091469</v>
+        <v>2.127579418669384</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.952328830284092</v>
+        <v>-6.848438067593121</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1771674061718866</v>
+        <v>0.2187237112482752</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.308649591011578</v>
+        <v>-1.265671948381719</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.173265607992324</v>
+        <v>2.19905219357024</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.931179631380648</v>
+        <v>-6.827288868689678</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1933280639705894</v>
+        <v>0.2348843690469775</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.287500392108135</v>
+        <v>-1.244522749478276</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.193656105571716</v>
+        <v>2.219442691149631</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.687414189397204</v>
+        <v>-6.583523426706233</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2866149491110179</v>
+        <v>0.328171254187406</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.287500392108135</v>
+        <v>-1.244522749478276</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.189436813918766</v>
+        <v>2.215223399496681</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.585651369119909</v>
+        <v>-6.481760606428939</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3294443911419518</v>
+        <v>0.3710006962183399</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.231303681085847</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.199492568874239</v>
+        <v>2.225279154452155</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.335800975170835</v>
+        <v>-6.231910212479864</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4221266237052839</v>
+        <v>0.4636829287816719</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.231303681085847</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.192234643857941</v>
+        <v>2.218021229435857</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.159908882703402</v>
+        <v>-6.056018120012432</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4960825842129055</v>
+        <v>0.5376388892892936</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.274281323715706</v>
+        <v>-1.231303681085847</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.19583376737859</v>
+        <v>2.221620352956506</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.988462419680938</v>
+        <v>-5.884571656989968</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5779886754764449</v>
+        <v>0.6195449805528326</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.102834860693243</v>
+        <v>-1.059857218063384</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.312029151246622</v>
+        <v>2.337815736824537</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.914172853942599</v>
+        <v>-5.810282091251629</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6067249793880776</v>
+        <v>0.6482812844644652</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.028545294954904</v>
+        <v>-0.9855676523250445</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.355623368305922</v>
+        <v>2.381409953883838</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.850537111708665</v>
+        <v>-5.746646349017695</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6368740773359685</v>
+        <v>0.6784303824123565</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9649095527209691</v>
+        <v>-0.92193191009111</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.3984996147006</v>
+        <v>2.424286200278516</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.739110352382744</v>
+        <v>-5.635219589691775</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6626390398501321</v>
+        <v>0.7041953449265201</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9649095527209691</v>
+        <v>-0.92193191009111</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.379693873484396</v>
+        <v>2.405480459062312</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.498679855577884</v>
+        <v>-5.394789092886914</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7605543151969538</v>
+        <v>0.8021106202733415</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7244790559161088</v>
+        <v>-0.6815014132862497</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.52569524819219</v>
+        <v>2.551481833770105</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.42643728740669</v>
+        <v>-5.32254652471572</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7933806563002519</v>
+        <v>0.8349369613766395</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7244790559161088</v>
+        <v>-0.6815014132862497</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.52962456202701</v>
+        <v>2.555411147604925</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.373438965125302</v>
+        <v>-5.269548202434332</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.815258569130147</v>
+        <v>0.8568148742065347</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.66914279691417</v>
+        <v>-0.6261651542843109</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.563504901345513</v>
+        <v>2.589291486923428</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.264634079645575</v>
+        <v>-5.160743316954605</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8557785945420311</v>
+        <v>0.8973348996184192</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.66914279691417</v>
+        <v>-0.6261651542843109</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.560502972565506</v>
+        <v>2.586289558143422</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.044613281608564</v>
+        <v>-4.940722518917594</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9453659507674494</v>
+        <v>0.9869222558438375</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5279229518461898</v>
+        <v>-0.4849453092163306</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.646813916616909</v>
+        <v>2.672600502194824</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.911745592545286</v>
+        <v>-4.807854829854317</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.014407209194584</v>
+        <v>1.055963514270972</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5279229518461898</v>
+        <v>-0.4849453092163306</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.662708099418732</v>
+        <v>2.688494684996648</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.791572509180788</v>
+        <v>-4.687681746489818</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.063622286980685</v>
+        <v>1.105178592057073</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4077498684816908</v>
+        <v>-0.3647722258518317</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.735957793877733</v>
+        <v>2.761744379455649</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.64690036408105</v>
+        <v>-4.54300960139008</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.13157924758202</v>
+        <v>1.173135552658408</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2630777233819534</v>
+        <v>-0.2201000807520943</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.832849183499015</v>
+        <v>2.858635769076931</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.706775191438743</v>
+        <v>-4.602884428747773</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.093666808040369</v>
+        <v>1.135223113116757</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3229525507396455</v>
+        <v>-0.2799749081097864</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.782961778485826</v>
+        <v>2.808748364063742</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.586954960527906</v>
+        <v>-4.483064197836936</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.156884069638912</v>
+        <v>1.1984403747153</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3229525507396455</v>
+        <v>-0.2799749081097864</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.798250947720035</v>
+        <v>2.82403753329795</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.992094879537234</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.589424666989712</v>
+        <v>-4.485533904298742</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.155968588427602</v>
+        <v>1.19752489350399</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3254222572014517</v>
+        <v>-0.2824446145715925</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.796841525216363</v>
+        <v>2.822628110794279</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.003101802011936</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.657794853313722</v>
+        <v>-4.553904090622752</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.1396274363727</v>
+        <v>1.181183741449088</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2731689155353776</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.813413867112794</v>
+        <v>2.83920045269071</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.993538510643827</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.671582906160769</v>
+        <v>-4.567692143469799</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.124548923865773</v>
+        <v>1.166105228942161</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2731689155353776</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.803850575744685</v>
+        <v>2.829637161322601</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.818248075684214</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.702576065489474</v>
+        <v>-4.598685302798504</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9368612251746773</v>
+        <v>0.9784175302510651</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2731689155353776</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.628560140785072</v>
+        <v>2.654346726362988</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.822815307676002</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.527101805697004</v>
+        <v>-4.423211043006035</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.011618161083453</v>
+        <v>1.053174466159841</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2731689155353776</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.63312737277686</v>
+        <v>2.658913958354776</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.798557336437209</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.638038058338253</v>
+        <v>-4.534147295647283</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9429856887881605</v>
+        <v>0.9845419938645483</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3161465581652367</v>
+        <v>-0.2731689155353776</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.608869401538067</v>
+        <v>2.634655987115983</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.801688721657114</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.604374512865971</v>
+        <v>-4.500483750175001</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9595824921969789</v>
+        <v>1.001138797273367</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.2395053700630957</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.632198914041342</v>
+        <v>2.657985499619257</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.811861108089247</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.544521893662248</v>
+        <v>-4.440631130971278</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9936959263106004</v>
+        <v>1.035252231386988</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.2395053700630957</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.642371300473474</v>
+        <v>2.668157886051389</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.806807378663107</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.45827843063587</v>
+        <v>-4.3543876679449</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.023139582095012</v>
+        <v>1.0646958871714</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2824830126929549</v>
+        <v>-0.2395053700630957</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.637317571047335</v>
+        <v>2.66310415662525</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.798583154107633</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.50358525003485</v>
+        <v>-4.39969448734388</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9967926297799454</v>
+        <v>1.038348934856333</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3232931757021857</v>
+        <v>-0.2803155330723265</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.604607248686321</v>
+        <v>2.630393834264237</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.799135027140734</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.532618354737151</v>
+        <v>-4.428727592046181</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9857312609321265</v>
+        <v>1.027287566008515</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3232931757021857</v>
+        <v>-0.2803155330723265</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.605159121719423</v>
+        <v>2.630945707297339</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.7284077190321</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.439807873286291</v>
+        <v>-4.335917110595322</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9521281454038362</v>
+        <v>0.993684450480224</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2304826942513263</v>
+        <v>-0.1875050516214672</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.590118102481304</v>
+        <v>2.61590468805922</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.730281194956701</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.484197342615719</v>
+        <v>-4.380306579924749</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9362458335966659</v>
+        <v>0.9778021386730538</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.274872163580754</v>
+        <v>-0.2318945209508949</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.565357896808249</v>
+        <v>2.591144482386164</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.725356903468424</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.371526124379469</v>
+        <v>-4.267635361688499</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9763900294028889</v>
+        <v>1.017946334479277</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1622009453445038</v>
+        <v>-0.1192233027146447</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.628036336261722</v>
+        <v>2.653822921839637</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.730848199299091</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.259149123196796</v>
+        <v>-4.155258360505826</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.026832125706625</v>
+        <v>1.068388430783013</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1622009453445038</v>
+        <v>-0.1192233027146447</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.633527632092389</v>
+        <v>2.659314217670305</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.74234540106763</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.286929521098148</v>
+        <v>-4.183038758407179</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.027217168314623</v>
+        <v>1.068773473391011</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1899813432458569</v>
+        <v>-0.1470037006159977</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.628356595120116</v>
+        <v>2.654143180698032</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.580701121068283</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.369930802123427</v>
+        <v>-4.266040039432458</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8323723759051651</v>
+        <v>0.873928680981553</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.1655745851431715</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.455569784404465</v>
+        <v>2.481356369982381</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.700850781787489</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.478544880566758</v>
+        <v>-4.374654117875789</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9090764052470384</v>
+        <v>0.9506327103234262</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.1655745851431715</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.575719445123671</v>
+        <v>2.601506030701586</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.715363807889812</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.443135842318616</v>
+        <v>-4.339245079627646</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9377530466486184</v>
+        <v>0.9793093517250062</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.1655745851431715</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.590232471225994</v>
+        <v>2.616019056803909</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.712783249232181</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.404752179760465</v>
+        <v>-4.300861417069495</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9505259530142476</v>
+        <v>0.9920822580906354</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1701685652148794</v>
+        <v>-0.1271909225850203</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.610682110103253</v>
+        <v>2.636468695681168</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.709512278077483</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.227635849725298</v>
+        <v>-4.123745087034329</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.018101513873616</v>
+        <v>1.059657818950004</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1701685652148794</v>
+        <v>-0.1271909225850203</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.607411138948556</v>
+        <v>2.633197724526471</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.710195669839396</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.272728094558844</v>
+        <v>-4.168837331867874</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.000748007702111</v>
+        <v>1.042304312778499</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2320646083842692</v>
+        <v>-0.1890869657544101</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.570956904808835</v>
+        <v>2.59674349038675</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.70398264514581</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.093352673320076</v>
+        <v>-3.989461910629107</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.066285151504033</v>
+        <v>1.10784145658042</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.07528785021355056</v>
+        <v>-0.03231020758369141</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.65880993501768</v>
+        <v>2.684596520595596</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.6847901004774</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.138366886840682</v>
+        <v>-4.034476124149712</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.02908692142738</v>
+        <v>1.070643226503768</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1056367455281552</v>
+        <v>-0.06265910289829602</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.621408053160507</v>
+        <v>2.647194638738423</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.690481662816346</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.405371397113117</v>
+        <v>-4.301480634422147</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9279766796573519</v>
+        <v>0.9695329847337397</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2999997835711037</v>
+        <v>-0.2570221409412446</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.510481792673684</v>
+        <v>2.5362683782516</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.689685584712847</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.50656917855029</v>
+        <v>-4.40267841585932</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8867014889789842</v>
+        <v>0.928257794055372</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3684085971164229</v>
+        <v>-0.3254309544865638</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.468640426442994</v>
+        <v>2.49442701202091</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.687285546267164</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.500058211935977</v>
+        <v>-4.396167449245008</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8869058371790259</v>
+        <v>0.9284621422554138</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3684085971164229</v>
+        <v>-0.3254309544865638</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.466240387997311</v>
+        <v>2.492026973575226</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.683810265475409</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.48102008422868</v>
+        <v>-4.37712932153771</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8910458074701897</v>
+        <v>0.9326021125465775</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4265922084476175</v>
+        <v>-0.3836145658177583</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.427854940406839</v>
+        <v>2.453641525984754</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.86139213441409</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.512146715379298</v>
+        <v>-4.408255952688329</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.056177023948623</v>
+        <v>1.097733329025011</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4265922084476175</v>
+        <v>-0.3836145658177583</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.60543680934552</v>
+        <v>2.631223394923435</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.862225463400223</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.526013476713216</v>
+        <v>-4.422122714022247</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.051463648401189</v>
+        <v>1.093019953477577</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4644501251814404</v>
+        <v>-0.4214724825515813</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.583555388291359</v>
+        <v>2.609341973869275</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.868233993797149</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.481209305173286</v>
+        <v>-4.377318542482317</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.075393847414087</v>
+        <v>1.116950152490475</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4644501251814404</v>
+        <v>-0.4214724825515813</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.589563918688285</v>
+        <v>2.615350504266201</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.947386641589171</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.333466334938284</v>
+        <v>-4.229575572247314</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.21364368330011</v>
+        <v>1.255199988376498</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2966427679465573</v>
+        <v>-0.2536651253166981</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.769400980821237</v>
+        <v>2.795187566399152</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.950180263120652</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.435481017469505</v>
+        <v>-4.331590254778535</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.175631431819103</v>
+        <v>1.21718773689549</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2966427679465573</v>
+        <v>-0.2536651253166981</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.772194602352718</v>
+        <v>2.797981187930633</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.95084261151231</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.429328311416721</v>
+        <v>-4.325437548725751</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.178754862631875</v>
+        <v>1.220311167708263</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.290490061893773</v>
+        <v>-0.2475124192639138</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.776548574376047</v>
+        <v>2.802335159953962</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.949923088252421</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.446137609567223</v>
+        <v>-4.342246846876253</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.171111620111784</v>
+        <v>1.212667925188172</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3072993600442746</v>
+        <v>-0.2643217174144155</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.765543472225856</v>
+        <v>2.791330057803771</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.016258642049241</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.3838396107911</v>
+        <v>-4.279948848100131</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.262366373419054</v>
+        <v>1.303922678495442</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3072993600442746</v>
+        <v>-0.2643217174144155</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.831879026022677</v>
+        <v>2.857665611600592</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.724839514438639</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.182049413125942</v>
+        <v>-4.078158650434973</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.051663324874515</v>
+        <v>1.093219629950903</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1092811678751202</v>
+        <v>-0.06630352524526106</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.659270813713567</v>
+        <v>2.685057399291483</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.795129746760815</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.108671316037206</v>
+        <v>-4.004780553346237</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.151304796032185</v>
+        <v>1.192861101108573</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.03590307078638366</v>
+        <v>0.007074571843475486</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.773587904288985</v>
+        <v>2.7993744898669</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.809757482876858</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.206411860662181</v>
+        <v>-4.102521097971211</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.126836314298239</v>
+        <v>1.168392619374627</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.05179234891936385</v>
+        <v>-0.008814706289504703</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.77868207352524</v>
+        <v>2.804468659103156</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.80829346370153</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.38274962078511</v>
+        <v>-4.27885885809414</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.054837191073739</v>
+        <v>1.096393496150127</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2281301090422932</v>
+        <v>-0.1851524664124341</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.671415398276154</v>
+        <v>2.69720198385407</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.806785081741459</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.306327574353183</v>
+        <v>-4.202436811662214</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.083897627686438</v>
+        <v>1.125453932762826</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2281301090422932</v>
+        <v>-0.1851524664124341</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.669907016316083</v>
+        <v>2.695693601893999</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.806647949176895</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.261954442714615</v>
+        <v>-4.158063680023645</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.101509747777302</v>
+        <v>1.14306605285369</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1837569774037247</v>
+        <v>-0.1407793347738655</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.69639376273466</v>
+        <v>2.722180348312576</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.801041743315485</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.139120221827447</v>
+        <v>-4.035229459136477</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.145037230270759</v>
+        <v>1.186593535347147</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1837569774037247</v>
+        <v>-0.1407793347738655</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.690787556873251</v>
+        <v>2.716574142451166</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.807423500343289</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.091464491266391</v>
+        <v>-3.987573728575422</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.170481279522986</v>
+        <v>1.212037584599374</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.136101246842669</v>
+        <v>-0.09312360421280985</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.725762752237688</v>
+        <v>2.751549337815604</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.812315873718014</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.990946332767637</v>
+        <v>-3.887055570076667</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.215580916297212</v>
+        <v>1.257137221373601</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.03558308834391444</v>
+        <v>0.00739455428594471</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.790966020711666</v>
+        <v>2.816752606289581</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.799070546193887</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.051612923170026</v>
+        <v>-3.947722160479056</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.178068952612129</v>
+        <v>1.219625257688517</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1172814050624481</v>
+        <v>-0.07430376243258896</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.728701703156418</v>
+        <v>2.754488288734334</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.803168248804515</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.006774521561628</v>
+        <v>-3.902883758870658</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.200102015866117</v>
+        <v>1.241658320942505</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1127379721175786</v>
+        <v>-0.06976032948771949</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.735525465533968</v>
+        <v>2.761312051111884</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.807329188435593</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.107533157318626</v>
+        <v>-4.003642394627656</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.163959501194395</v>
+        <v>1.205515806270784</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2015635408445841</v>
+        <v>-0.1585858982147249</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.686391063928843</v>
+        <v>2.712177649506758</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.81320879096343</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.063330320232725</v>
+        <v>-3.959439557541756</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.187520238556592</v>
+        <v>1.229076543632981</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1573607037586836</v>
+        <v>-0.1143830611288245</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.71879236870822</v>
+        <v>2.744578954286136</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.811618791432678</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.100309347896169</v>
+        <v>-3.996418585205199</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.171138627960463</v>
+        <v>1.212694933036851</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1203868019673531</v>
+        <v>-0.07740915933749393</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.739386710252266</v>
+        <v>2.765173295830182</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.862866556615717</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.12036742676101</v>
+        <v>-4.016476664070039</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.214363161597566</v>
+        <v>1.255919466673955</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1203868019673531</v>
+        <v>-0.07740915933749393</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.790634475435306</v>
+        <v>2.816421061013221</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.861307261209971</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.080436753583119</v>
+        <v>-3.976545990892149</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.228776135462975</v>
+        <v>1.270332440539364</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.08045612878946273</v>
+        <v>-0.03747848615960359</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.813033583936293</v>
+        <v>2.838820169514209</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.856255489448241</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.029404660860592</v>
+        <v>-3.92551389816962</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.244137200790256</v>
+        <v>1.285693505866645</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.02942403606693478</v>
+        <v>0.01355360656292437</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.83860106780808</v>
+        <v>2.864387653385995</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.873442893540946</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.964180479733386</v>
+        <v>-3.860289717042415</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.287414277333844</v>
+        <v>1.328970582410232</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.03580014506027085</v>
+        <v>0.07877778769013</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.894922980577108</v>
+        <v>2.920709566155024</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.869403865840226</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.926753459662252</v>
+        <v>-3.822862696971281</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.298346057661577</v>
+        <v>1.339902362737966</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.04105168308945251</v>
+        <v>0.08402932571931165</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.894034875693898</v>
+        <v>2.919821461271813</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.870660658171466</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.946865115696961</v>
+        <v>-3.842974353005989</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.291558187578934</v>
+        <v>1.333114492655323</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0520790280868717</v>
+        <v>0.09505667071673085</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.90190807502359</v>
+        <v>2.927694660601505</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.031218429192677</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.893120301269756</v>
+        <v>-3.789229538578784</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.473613884371027</v>
+        <v>1.515170189447416</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.06214233752733367</v>
+        <v>0.1051199801571928</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.068503831709077</v>
+        <v>3.094290417286993</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.151331338410494</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.869328732663614</v>
+        <v>-3.765437969972642</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.603243421031301</v>
+        <v>1.64479972610769</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.08593390613347596</v>
+        <v>0.1289115487633351</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.20289168209058</v>
+        <v>3.228678267668495</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.143039314424353</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.843244648399806</v>
+        <v>-3.739353885708834</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.605385030750683</v>
+        <v>1.646941335827072</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.08593390613347596</v>
+        <v>0.1289115487633351</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.194599658104439</v>
+        <v>3.220386243682354</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.141232510008133</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.765113467550859</v>
+        <v>-3.661222704859887</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.634830698674042</v>
+        <v>1.67638700375043</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1601107170171605</v>
+        <v>0.2030883596470197</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.237298940218429</v>
+        <v>3.263085525796344</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.158786915734924</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.756221006157576</v>
+        <v>-3.652330243466604</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.655942088958146</v>
+        <v>1.697498394034535</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1601107170171605</v>
+        <v>0.2030883596470197</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.254853345945221</v>
+        <v>3.280639931523136</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.150641963139508</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.924697123127454</v>
+        <v>-3.820806360436482</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.580406689574779</v>
+        <v>1.621962994651168</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1321628813005797</v>
+        <v>0.1751405239304389</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.229939691919856</v>
+        <v>3.255726277497772</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.13191166032737</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.22689759426587</v>
+        <v>-3.123006831574899</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.840796198307274</v>
+        <v>1.882352503383663</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.06181482193016902</v>
+        <v>0.1047924645600282</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.169000553485471</v>
+        <v>3.194787139063387</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.122575682824274</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.204176490582718</v>
+        <v>-3.100285727891746</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.84054866227744</v>
+        <v>1.882104967353829</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.06181482193016902</v>
+        <v>0.1047924645600282</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.159664575982376</v>
+        <v>3.185451161560291</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.281481808675443</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.202451447292674</v>
+        <v>-3.098560684601702</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.000144805444626</v>
+        <v>2.041701110521015</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.06353986522021277</v>
+        <v>0.1065175078500719</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.319605727807571</v>
+        <v>3.345392313385487</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.31855963116909</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.357232454070929</v>
+        <v>-3.253341691379958</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.975310225226971</v>
+        <v>2.01686653030336</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.03017219116573666</v>
+        <v>0.07314983379559581</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.336662945868532</v>
+        <v>3.362449531446448</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.315234987158635</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.30579712068627</v>
+        <v>-3.201906357995298</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.99255971457038</v>
+        <v>2.034116019646769</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.08160752455039633</v>
+        <v>0.1245851671802555</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.364199501888873</v>
+        <v>3.389986087466788</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.325241140803377</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.278845896359782</v>
+        <v>-3.17495513366881</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.013346357945716</v>
+        <v>2.054902663022105</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.1394655132079746</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.383133863150246</v>
+        <v>3.408920448728161</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.509344272948336</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.414798904416098</v>
+        <v>-3.310908141725126</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.14306828686815</v>
+        <v>2.184624591944539</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.1394655132079746</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.567236995295206</v>
+        <v>3.593023580873121</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.50146096785133</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.43720702222097</v>
+        <v>-3.333316259529998</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.126221734649194</v>
+        <v>2.167778039725583</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.09648787057811548</v>
+        <v>0.1394655132079746</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.559353690198199</v>
+        <v>3.585140275776114</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.503514967400967</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.585212789700369</v>
+        <v>-3.481322027009398</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.069073427207071</v>
+        <v>2.11062973228346</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.009760861714574021</v>
+        <v>0.05273850434443317</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.509371484429712</v>
+        <v>3.535158070007627</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.559768685122814</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.594653715588899</v>
+        <v>-3.490762952897928</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.121550774573507</v>
+        <v>2.163107079649896</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.1321879792579654</v>
+        <v>0.1751656218878246</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.639081472677594</v>
+        <v>3.664868058255509</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.562659779668115</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.593366952049343</v>
+        <v>-3.489476189358371</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.12495657453463</v>
+        <v>2.166512879611019</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.133474742797522</v>
+        <v>0.1764523854273812</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.642744625346628</v>
+        <v>3.668531210924544</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.56077159256189</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.594924006038634</v>
+        <v>-3.491033243347663</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.122445565832689</v>
+        <v>2.164001870909078</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.133474742797522</v>
+        <v>0.1764523854273812</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.640856438240403</v>
+        <v>3.666643023818319</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.555591822164752</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.602195891562099</v>
+        <v>-3.498305128871127</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.114357041226165</v>
+        <v>2.155913346302554</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.1262028572740573</v>
+        <v>0.1691804999039164</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.631313536529187</v>
+        <v>3.657100122107102</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.554025832374905</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.600354872503848</v>
+        <v>-3.496464109812876</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.113527459059618</v>
+        <v>2.155083764136007</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.1274710839455257</v>
+        <v>0.1704487265753848</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.63050848274222</v>
+        <v>3.656295068320136</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.567099239240823</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.607263578003528</v>
+        <v>-3.503372815312557</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.123837383725665</v>
+        <v>2.165393688802054</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.1274710839455257</v>
+        <v>0.1704487265753848</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.643581889608139</v>
+        <v>3.669368475186054</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.567099239240823</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.608825220818388</v>
+        <v>-3.504934458127416</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.12321272659972</v>
+        <v>2.164769031676109</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.1274710839455257</v>
+        <v>0.1704487265753848</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.643581889608139</v>
+        <v>3.669368475186054</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.565623280367825</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.636726007927861</v>
+        <v>-3.532835245236889</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.110576452882933</v>
+        <v>2.152132757959322</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.09287415980259089</v>
+        <v>0.13585180243245</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.62134777624938</v>
+        <v>3.647134361827296</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.562387724345024</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.639759005440535</v>
+        <v>-3.535868242749563</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.106127697855062</v>
+        <v>2.147684002931451</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.08984116228991701</v>
+        <v>0.1328188049197762</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.616292421718974</v>
+        <v>3.64207900729689</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.543495943030273</v>
+        <v>3.72521314380182</v>
       </c>
       <c r="C2015" t="n">
         <v>3.629093683935528</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.67999450382911</v>
+        <v>-3.680515710915151</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.156739458090136</v>
+        <v>2.15653097525572</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.04960566390134186</v>
+        <v>-0.01182866324581128</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.658857082276333</v>
+        <v>3.621996485988042</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240705.xlsx
+++ b/tame_output/ON/bt/strategyON_20240705.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>56.1%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>25.4%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.0%</t>
+          <t>-68.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.2%</t>
+          <t>453.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-529.6%</t>
+          <t>-529.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.9%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.6%</t>
+          <t>-186.4%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-177.2%</t>
+          <t>-185.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-225.2%</t>
+          <t>-225.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-83.8%</t>
+          <t>-109.6%</t>
         </is>
       </c>
     </row>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.29376671976074</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539465</v>
+        <v>3.501052558539464</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919912</v>
+        <v>3.812453678919911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318098</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057531</v>
+        <v>3.82431123305753</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279191</v>
+        <v>3.82635497427919</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011504</v>
+        <v>3.835957987011502</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392992</v>
+        <v>3.780933911392991</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632787</v>
+        <v>3.773765222632785</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988308</v>
+        <v>3.764617879883078</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107479</v>
+        <v>3.798814771074788</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242302</v>
+        <v>3.7976948842423</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367692</v>
+        <v>3.82159350936769</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879973</v>
+        <v>3.822326997879971</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502345</v>
+        <v>3.848616626502343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675947</v>
+        <v>3.818668951675945</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539958</v>
+        <v>3.843274527539956</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496265</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577002</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942107</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264747767452</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.7291463984307</v>
+        <v>3.729146398430698</v>
       </c>
       <c r="C1935" t="n">
         <v>2.992094879537234</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003607</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
         <v>3.003101802011936</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508375</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
         <v>2.993538510643827</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.71090673141771</v>
+        <v>3.710906731417708</v>
       </c>
       <c r="C1938" t="n">
         <v>2.818248075684214</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205906</v>
+        <v>3.746042526205905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.822815307676002</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225451</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.798557336437209</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.7732102971113</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.801688721657114</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226417</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.811861108089247</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742306</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.806807378663107</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316053</v>
+        <v>3.752027499316051</v>
       </c>
       <c r="C1944" t="n">
         <v>2.798583154107633</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803198</v>
+        <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
         <v>2.799135027140734</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809505</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.7284077190321</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560433</v>
+        <v>3.748285816560431</v>
       </c>
       <c r="C1947" t="n">
         <v>2.730281194956701</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472746</v>
+        <v>3.721077195472744</v>
       </c>
       <c r="C1948" t="n">
         <v>2.725356903468424</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798545</v>
+        <v>3.743047603798543</v>
       </c>
       <c r="C1949" t="n">
         <v>2.730848199299091</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498873</v>
+        <v>3.689597840498871</v>
       </c>
       <c r="C1950" t="n">
         <v>2.74234540106763</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705333</v>
+        <v>3.643069621705331</v>
       </c>
       <c r="C1951" t="n">
         <v>2.580701121068283</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729278</v>
+        <v>3.682716310729276</v>
       </c>
       <c r="C1952" t="n">
         <v>2.700850781787489</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190777</v>
+        <v>3.733012441190775</v>
       </c>
       <c r="C1953" t="n">
         <v>2.715363807889812</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913434</v>
+        <v>3.741174069913432</v>
       </c>
       <c r="C1954" t="n">
         <v>2.712783249232181</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532495</v>
+        <v>3.751147197532493</v>
       </c>
       <c r="C1955" t="n">
         <v>2.709512278077483</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793912</v>
+        <v>3.741328448793911</v>
       </c>
       <c r="C1956" t="n">
         <v>2.710195669839396</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011245</v>
+        <v>3.750729377011243</v>
       </c>
       <c r="C1957" t="n">
         <v>2.70398264514581</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982239</v>
+        <v>3.716991718982237</v>
       </c>
       <c r="C1958" t="n">
         <v>2.6847901004774</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509548</v>
+        <v>3.737026608509546</v>
       </c>
       <c r="C1959" t="n">
         <v>2.690481662816346</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760819</v>
+        <v>3.702309454760817</v>
       </c>
       <c r="C1960" t="n">
         <v>2.689685584712847</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815464</v>
+        <v>3.705571661815462</v>
       </c>
       <c r="C1961" t="n">
         <v>2.687285546267164</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378108</v>
+        <v>3.709510443378107</v>
       </c>
       <c r="C1962" t="n">
         <v>2.683810265475409</v>
@@ -46697,19 +46697,19 @@
         <v>3.731064473131259</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.86139213441409</v>
+        <v>2.60274785493588</v>
       </c>
       <c r="D1963" t="n">
         <v>-4.408255952688329</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.097733329025011</v>
+        <v>0.8390890495468015</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3836145658177583</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.631223394923435</v>
+        <v>2.372579115445225</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067875</v>
+        <v>3.722447362067874</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.862225463400223</v>
+        <v>2.603581183922014</v>
       </c>
       <c r="D1964" t="n">
         <v>-4.422122714022247</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.093019953477577</v>
+        <v>0.834375673999368</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4214724825515813</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.609341973869275</v>
+        <v>2.350697694391065</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789131</v>
+        <v>3.78742558078913</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.868233993797149</v>
+        <v>2.60958971431894</v>
       </c>
       <c r="D1965" t="n">
         <v>-4.377318542482317</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.116950152490475</v>
+        <v>0.8583058730122657</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4214724825515813</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.615350504266201</v>
+        <v>2.356706224787991</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519918</v>
+        <v>3.781501250519917</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.947386641589171</v>
+        <v>2.688742362110962</v>
       </c>
       <c r="D1966" t="n">
         <v>-4.229575572247314</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.255199988376498</v>
+        <v>0.9965557088982888</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2536651253166981</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.795187566399152</v>
+        <v>2.536543286920943</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918118</v>
+        <v>3.802245929181179</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.950180263120652</v>
+        <v>2.691535983642443</v>
       </c>
       <c r="D1967" t="n">
         <v>-4.331590254778535</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.21718773689549</v>
+        <v>0.9585434574172811</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2536651253166981</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.797981187930633</v>
+        <v>2.539336908452424</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539474</v>
+        <v>3.805608985394739</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.95084261151231</v>
+        <v>2.692198332034101</v>
       </c>
       <c r="D1968" t="n">
         <v>-4.325437548725751</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.220311167708263</v>
+        <v>0.9616668882300532</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.2475124192639138</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.802335159953962</v>
+        <v>2.543690880475753</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890619</v>
+        <v>3.798239794890617</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.949923088252421</v>
+        <v>2.691278808774211</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.342246846876253</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.212667925188172</v>
+        <v>0.9540236457099627</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2643217174144155</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.791330057803771</v>
+        <v>2.532685778325562</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798435</v>
+        <v>3.867362636798434</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.016258642049241</v>
+        <v>2.757614362571032</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.279948848100131</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.303922678495442</v>
+        <v>1.045278399017233</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2643217174144155</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.857665611600592</v>
+        <v>2.599021332122383</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992202</v>
+        <v>3.848729139992201</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.724839514438639</v>
+        <v>2.46619523496043</v>
       </c>
       <c r="D1971" t="n">
         <v>-4.078158650434973</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.093219629950903</v>
+        <v>0.8345753504726938</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.06630352524526106</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.685057399291483</v>
+        <v>2.426413119813274</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852432</v>
+        <v>3.841444817852431</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.795129746760815</v>
+        <v>2.536485467282605</v>
       </c>
       <c r="D1972" t="n">
         <v>-4.004780553346237</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.192861101108573</v>
+        <v>0.9342168216303637</v>
       </c>
       <c r="F1972" t="n">
         <v>0.007074571843475486</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.7993744898669</v>
+        <v>2.540730210388691</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319557</v>
+        <v>3.819063300319556</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.809757482876858</v>
+        <v>2.551113203398649</v>
       </c>
       <c r="D1973" t="n">
         <v>-4.102521097971211</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.168392619374627</v>
+        <v>0.9097483398964177</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.008814706289504703</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.804468659103156</v>
+        <v>2.545824379624946</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489395</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.80829346370153</v>
+        <v>2.549649184223321</v>
       </c>
       <c r="D1974" t="n">
         <v>-4.27885885809414</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.096393496150127</v>
+        <v>0.8377492166719176</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.1851524664124341</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.69720198385407</v>
+        <v>2.438557704375861</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397805</v>
+        <v>3.836411672397804</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.806785081741459</v>
+        <v>2.548140802263249</v>
       </c>
       <c r="D1975" t="n">
         <v>-4.202436811662214</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.125453932762826</v>
+        <v>0.866809653284617</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.1851524664124341</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.695693601893999</v>
+        <v>2.437049322415789</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031626</v>
+        <v>3.833513460316259</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.806647949176895</v>
+        <v>2.548003669698685</v>
       </c>
       <c r="D1976" t="n">
         <v>-4.158063680023645</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.14306605285369</v>
+        <v>0.8844217733754807</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.1407793347738655</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.722180348312576</v>
+        <v>2.463536068834366</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105974</v>
+        <v>3.821562117105973</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.801041743315485</v>
+        <v>2.542397463837276</v>
       </c>
       <c r="D1977" t="n">
         <v>-4.035229459136477</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.186593535347147</v>
+        <v>0.9279492558689379</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.1407793347738655</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.716574142451166</v>
+        <v>2.457929862972957</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190332</v>
+        <v>3.833011148190331</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.807423500343289</v>
+        <v>2.548779220865081</v>
       </c>
       <c r="D1978" t="n">
         <v>-3.987573728575422</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.212037584599374</v>
+        <v>0.9533933051211649</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.09312360421280985</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.751549337815604</v>
+        <v>2.492905058337395</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569625</v>
+        <v>3.822678210569624</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.812315873718014</v>
+        <v>2.553671594239805</v>
       </c>
       <c r="D1979" t="n">
         <v>-3.887055570076667</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.257137221373601</v>
+        <v>0.9984929418953916</v>
       </c>
       <c r="F1979" t="n">
         <v>0.00739455428594471</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.816752606289581</v>
+        <v>2.558108326811372</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.8288088775573</v>
+        <v>3.828808877557299</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.799070546193887</v>
+        <v>2.540426266715678</v>
       </c>
       <c r="D1980" t="n">
         <v>-3.947722160479056</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.219625257688517</v>
+        <v>0.9609809782103083</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.07430376243258896</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.754488288734334</v>
+        <v>2.495844009256125</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932776</v>
+        <v>3.816837033932775</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.803168248804515</v>
+        <v>2.544523969326306</v>
       </c>
       <c r="D1981" t="n">
         <v>-3.902883758870658</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.241658320942505</v>
+        <v>0.9830140414642961</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.06976032948771949</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.761312051111884</v>
+        <v>2.502667771633675</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.81793235491706</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.807329188435593</v>
+        <v>2.548684908957384</v>
       </c>
       <c r="D1982" t="n">
         <v>-4.003642394627656</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.205515806270784</v>
+        <v>0.9468715267925747</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.1585858982147249</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.712177649506758</v>
+        <v>2.453533370028549</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.82668474540597</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.81320879096343</v>
+        <v>2.554564511485221</v>
       </c>
       <c r="D1983" t="n">
         <v>-3.959439557541756</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.229076543632981</v>
+        <v>0.970432264154772</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.1143830611288245</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.744578954286136</v>
+        <v>2.485934674807927</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265654</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.811618791432678</v>
+        <v>2.552974511954469</v>
       </c>
       <c r="D1984" t="n">
         <v>-3.996418585205199</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.212694933036851</v>
+        <v>0.9540506535586424</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.07740915933749393</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.765173295830182</v>
+        <v>2.506529016351973</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284888</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.862866556615717</v>
+        <v>2.604222277137509</v>
       </c>
       <c r="D1985" t="n">
         <v>-4.016476664070039</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.255919466673955</v>
+        <v>0.9972751871957457</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.07740915933749393</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.816421061013221</v>
+        <v>2.557776781535012</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321031</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.861307261209971</v>
+        <v>2.602662981731762</v>
       </c>
       <c r="D1986" t="n">
         <v>-3.976545990892149</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.270332440539364</v>
+        <v>1.011688161061155</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.03747848615960359</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.838820169514209</v>
+        <v>2.580175890036</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475148</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.856255489448241</v>
+        <v>2.597611209970032</v>
       </c>
       <c r="D1987" t="n">
         <v>-3.92551389816962</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.285693505866645</v>
+        <v>1.027049226388436</v>
       </c>
       <c r="F1987" t="n">
         <v>0.01355360656292437</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.864387653385995</v>
+        <v>2.605743373907786</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404864</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.873442893540946</v>
+        <v>2.614798614062737</v>
       </c>
       <c r="D1988" t="n">
         <v>-3.860289717042415</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.328970582410232</v>
+        <v>1.070326302932024</v>
       </c>
       <c r="F1988" t="n">
         <v>0.07877778769013</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.920709566155024</v>
+        <v>2.662065286676815</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882568</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.869403865840226</v>
+        <v>2.610759586362017</v>
       </c>
       <c r="D1989" t="n">
         <v>-3.822862696971281</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.339902362737966</v>
+        <v>1.081258083259757</v>
       </c>
       <c r="F1989" t="n">
         <v>0.08402932571931165</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.919821461271813</v>
+        <v>2.661177181793604</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992672</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.870660658171466</v>
+        <v>2.612016378693257</v>
       </c>
       <c r="D1990" t="n">
         <v>-3.842974353005989</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.333114492655323</v>
+        <v>1.074470213177114</v>
       </c>
       <c r="F1990" t="n">
         <v>0.09505667071673085</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.927694660601505</v>
+        <v>2.669050381123296</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636298</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.031218429192677</v>
+        <v>2.772574149714468</v>
       </c>
       <c r="D1991" t="n">
         <v>-3.789229538578784</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.515170189447416</v>
+        <v>1.256525909969207</v>
       </c>
       <c r="F1991" t="n">
         <v>0.1051199801571928</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.094290417286993</v>
+        <v>2.835646137808784</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957636</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.151331338410494</v>
+        <v>2.892687058932285</v>
       </c>
       <c r="D1992" t="n">
         <v>-3.765437969972642</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.64479972610769</v>
+        <v>1.386155446629481</v>
       </c>
       <c r="F1992" t="n">
         <v>0.1289115487633351</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.228678267668495</v>
+        <v>2.970033988190286</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998762</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.143039314424353</v>
+        <v>2.884395034946144</v>
       </c>
       <c r="D1993" t="n">
         <v>-3.739353885708834</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.646941335827072</v>
+        <v>1.388297056348863</v>
       </c>
       <c r="F1993" t="n">
         <v>0.1289115487633351</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.220386243682354</v>
+        <v>2.961741964204145</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896936</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.141232510008133</v>
+        <v>2.882588230529924</v>
       </c>
       <c r="D1994" t="n">
         <v>-3.661222704859887</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.67638700375043</v>
+        <v>1.417742724272222</v>
       </c>
       <c r="F1994" t="n">
         <v>0.2030883596470197</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.263085525796344</v>
+        <v>3.004441246318136</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959866</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.158786915734924</v>
+        <v>2.900142636256715</v>
       </c>
       <c r="D1995" t="n">
         <v>-3.652330243466604</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.697498394034535</v>
+        <v>1.438854114556326</v>
       </c>
       <c r="F1995" t="n">
         <v>0.2030883596470197</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.280639931523136</v>
+        <v>3.021995652044927</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945375</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.150641963139508</v>
+        <v>2.891997683661299</v>
       </c>
       <c r="D1996" t="n">
         <v>-3.820806360436482</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.621962994651168</v>
+        <v>1.363318715172959</v>
       </c>
       <c r="F1996" t="n">
         <v>0.1751405239304389</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.255726277497772</v>
+        <v>2.997081998019563</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782718</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.13191166032737</v>
+        <v>2.873267380849161</v>
       </c>
       <c r="D1997" t="n">
         <v>-3.123006831574899</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.882352503383663</v>
+        <v>1.623708223905454</v>
       </c>
       <c r="F1997" t="n">
         <v>0.1047924645600282</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.194787139063387</v>
+        <v>2.936142859585178</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632648</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.122575682824274</v>
+        <v>2.863931403346065</v>
       </c>
       <c r="D1998" t="n">
         <v>-3.100285727891746</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.882104967353829</v>
+        <v>1.62346068787562</v>
       </c>
       <c r="F1998" t="n">
         <v>0.1047924645600282</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.185451161560291</v>
+        <v>2.926806882082083</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777686</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.281481808675443</v>
+        <v>3.022837529197234</v>
       </c>
       <c r="D1999" t="n">
         <v>-3.098560684601702</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.041701110521015</v>
+        <v>1.783056831042806</v>
       </c>
       <c r="F1999" t="n">
         <v>0.1065175078500719</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.345392313385487</v>
+        <v>3.086748033907278</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644424</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.31855963116909</v>
+        <v>3.059915351690881</v>
       </c>
       <c r="D2000" t="n">
         <v>-3.253341691379958</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.01686653030336</v>
+        <v>1.758222250825151</v>
       </c>
       <c r="F2000" t="n">
         <v>0.07314983379559581</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.362449531446448</v>
+        <v>3.103805251968239</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799972</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.315234987158635</v>
+        <v>3.056590707680426</v>
       </c>
       <c r="D2001" t="n">
         <v>-3.201906357995298</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.034116019646769</v>
+        <v>1.77547174016856</v>
       </c>
       <c r="F2001" t="n">
         <v>0.1245851671802555</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.389986087466788</v>
+        <v>3.13134180798858</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331127</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.325241140803377</v>
+        <v>3.066596861325168</v>
       </c>
       <c r="D2002" t="n">
         <v>-3.17495513366881</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.054902663022105</v>
+        <v>1.796258383543897</v>
       </c>
       <c r="F2002" t="n">
         <v>0.1394655132079746</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.408920448728161</v>
+        <v>3.150276169249953</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.76805206778412</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.509344272948336</v>
+        <v>3.250699993470128</v>
       </c>
       <c r="D2003" t="n">
         <v>-3.310908141725126</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.184624591944539</v>
+        <v>1.92598031246633</v>
       </c>
       <c r="F2003" t="n">
         <v>0.1394655132079746</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.593023580873121</v>
+        <v>3.334379301394912</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714434</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.50146096785133</v>
+        <v>3.242816688373121</v>
       </c>
       <c r="D2004" t="n">
         <v>-3.333316259529998</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.167778039725583</v>
+        <v>1.909133760247374</v>
       </c>
       <c r="F2004" t="n">
         <v>0.1394655132079746</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.585140275776114</v>
+        <v>3.326495996297905</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155044</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.503514967400967</v>
+        <v>3.244870687922758</v>
       </c>
       <c r="D2005" t="n">
         <v>-3.481322027009398</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.11062973228346</v>
+        <v>1.851985452805252</v>
       </c>
       <c r="F2005" t="n">
         <v>0.05273850434443317</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.535158070007627</v>
+        <v>3.276513790529418</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161989</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.559768685122814</v>
+        <v>3.301124405644605</v>
       </c>
       <c r="D2006" t="n">
         <v>-3.490762952897928</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.163107079649896</v>
+        <v>1.904462800171687</v>
       </c>
       <c r="F2006" t="n">
         <v>0.1751656218878246</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.664868058255509</v>
+        <v>3.4062237787773</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321646</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.562659779668115</v>
+        <v>3.304015500189906</v>
       </c>
       <c r="D2007" t="n">
         <v>-3.489476189358371</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.166512879611019</v>
+        <v>1.90786860013281</v>
       </c>
       <c r="F2007" t="n">
         <v>0.1764523854273812</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.668531210924544</v>
+        <v>3.409886931446335</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347715</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.56077159256189</v>
+        <v>3.302127313083681</v>
       </c>
       <c r="D2008" t="n">
         <v>-3.491033243347663</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.164001870909078</v>
+        <v>1.905357591430869</v>
       </c>
       <c r="F2008" t="n">
         <v>0.1764523854273812</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.666643023818319</v>
+        <v>3.40799874434011</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887759</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.555591822164752</v>
+        <v>3.296947542686544</v>
       </c>
       <c r="D2009" t="n">
         <v>-3.498305128871127</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.155913346302554</v>
+        <v>1.897269066824345</v>
       </c>
       <c r="F2009" t="n">
         <v>0.1691804999039164</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.657100122107102</v>
+        <v>3.398455842628894</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343077</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.554025832374905</v>
+        <v>3.295381552896696</v>
       </c>
       <c r="D2010" t="n">
         <v>-3.496464109812876</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.155083764136007</v>
+        <v>1.896439484657798</v>
       </c>
       <c r="F2010" t="n">
         <v>0.1704487265753848</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.656295068320136</v>
+        <v>3.397650788841927</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754911907647117</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.567099239240823</v>
+        <v>3.308454959762615</v>
       </c>
       <c r="D2011" t="n">
         <v>-3.503372815312557</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.165393688802054</v>
+        <v>1.906749409323845</v>
       </c>
       <c r="F2011" t="n">
         <v>0.1704487265753848</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.669368475186054</v>
+        <v>3.410724195707846</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.74989685176354</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.567099239240823</v>
+        <v>3.308454959762615</v>
       </c>
       <c r="D2012" t="n">
         <v>-3.504934458127416</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.164769031676109</v>
+        <v>1.906124752197901</v>
       </c>
       <c r="F2012" t="n">
         <v>0.1704487265753848</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.669368475186054</v>
+        <v>3.410724195707846</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715834055392124</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.565623280367825</v>
+        <v>3.306979000889616</v>
       </c>
       <c r="D2013" t="n">
         <v>-3.532835245236889</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.152132757959322</v>
+        <v>1.893488478481113</v>
       </c>
       <c r="F2013" t="n">
         <v>0.13585180243245</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.647134361827296</v>
+        <v>3.388490082349087</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684909939172535</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.562387724345024</v>
+        <v>3.303743444866815</v>
       </c>
       <c r="D2014" t="n">
         <v>-3.535868242749563</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.147684002931451</v>
+        <v>1.889039723453243</v>
       </c>
       <c r="F2014" t="n">
         <v>0.1328188049197762</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.64207900729689</v>
+        <v>3.383434727818681</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.72521314380182</v>
+        <v>3.84212069346173</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.629093683935528</v>
+        <v>3.370449404457319</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.680515710915151</v>
+        <v>-3.67949426748681</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.15653097525572</v>
+        <v>1.898295273148848</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.01182866324581128</v>
+        <v>-0.0108072198174704</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.621996485988042</v>
+        <v>3.363965072566837</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240705.xlsx
+++ b/tame_output/ON/bt/strategyON_20240705.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>51.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>110.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-50.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.7%</t>
+          <t>-70.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.1%</t>
+          <t>447.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-529.5%</t>
+          <t>-533.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-37.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-39.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-186.4%</t>
+          <t>-162.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>117.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-185.0%</t>
+          <t>-151.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-225.1%</t>
+          <t>-223.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-109.6%</t>
+          <t>-82.7%</t>
         </is>
       </c>
     </row>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539464</v>
+        <v>3.501052558539465</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.30744938049405</v>
+        <v>-10.41134014318502</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9613821733677614</v>
+        <v>-1.00293847844415</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.66928454656672</v>
+        <v>-2.712262189196578</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.560383275203574</v>
+        <v>1.534596689625658</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.43348617386234</v>
+        <v>-10.53737693655331</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.009103162085963</v>
+        <v>-1.050659467162351</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.644032923756977</v>
+        <v>-2.687010566386836</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.578227977518534</v>
+        <v>1.552441391940618</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.38147065989352</v>
+        <v>-10.48536142258449</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9843066208120357</v>
+        <v>-1.025862925888425</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.644032923756977</v>
+        <v>-2.687010566386836</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.582218313204935</v>
+        <v>1.556431727627019</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.52314250161764</v>
+        <v>-10.62703326430861</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.042450584400425</v>
+        <v>-1.084006889476814</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.644032923756977</v>
+        <v>-2.687010566386836</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.580743086306193</v>
+        <v>1.554956500728278</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.47355165719281</v>
+        <v>-10.57744241988378</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.00756083646562</v>
+        <v>-1.049117141542009</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.594442079332143</v>
+        <v>-2.637419721962002</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.625551003125965</v>
+        <v>1.59976441754805</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770583</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.46074426418804</v>
+        <v>-10.56463502687901</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.015489012910393</v>
+        <v>-1.057045317986782</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.643297854341044</v>
+        <v>-2.686275496970903</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.583186404473942</v>
+        <v>1.557399818896027</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.23489911146862</v>
+        <v>-10.33878987415959</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9155718787864209</v>
+        <v>-0.9571281838628081</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.60137117875388</v>
+        <v>-2.64434882138374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.617921482862449</v>
+        <v>1.592134897284533</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812105</v>
+        <v>3.684843823812106</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.11032045513103</v>
+        <v>-10.214211217822</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8646012716953249</v>
+        <v>-0.9061575767717129</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.60137117875388</v>
+        <v>-2.64434882138374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.619060627418508</v>
+        <v>1.593274041840592</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646219</v>
+        <v>3.71093553364622</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.16321574317532</v>
+        <v>-10.26710650586629</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8831256127509315</v>
+        <v>-0.9246819178273196</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.596415832665434</v>
+        <v>-2.639393475295293</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.624667609233683</v>
+        <v>1.598881023655768</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.09108256788744</v>
+        <v>-10.19497333057841</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8485386383971427</v>
+        <v>-0.8900949434735308</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.596415832665434</v>
+        <v>-2.639393475295293</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.63040131347232</v>
+        <v>1.604614727894404</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857792995533</v>
+        <v>3.728577929955331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.01971617527779</v>
+        <v>-10.12360693796876</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8297293437471494</v>
+        <v>-0.8712856488235374</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.525049440055786</v>
+        <v>-2.568027082685645</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.663483886644243</v>
+        <v>1.637697301066328</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232416</v>
+        <v>3.747702660232417</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.926257141292567</v>
+        <v>-10.03014790398354</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.802229211465967</v>
+        <v>-0.8437855165423547</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.525049440055786</v>
+        <v>-2.568027082685645</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.653600405331336</v>
+        <v>1.62781381975342</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436232</v>
+        <v>3.766317079436233</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.659015340424169</v>
+        <v>-9.762906103115139</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6971670516179818</v>
+        <v>-0.7387233566943694</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.525049440055786</v>
+        <v>-2.568027082685645</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.651765844831962</v>
+        <v>1.625979259254047</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311952</v>
+        <v>3.784684521311953</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.561108301747678</v>
+        <v>-9.664999064438648</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6583045511208461</v>
+        <v>-0.6998608561972341</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.45706369019523</v>
+        <v>-2.500041332825089</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.692256979774835</v>
+        <v>1.66647039419692</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097248</v>
+        <v>3.800829354097249</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.53715476077172</v>
+        <v>-9.64104552346269</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6480546285849695</v>
+        <v>-0.6896109336613572</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.433110149219272</v>
+        <v>-2.476087791849131</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.707297610505903</v>
+        <v>1.681511024927988</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017776</v>
+        <v>3.789311112017777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.273094822448924</v>
+        <v>-9.376985585139893</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5556909694176029</v>
+        <v>-0.5972472744939905</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.169050210896476</v>
+        <v>-2.212027853526335</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.852473257337829</v>
+        <v>1.826686671759913</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839729</v>
+        <v>3.83325274783973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.566015198944086</v>
+        <v>-8.669905961635056</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2756461536759689</v>
+        <v>-0.3172024587523565</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.169050210896476</v>
+        <v>-2.212027853526335</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.849686223677528</v>
+        <v>1.823899638099612</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.525830900577896</v>
+        <v>-8.629721663268866</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2592288104416514</v>
+        <v>-0.300785115518039</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.128865912530285</v>
+        <v>-2.171843555160144</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.874140426585084</v>
+        <v>1.848353841007168</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.362431029638532</v>
+        <v>-8.466321792329502</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.194502040845149</v>
+        <v>-0.2360583459215366</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.965466041590923</v>
+        <v>-2.008443684220782</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.971547170369458</v>
+        <v>1.945760584791542</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.128949807408933</v>
+        <v>-8.232840570099903</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.09318512311545657</v>
+        <v>-0.1347414281918446</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.731984819361324</v>
+        <v>-1.774962461991183</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.11956033254507</v>
+        <v>2.093773746967154</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.979283416401418</v>
+        <v>-8.083174179092389</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.03621077702540987</v>
+        <v>-0.07776708210179795</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.639081328118788</v>
+        <v>-1.682058970748648</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.172410216977632</v>
+        <v>2.146623631399716</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.847007942770531</v>
+        <v>-7.950898705461502</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.01206689917397163</v>
+        <v>-0.02948940590241644</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.506805854487902</v>
+        <v>-1.549783497117761</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.247142987903191</v>
+        <v>2.221356402325275</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105956</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.69126961021079</v>
+        <v>-7.79516037290176</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.07717729288550501</v>
+        <v>0.03562098780911693</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.35106752192816</v>
+        <v>-1.394045164558019</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.343401048126672</v>
+        <v>2.317614462548757</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.442269811527209</v>
+        <v>-7.538898534079141</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1896835535825963</v>
+        <v>0.1510320645618233</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.35106752192816</v>
+        <v>-1.394045164558019</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.356307389350331</v>
+        <v>2.330520803772416</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69293185560765</v>
+        <v>3.692931855607649</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.547859801300313</v>
+        <v>-7.644488523852246</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.01947162807413605</v>
+        <v>-0.01917986094663737</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.456657511701265</v>
+        <v>-1.499635154331124</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.16497746588725</v>
+        <v>2.139190880309334</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987908</v>
+        <v>3.770422583987907</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.56659470341891</v>
+        <v>-7.663223425970843</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.06052200910378325</v>
+        <v>0.02187052008301027</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.462253521361396</v>
+        <v>-1.505231163991255</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.210164201968257</v>
+        <v>2.184377616390342</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.418654662011311</v>
+        <v>-7.515283384563244</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0001808970213446059</v>
+        <v>-0.03883238604211758</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.441932605452838</v>
+        <v>-1.484910248082697</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.102477828825224</v>
+        <v>2.076691243247309</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.365685139757322</v>
+        <v>-7.462313862309255</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.01229292562677298</v>
+        <v>-0.02635856339400044</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.38896308319885</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.125545555924139</v>
+        <v>2.099758970346224</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.322136732986632</v>
+        <v>-7.418765455538565</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.022751676239956</v>
+        <v>-0.01589981278081742</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.38896308319885</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.118584943829046</v>
+        <v>2.092798358251131</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.079988339532774</v>
+        <v>-7.176617062084707</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1340733880026423</v>
+        <v>0.09542189898186892</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.38896308319885</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.133047298210189</v>
+        <v>2.107260712632274</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.971729202410252</v>
+        <v>-7.068357924962185</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.171909163310846</v>
+        <v>0.1332576742900726</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.38896308319885</v>
+        <v>-1.431940725828709</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.127579418669384</v>
+        <v>2.101792833091469</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.82805292879205</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.848438067593121</v>
+        <v>-6.945066790145054</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2187237112482752</v>
+        <v>0.1800722222275017</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.265671948381719</v>
+        <v>-1.308649591011578</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.19905219357024</v>
+        <v>2.173265607992324</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919911</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.827288868689678</v>
+        <v>-6.705588390497597</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2348843690469775</v>
+        <v>0.2835645603238097</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.244522749478276</v>
+        <v>-1.069171191364122</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.219442691149631</v>
+        <v>2.324653626018123</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.583523426706233</v>
+        <v>-6.461822948514153</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.328171254187406</v>
+        <v>0.3768514454642382</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.244522749478276</v>
+        <v>-1.069171191364122</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.215223399496681</v>
+        <v>2.320434334365174</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.481760606428939</v>
+        <v>-6.360060128236858</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3710006962183399</v>
+        <v>0.4196808874951721</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.231303681085847</v>
+        <v>-1.055952122971693</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.225279154452155</v>
+        <v>2.330490089320647</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427919</v>
+        <v>3.826354974279189</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.231910212479864</v>
+        <v>-6.110209734287784</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4636829287816719</v>
+        <v>0.5123631200585042</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.231303681085847</v>
+        <v>-1.055952122971693</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.218021229435857</v>
+        <v>2.323232164304349</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.056018120012432</v>
+        <v>-5.934317641820352</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5376388892892936</v>
+        <v>0.5863190805661258</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.231303681085847</v>
+        <v>-1.055952122971693</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.221620352956506</v>
+        <v>2.326831287824998</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.884571656989968</v>
+        <v>-5.762871178797888</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6195449805528326</v>
+        <v>0.6682251718296648</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.059857218063384</v>
+        <v>-0.8845056599492299</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.337815736824537</v>
+        <v>2.44302667169303</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.810282091251629</v>
+        <v>-5.688581613059549</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6482812844644652</v>
+        <v>0.6969614757412974</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9855676523250445</v>
+        <v>-0.8102160942108907</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.381409953883838</v>
+        <v>2.48662088875233</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.746646349017695</v>
+        <v>-5.624945870825615</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6784303824123565</v>
+        <v>0.7271105736891883</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.92193191009111</v>
+        <v>-0.7465803519769562</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.424286200278516</v>
+        <v>2.529497135147008</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.635219589691775</v>
+        <v>-5.513519111499694</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7041953449265201</v>
+        <v>0.7528755362033523</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.92193191009111</v>
+        <v>-0.7465803519769562</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.405480459062312</v>
+        <v>2.510691393930804</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.394789092886914</v>
+        <v>-5.273088614694834</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8021106202733415</v>
+        <v>0.8507908115501737</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6815014132862497</v>
+        <v>-0.5061498551720959</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.551481833770105</v>
+        <v>2.656692768638597</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.32254652471572</v>
+        <v>-5.200846046523639</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8349369613766395</v>
+        <v>0.8836171526534717</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6815014132862497</v>
+        <v>-0.5061498551720959</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.555411147604925</v>
+        <v>2.660622082473417</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.269548202434332</v>
+        <v>-5.147847724242252</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8568148742065347</v>
+        <v>0.9054950654833669</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6261651542843109</v>
+        <v>-0.450813596170157</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.589291486923428</v>
+        <v>2.694502421791921</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.160743316954605</v>
+        <v>-5.039042838762525</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8973348996184192</v>
+        <v>0.9460150908952514</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6261651542843109</v>
+        <v>-0.450813596170157</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.586289558143422</v>
+        <v>2.691500493011914</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.940722518917594</v>
+        <v>-4.819022040725514</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9869222558438375</v>
+        <v>1.03560244712067</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4849453092163306</v>
+        <v>-0.3095937511021768</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.672600502194824</v>
+        <v>2.777811437063316</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.807854829854317</v>
+        <v>-4.686154351662236</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.055963514270972</v>
+        <v>1.104643705547804</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4849453092163306</v>
+        <v>-0.3095937511021768</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.688494684996648</v>
+        <v>2.79370561986514</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.687681746489818</v>
+        <v>-4.565981268297738</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.105178592057073</v>
+        <v>1.153858783333905</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3647722258518317</v>
+        <v>-0.1894206677376779</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.761744379455649</v>
+        <v>2.866955314324141</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.54300960139008</v>
+        <v>-4.421309123198</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.173135552658408</v>
+        <v>1.22181574393524</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2201000807520943</v>
+        <v>-0.04474852263794044</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.858635769076931</v>
+        <v>2.963846703945423</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.602884428747773</v>
+        <v>-4.481183950555693</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.135223113116757</v>
+        <v>1.183903304393589</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2799749081097864</v>
+        <v>-0.1046233499956326</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.808748364063742</v>
+        <v>2.913959298932234</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.483064197836936</v>
+        <v>-4.361363719644856</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.1984403747153</v>
+        <v>1.247120565992132</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2799749081097864</v>
+        <v>-0.1046233499956326</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.82403753329795</v>
+        <v>2.929248468166442</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430698</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.992094879537234</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.485533904298742</v>
+        <v>-4.363833426106662</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.19752489350399</v>
+        <v>1.246205084780822</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2824446145715925</v>
+        <v>-0.1070930564574387</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.822628110794279</v>
+        <v>2.927839045662771</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.003101802011936</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.553904090622752</v>
+        <v>-4.432203612430672</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.181183741449088</v>
+        <v>1.22986393272592</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2731689155353776</v>
+        <v>-0.09781735742122377</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.83920045269071</v>
+        <v>2.944411387559202</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.993538510643827</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.567692143469799</v>
+        <v>-4.445991665277718</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.166105228942161</v>
+        <v>1.214785420218992</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2731689155353776</v>
+        <v>-0.09781735742122377</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.829637161322601</v>
+        <v>2.934848096191093</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.818248075684214</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.598685302798504</v>
+        <v>-4.476984824606424</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9784175302510651</v>
+        <v>1.027097721527897</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2731689155353776</v>
+        <v>-0.09781735742122377</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.654346726362988</v>
+        <v>2.75955766123148</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.822815307676002</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.423211043006035</v>
+        <v>-4.301510564813954</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.053174466159841</v>
+        <v>1.101854657436673</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2731689155353776</v>
+        <v>-0.09781735742122377</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.658913958354776</v>
+        <v>2.764124893223268</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.798557336437209</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.534147295647283</v>
+        <v>-4.412446817455203</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9845419938645483</v>
+        <v>1.03322218514138</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2731689155353776</v>
+        <v>-0.09781735742122377</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.634655987115983</v>
+        <v>2.739866921984475</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.801688721657114</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.500483750175001</v>
+        <v>-4.378783271982921</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.001138797273367</v>
+        <v>1.049818988550199</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2395053700630957</v>
+        <v>-0.06415381194894193</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.657985499619257</v>
+        <v>2.76319643448775</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.811861108089247</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.440631130971278</v>
+        <v>-4.318930652779198</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.035252231386988</v>
+        <v>1.083932422663821</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2395053700630957</v>
+        <v>-0.06415381194894193</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.668157886051389</v>
+        <v>2.773368820919882</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.806807378663107</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.3543876679449</v>
+        <v>-4.23268718975282</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.0646958871714</v>
+        <v>1.113376078448232</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2395053700630957</v>
+        <v>-0.06415381194894193</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.66310415662525</v>
+        <v>2.768315091493742</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.798583154107633</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.39969448734388</v>
+        <v>-4.2779940091518</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.038348934856333</v>
+        <v>1.087029126133165</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2803155330723265</v>
+        <v>-0.1049639749581727</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.630393834264237</v>
+        <v>2.735604769132729</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.799135027140734</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.428727592046181</v>
+        <v>-4.307027113854101</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.027287566008515</v>
+        <v>1.075967757285347</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2803155330723265</v>
+        <v>-0.1049639749581727</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.630945707297339</v>
+        <v>2.736156642165831</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.7284077190321</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.335917110595322</v>
+        <v>-4.214216632403241</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.993684450480224</v>
+        <v>1.042364641757056</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1875050516214672</v>
+        <v>-0.01215349350731337</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.61590468805922</v>
+        <v>2.721115622927712</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.730281194956701</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.380306579924749</v>
+        <v>-4.258606101732669</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9778021386730538</v>
+        <v>1.026482329949886</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2318945209508949</v>
+        <v>-0.05654296283674104</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.591144482386164</v>
+        <v>2.696355417254656</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.725356903468424</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.267635361688499</v>
+        <v>-4.145934883496419</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.017946334479277</v>
+        <v>1.066626525756109</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1192233027146447</v>
+        <v>0.05612825539950916</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.653822921839637</v>
+        <v>2.759033856708129</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.730848199299091</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.155258360505826</v>
+        <v>-4.033557882313746</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.068388430783013</v>
+        <v>1.117068622059845</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1192233027146447</v>
+        <v>0.05612825539950916</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.659314217670305</v>
+        <v>2.764525152538797</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.74234540106763</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.183038758407179</v>
+        <v>-4.061338280215098</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.068773473391011</v>
+        <v>1.117453664667843</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1470037006159977</v>
+        <v>0.0283478574981561</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.654143180698032</v>
+        <v>2.759354115566524</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705331</v>
+        <v>3.643069621705332</v>
       </c>
       <c r="C1951" t="n">
         <v>2.580701121068283</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.266040039432458</v>
+        <v>-4.144339561240377</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.873928680981553</v>
+        <v>0.9226088722583852</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1655745851431715</v>
+        <v>0.009776972970982345</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.481356369982381</v>
+        <v>2.586567304850873</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.700850781787489</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.374654117875789</v>
+        <v>-4.252953639683708</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9506327103234262</v>
+        <v>0.9993129016002582</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1655745851431715</v>
+        <v>0.009776972970982345</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.601506030701586</v>
+        <v>2.706716965570079</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.715363807889812</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.339245079627646</v>
+        <v>-4.217544601435566</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9793093517250062</v>
+        <v>1.027989543001838</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1655745851431715</v>
+        <v>0.009776972970982345</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.616019056803909</v>
+        <v>2.721229991672402</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.712783249232181</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.300861417069495</v>
+        <v>-4.179160938877414</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9920822580906354</v>
+        <v>1.040762449367468</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1271909225850203</v>
+        <v>0.04816063552913352</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.636468695681168</v>
+        <v>2.741679630549661</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.709512278077483</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.123745087034329</v>
+        <v>-4.002044608842248</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.059657818950004</v>
+        <v>1.108338010226836</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1271909225850203</v>
+        <v>0.04816063552913352</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.633197724526471</v>
+        <v>2.738408659394963</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.710195669839396</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.168837331867874</v>
+        <v>-4.047136853675794</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.042304312778499</v>
+        <v>1.090984504055331</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1890869657544101</v>
+        <v>-0.01373540764025627</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.59674349038675</v>
+        <v>2.701954425255243</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.70398264514581</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.989461910629107</v>
+        <v>-3.867761432437026</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.10784145658042</v>
+        <v>1.156521647857253</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.03231020758369141</v>
+        <v>0.1430413505304624</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.684596520595596</v>
+        <v>2.789807455464088</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.6847901004774</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.034476124149712</v>
+        <v>-3.912775645957633</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.070643226503768</v>
+        <v>1.1193234177806</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.06265910289829602</v>
+        <v>0.1126924552158578</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.647194638738423</v>
+        <v>2.752405573606915</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.690481662816346</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.301480634422147</v>
+        <v>-4.179780156230068</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9695329847337397</v>
+        <v>1.018213176010571</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2570221409412446</v>
+        <v>-0.08167058282709078</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.5362683782516</v>
+        <v>2.641479313120092</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.689685584712847</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.40267841585932</v>
+        <v>-4.280977937667241</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.928257794055372</v>
+        <v>0.9769379853322038</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3254309544865638</v>
+        <v>-0.15007939637241</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.49442701202091</v>
+        <v>2.599637946889402</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.687285546267164</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.396167449245008</v>
+        <v>-4.274466971052928</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9284621422554138</v>
+        <v>0.9771423335322456</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3254309544865638</v>
+        <v>-0.15007939637241</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.492026973575226</v>
+        <v>2.597237908443718</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.683810265475409</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.37712932153771</v>
+        <v>-4.255428843345631</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9326021125465775</v>
+        <v>0.9812823038234093</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3836145658177583</v>
+        <v>-0.2082630077036045</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.453641525984754</v>
+        <v>2.558852460853247</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131259</v>
+        <v>3.731064473131258</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.60274785493588</v>
+        <v>2.86139213441409</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.408255952688329</v>
+        <v>-4.286555474496249</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8390890495468015</v>
+        <v>1.146413520301843</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3836145658177583</v>
+        <v>-0.2082630077036045</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.372579115445225</v>
+        <v>2.736434329791927</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067874</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.603581183922014</v>
+        <v>2.862225463400223</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.422122714022247</v>
+        <v>-4.300422235830167</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.834375673999368</v>
+        <v>1.141700144754409</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4214724825515813</v>
+        <v>-0.2461209244374274</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.350697694391065</v>
+        <v>2.714552908737767</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.78742558078913</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.60958971431894</v>
+        <v>2.868233993797149</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.377318542482317</v>
+        <v>-4.255618064290237</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8583058730122657</v>
+        <v>1.165630343767307</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4214724825515813</v>
+        <v>-0.2461209244374274</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.356706224787991</v>
+        <v>2.720561439134693</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519917</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.688742362110962</v>
+        <v>2.947386641589171</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.229575572247314</v>
+        <v>-4.107875094055235</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9965557088982888</v>
+        <v>1.30388017965333</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2536651253166981</v>
+        <v>-0.07831356720254429</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.536543286920943</v>
+        <v>2.900398501267645</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181179</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.691535983642443</v>
+        <v>2.950180263120652</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.331590254778535</v>
+        <v>-4.209889776586456</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9585434574172811</v>
+        <v>1.265867928172322</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2536651253166981</v>
+        <v>-0.07831356720254429</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.539336908452424</v>
+        <v>2.903192122799126</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394739</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.692198332034101</v>
+        <v>2.95084261151231</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.325437548725751</v>
+        <v>-4.203737070533672</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9616668882300532</v>
+        <v>1.268991358985094</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2475124192639138</v>
+        <v>-0.07216086114976</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.543690880475753</v>
+        <v>2.907546094822455</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890617</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.691278808774211</v>
+        <v>2.949923088252421</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.342246846876253</v>
+        <v>-4.220546368684174</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9540236457099627</v>
+        <v>1.261348116465004</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2643217174144155</v>
+        <v>-0.08897015930026164</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.532685778325562</v>
+        <v>2.896540992672264</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798434</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.757614362571032</v>
+        <v>3.016258642049241</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.279948848100131</v>
+        <v>-4.158248369908051</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.045278399017233</v>
+        <v>1.352602869772274</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2643217174144155</v>
+        <v>-0.08897015930026164</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.599021332122383</v>
+        <v>2.962876546469085</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992201</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.46619523496043</v>
+        <v>2.724839514438639</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.078158650434973</v>
+        <v>-3.956458172242893</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8345753504726938</v>
+        <v>1.141899821227735</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.06630352524526106</v>
+        <v>0.1090480328688928</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.426413119813274</v>
+        <v>2.790268334159975</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852431</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.536485467282605</v>
+        <v>2.795129746760815</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.004780553346237</v>
+        <v>-3.883080075154157</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9342168216303637</v>
+        <v>1.241541292385405</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.007074571843475486</v>
+        <v>0.1824261299576293</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.540730210388691</v>
+        <v>2.904585424735393</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319556</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.551113203398649</v>
+        <v>2.809757482876858</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.102521097971211</v>
+        <v>-3.980820619779131</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9097483398964177</v>
+        <v>1.217072810651459</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.008814706289504703</v>
+        <v>0.1665368518246491</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.545824379624946</v>
+        <v>2.909679593971648</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489395</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.549649184223321</v>
+        <v>2.80829346370153</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.27885885809414</v>
+        <v>-4.157158379902061</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8377492166719176</v>
+        <v>1.145073687426958</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1851524664124341</v>
+        <v>-0.009800908298280286</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.438557704375861</v>
+        <v>2.802412918722562</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397804</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.548140802263249</v>
+        <v>2.806785081741459</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.202436811662214</v>
+        <v>-4.080736333470134</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.866809653284617</v>
+        <v>1.174134124039658</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1851524664124341</v>
+        <v>-0.009800908298280286</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.437049322415789</v>
+        <v>2.800904536762491</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316259</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.548003669698685</v>
+        <v>2.806647949176895</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.158063680023645</v>
+        <v>-4.036363201831565</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8844217733754807</v>
+        <v>1.191746244130521</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1407793347738655</v>
+        <v>0.03457222334028831</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.463536068834366</v>
+        <v>2.827391283181068</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105973</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.542397463837276</v>
+        <v>2.801041743315485</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.035229459136477</v>
+        <v>-3.913528980944398</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9279492558689379</v>
+        <v>1.235273726623979</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1407793347738655</v>
+        <v>0.03457222334028831</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.457929862972957</v>
+        <v>2.821785077319658</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190331</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.548779220865081</v>
+        <v>2.807423500343289</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.987573728575422</v>
+        <v>-3.865873250383342</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9533933051211649</v>
+        <v>1.260717775876205</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.09312360421280985</v>
+        <v>0.08222795390134396</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.492905058337395</v>
+        <v>2.856760272684096</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569624</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.553671594239805</v>
+        <v>2.812315873718014</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.887055570076667</v>
+        <v>-3.765355091884588</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9984929418953916</v>
+        <v>1.305817412650432</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.00739455428594471</v>
+        <v>0.1827461124000985</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.558108326811372</v>
+        <v>2.921963541158074</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557299</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.540426266715678</v>
+        <v>2.799070546193887</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.947722160479056</v>
+        <v>-3.826021682286977</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9609809782103083</v>
+        <v>1.268305448965349</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.07430376243258896</v>
+        <v>0.1010477956815649</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.495844009256125</v>
+        <v>2.859699223602826</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932775</v>
+        <v>3.816837033932774</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.544523969326306</v>
+        <v>2.803168248804515</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.902883758870658</v>
+        <v>-3.781183280678579</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9830140414642961</v>
+        <v>1.290338512219336</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.06976032948771949</v>
+        <v>0.1055912286264343</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.502667771633675</v>
+        <v>2.866522985980376</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491706</v>
+        <v>3.817932354917058</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.548684908957384</v>
+        <v>2.807329188435593</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.003642394627656</v>
+        <v>-3.881941916435577</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9468715267925747</v>
+        <v>1.254195997547615</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1585858982147249</v>
+        <v>0.01676565989942891</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.453533370028549</v>
+        <v>2.817388584375251</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82668474540597</v>
+        <v>3.826684745405968</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.554564511485221</v>
+        <v>2.81320879096343</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.959439557541756</v>
+        <v>-3.837739079349677</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.970432264154772</v>
+        <v>1.277756734909812</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1143830611288245</v>
+        <v>0.06096849698532936</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.485934674807927</v>
+        <v>2.849789889154628</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265654</v>
+        <v>3.838199629265653</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.552974511954469</v>
+        <v>2.811618791432678</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.996418585205199</v>
+        <v>-3.87471810701312</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9540506535586424</v>
+        <v>1.261375124313683</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.07740915933749393</v>
+        <v>0.09794239877665989</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.506529016351973</v>
+        <v>2.870384230698674</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284888</v>
+        <v>3.863895080284887</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.604222277137509</v>
+        <v>2.862866556615717</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.016476664070039</v>
+        <v>-3.89477618587796</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9972751871957457</v>
+        <v>1.304599657950786</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.07740915933749393</v>
+        <v>0.09794239877665989</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.557776781535012</v>
+        <v>2.921631995881714</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321031</v>
+        <v>3.86533868132103</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.602662981731762</v>
+        <v>2.861307261209971</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.976545990892149</v>
+        <v>-3.85484551270007</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.011688161061155</v>
+        <v>1.319012631816195</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.03747848615960359</v>
+        <v>0.1378730719545502</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.580175890036</v>
+        <v>2.944031104382701</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475148</v>
+        <v>3.864489842475147</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.597611209970032</v>
+        <v>2.856255489448241</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.92551389816962</v>
+        <v>-3.803813419977542</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.027049226388436</v>
+        <v>1.334373697143477</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.01355360656292437</v>
+        <v>0.1889051646770782</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.605743373907786</v>
+        <v>2.969598588254488</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404864</v>
+        <v>3.842547360404863</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.614798614062737</v>
+        <v>2.873442893540946</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.860289717042415</v>
+        <v>-3.738589238850336</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.070326302932024</v>
+        <v>1.377650773687064</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.07877778769013</v>
+        <v>0.2541293458042838</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.662065286676815</v>
+        <v>3.025920501023516</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882568</v>
+        <v>3.840061186882567</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.610759586362017</v>
+        <v>2.869403865840226</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.822862696971281</v>
+        <v>-3.701162218779202</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.081258083259757</v>
+        <v>1.388582554014798</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.08402932571931165</v>
+        <v>0.2593808838334655</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.661177181793604</v>
+        <v>3.025032396140305</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992672</v>
+        <v>3.84516980899267</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.612016378693257</v>
+        <v>2.870660658171466</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.842974353005989</v>
+        <v>-3.721273874813911</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.074470213177114</v>
+        <v>1.381794683932155</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.09505667071673085</v>
+        <v>0.2704082288308847</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.669050381123296</v>
+        <v>3.032905595469997</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636298</v>
+        <v>3.828661445636296</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.772574149714468</v>
+        <v>3.031218429192677</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.789229538578784</v>
+        <v>-3.667529060386706</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.256525909969207</v>
+        <v>1.563850380724247</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1051199801571928</v>
+        <v>0.2804715382713466</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.835646137808784</v>
+        <v>3.199501352155485</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957636</v>
+        <v>3.813222820957634</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.892687058932285</v>
+        <v>3.151331338410494</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.765437969972642</v>
+        <v>-3.643737491780564</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.386155446629481</v>
+        <v>1.693479917384521</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1289115487633351</v>
+        <v>0.3042631068774889</v>
       </c>
       <c r="G1992" t="n">
-        <v>2.970033988190286</v>
+        <v>3.333889202536988</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998762</v>
+        <v>3.81423072799876</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.884395034946144</v>
+        <v>3.143039314424353</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.739353885708834</v>
+        <v>-3.617653407516756</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.388297056348863</v>
+        <v>1.695621527103904</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1289115487633351</v>
+        <v>0.3042631068774889</v>
       </c>
       <c r="G1993" t="n">
-        <v>2.961741964204145</v>
+        <v>3.325597178550847</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896936</v>
+        <v>3.803397818896934</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.882588230529924</v>
+        <v>3.141232510008133</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.661222704859887</v>
+        <v>-3.539522226667809</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.417742724272222</v>
+        <v>1.725067195027262</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2030883596470197</v>
+        <v>0.3784399177611735</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.004441246318136</v>
+        <v>3.368296460664837</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959866</v>
+        <v>3.796264143959864</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.900142636256715</v>
+        <v>3.158786915734924</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.652330243466604</v>
+        <v>-3.530629765274526</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.438854114556326</v>
+        <v>1.746178585311366</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2030883596470197</v>
+        <v>0.3784399177611735</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.021995652044927</v>
+        <v>3.385850866391628</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945375</v>
+        <v>3.794424941945373</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.891997683661299</v>
+        <v>3.150641963139508</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.820806360436482</v>
+        <v>-3.699105882244404</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.363318715172959</v>
+        <v>1.670643185927999</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1751405239304389</v>
+        <v>0.3504920820445927</v>
       </c>
       <c r="G1996" t="n">
-        <v>2.997081998019563</v>
+        <v>3.360937212366264</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782718</v>
+        <v>3.795574066782716</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.873267380849161</v>
+        <v>3.13191166032737</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.123006831574899</v>
+        <v>-3.00130635338282</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.623708223905454</v>
+        <v>1.931032694660495</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1047924645600282</v>
+        <v>0.280144022674182</v>
       </c>
       <c r="G1997" t="n">
-        <v>2.936142859585178</v>
+        <v>3.299998073931879</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632648</v>
+        <v>3.784671345632646</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.863931403346065</v>
+        <v>3.122575682824274</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.100285727891746</v>
+        <v>-2.978585249699668</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.62346068787562</v>
+        <v>1.93078515863066</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1047924645600282</v>
+        <v>0.280144022674182</v>
       </c>
       <c r="G1998" t="n">
-        <v>2.926806882082083</v>
+        <v>3.290662096428784</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777686</v>
+        <v>3.783205696777684</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.022837529197234</v>
+        <v>3.281481808675443</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.098560684601702</v>
+        <v>-2.976860206409624</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.783056831042806</v>
+        <v>2.090381301797847</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1065175078500719</v>
+        <v>0.2818690659642257</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.086748033907278</v>
+        <v>3.450603248253979</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644424</v>
+        <v>3.779933725644423</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.059915351690881</v>
+        <v>3.31855963116909</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.253341691379958</v>
+        <v>-3.131641213187879</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.758222250825151</v>
+        <v>2.065546721580191</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.07314983379559581</v>
+        <v>0.2485013919097496</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.103805251968239</v>
+        <v>3.46766046631494</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799972</v>
+        <v>3.76944361979997</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.056590707680426</v>
+        <v>3.315234987158635</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.201906357995298</v>
+        <v>-3.080205879803219</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.77547174016856</v>
+        <v>2.0827962109236</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.1245851671802555</v>
+        <v>0.2999367252944093</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.13134180798858</v>
+        <v>3.495197022335281</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331127</v>
+        <v>3.766673496331125</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.066596861325168</v>
+        <v>3.325241140803377</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.17495513366881</v>
+        <v>-3.053254655476731</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.796258383543897</v>
+        <v>2.103582854298937</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1394655132079746</v>
+        <v>0.3148170713221284</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.150276169249953</v>
+        <v>3.514131383596654</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778412</v>
+        <v>3.768052067784119</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.250699993470128</v>
+        <v>3.509344272948336</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.310908141725126</v>
+        <v>-3.189207663533048</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.92598031246633</v>
+        <v>2.23330478322137</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1394655132079746</v>
+        <v>0.3148170713221284</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.334379301394912</v>
+        <v>3.698234515741614</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714434</v>
+        <v>3.743925505714432</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.242816688373121</v>
+        <v>3.50146096785133</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.333316259529998</v>
+        <v>-3.21161578133792</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.909133760247374</v>
+        <v>2.216458231002414</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.1394655132079746</v>
+        <v>0.3148170713221284</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.326495996297905</v>
+        <v>3.690351210644607</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155044</v>
+        <v>3.719118627155042</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.244870687922758</v>
+        <v>3.503514967400967</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.481322027009398</v>
+        <v>-3.359621548817319</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.851985452805252</v>
+        <v>2.159309923560292</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.05273850434443317</v>
+        <v>0.228090062458587</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.276513790529418</v>
+        <v>3.640369004876119</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161989</v>
+        <v>3.729452285161988</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.301124405644605</v>
+        <v>3.559768685122814</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.490762952897928</v>
+        <v>-3.369062474705849</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.904462800171687</v>
+        <v>2.211787270926727</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.1751656218878246</v>
+        <v>0.3505171800019784</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.4062237787773</v>
+        <v>3.770078993124002</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321646</v>
+        <v>3.714941193321645</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.304015500189906</v>
+        <v>3.562659779668115</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.489476189358371</v>
+        <v>-3.367775711166293</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.90786860013281</v>
+        <v>2.21519307088785</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.1764523854273812</v>
+        <v>0.351803943541535</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.409886931446335</v>
+        <v>3.773742145793036</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347715</v>
+        <v>3.727898186347713</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.302127313083681</v>
+        <v>3.56077159256189</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.491033243347663</v>
+        <v>-3.369332765155584</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.905357591430869</v>
+        <v>2.212682062185909</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.1764523854273812</v>
+        <v>0.351803943541535</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.40799874434011</v>
+        <v>3.771853958686811</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887759</v>
+        <v>3.710654104887757</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.296947542686544</v>
+        <v>3.555591822164752</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.498305128871127</v>
+        <v>-3.376604650679049</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.897269066824345</v>
+        <v>2.204593537579385</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.1691804999039164</v>
+        <v>0.3445320580180702</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.398455842628894</v>
+        <v>3.762311056975595</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343077</v>
+        <v>3.712897612343075</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.295381552896696</v>
+        <v>3.554025832374905</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.496464109812876</v>
+        <v>-3.374763631620798</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.896439484657798</v>
+        <v>2.203763955412839</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.1704487265753848</v>
+        <v>0.3458002846895387</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.397650788841927</v>
+        <v>3.761506003188628</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647117</v>
+        <v>3.754911907647116</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.308454959762615</v>
+        <v>3.567099239240823</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.503372815312557</v>
+        <v>-3.381672337120478</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.906749409323845</v>
+        <v>2.214073880078885</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.1704487265753848</v>
+        <v>0.3458002846895387</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.410724195707846</v>
+        <v>3.774579410054547</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176354</v>
+        <v>3.749896851763538</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.308454959762615</v>
+        <v>3.567099239240823</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.504934458127416</v>
+        <v>-3.383233979935338</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.906124752197901</v>
+        <v>2.213449222952941</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.1704487265753848</v>
+        <v>0.3458002846895387</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.410724195707846</v>
+        <v>3.774579410054547</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392124</v>
+        <v>3.715834055392122</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.306979000889616</v>
+        <v>3.565623280367825</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.532835245236889</v>
+        <v>-3.411134767044811</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.893488478481113</v>
+        <v>2.200812949236154</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.13585180243245</v>
+        <v>0.3112033605466039</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.388490082349087</v>
+        <v>3.752345296695788</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172535</v>
+        <v>3.684909939172533</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.303743444866815</v>
+        <v>3.562387724345024</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.535868242749563</v>
+        <v>-3.414167764557485</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.889039723453243</v>
+        <v>2.196364194208283</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.1328188049197762</v>
+        <v>0.30817036303393</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.383434727818681</v>
+        <v>3.747289942165382</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.84212069346173</v>
+        <v>3.409893696067393</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.370449404457319</v>
+        <v>3.629093683935528</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.67949426748681</v>
+        <v>-3.715216614894124</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.898295273148848</v>
+        <v>2.142650613664131</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.0108072198174704</v>
+        <v>0.007121512697290777</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.363965072566837</v>
+        <v>3.633366591553902</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240705.xlsx
+++ b/tame_output/ON/bt/strategyON_20240705.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,31 +973,31 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-681.4%</t>
+          <t>-662.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.7%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-66.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.7%</t>
+          <t>434.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-533.1%</t>
+          <t>-490.6%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,31 +1131,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-272.9%</t>
+          <t>-265.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-39.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-39.5%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-162.0%</t>
+          <t>-144.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-14.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>117.0%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-151.3%</t>
+          <t>-183.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-223.3%</t>
+          <t>-210.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-82.7%</t>
+          <t>-69.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2015"/>
+  <dimension ref="A1:G2016"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5724078633879268</v>
+        <v>-0.3792603279725552</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.897161149868867</v>
+        <v>2.974420164035016</v>
       </c>
       <c r="F1843" t="n">
         <v>1.367390796168583</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6541797638156785</v>
+        <v>-0.4610322284003069</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.854535115653005</v>
+        <v>2.931794129819154</v>
       </c>
       <c r="F1844" t="n">
         <v>1.394426369574719</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7213888716875563</v>
+        <v>-0.5282413362721845</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.832416789337956</v>
+        <v>2.909675803504105</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9289546560791682</v>
+        <v>-0.7358071206637964</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.747215271700552</v>
+        <v>2.8244742858667</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.346708679626005</v>
+        <v>-1.153561144210633</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.57804055378688</v>
+        <v>2.655299567953029</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.636840346231436</v>
+        <v>-1.443692810816065</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.461854103743629</v>
+        <v>2.539113117909778</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.844844404584514</v>
+        <v>-1.651696869169142</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.383544624956324</v>
+        <v>2.460803639122472</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.056256825472489</v>
+        <v>-1.863109290057117</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.294061112939122</v>
+        <v>2.37132012710527</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.422325552617142</v>
+        <v>-2.22917801720177</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.14071792138771</v>
+        <v>2.217976935553859</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.630816334068826</v>
+        <v>-2.437668798653454</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.077659898545804</v>
+        <v>2.154918912711953</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.878017518834048</v>
+        <v>-2.684869983418676</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.986878175048284</v>
+        <v>2.064137189214433</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.370402546858144</v>
+        <v>-3.177255011442773</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.791030555882378</v>
+        <v>1.868289570048526</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.755582937788217</v>
+        <v>-3.562435402372846</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.635500938323212</v>
+        <v>1.71275995248936</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.005453617802798</v>
+        <v>-3.812306082387427</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.537321789771996</v>
+        <v>1.614580803938144</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.21196539468982</v>
+        <v>-4.018817859274448</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.450823137673445</v>
+        <v>1.528082151839593</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.531309469770322</v>
+        <v>-4.33816193435495</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.324858434341504</v>
+        <v>1.402117448507652</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.963115262920109</v>
+        <v>-4.769967727504738</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.138469004548993</v>
+        <v>1.215728018715142</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.197809257052661</v>
+        <v>-5.00466172163729</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.032876181898063</v>
+        <v>1.110135196064211</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.533471904283114</v>
+        <v>-5.340324368867742</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8971917146618469</v>
+        <v>0.9744507288279953</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.897098149183427</v>
+        <v>-5.703950613768056</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.758228776935963</v>
+        <v>0.8354877911021115</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.262225531822174</v>
+        <v>-6.069077996406802</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6114323388862957</v>
+        <v>0.6886913530524441</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.670814309002852</v>
+        <v>-6.477666773587481</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4467583720287838</v>
+        <v>0.5240173861949318</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.947390409318684</v>
+        <v>-6.754242873903314</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3313133643739112</v>
+        <v>0.4085723785400592</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.363782283605682</v>
+        <v>-7.170634748190311</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1627506652679895</v>
+        <v>0.240009679434138</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.608053684332751</v>
+        <v>-7.414906148917381</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.07530079564584069</v>
+        <v>0.1525598098119891</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.813304703569512</v>
+        <v>-7.620157168154141</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.01070004690316795</v>
+        <v>0.06655896726298005</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.976884581753895</v>
+        <v>-7.783737046338524</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.07772707812192037</v>
+        <v>-0.0004680639557723687</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.273545923564093</v>
+        <v>-8.080398388148723</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1926126389167915</v>
+        <v>-0.1153536247506435</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.460265631873396</v>
+        <v>-8.267118096458026</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2713268267749158</v>
+        <v>-0.1940678126087678</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.843267020616027</v>
+        <v>-8.650119485200657</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4246294835935522</v>
+        <v>-0.3473704694274042</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.025136811601062</v>
+        <v>-8.831989276185691</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4948058840161362</v>
+        <v>-0.4175468698499878</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.384667134105063</v>
+        <v>-9.191519598689693</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6332677097196866</v>
+        <v>-0.5560086955535386</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.435016197559285</v>
+        <v>-9.241868662143915</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6454913151441981</v>
+        <v>-0.5682323009780497</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539465</v>
+        <v>3.501052558539466</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.532635474980681</v>
+        <v>-9.339487939565311</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6814972754909876</v>
+        <v>-0.6042382613248392</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937501</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.680161562986324</v>
+        <v>-9.487014027570954</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7376141543716725</v>
+        <v>-0.6603551402055241</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141704</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.884419738316188</v>
+        <v>-9.691272202900818</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8138042273849755</v>
+        <v>-0.7365452132188275</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729893</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.918072576824661</v>
+        <v>-9.724925041409291</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8227828083039288</v>
+        <v>-0.7455237941377808</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.41055738586864</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440636</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.844602745157212</v>
+        <v>-9.651455209741842</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7780231741435282</v>
+        <v>-0.7007641599773802</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.337087554201192</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.01972716254376</v>
+        <v>-9.826579627128385</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8335177203506285</v>
+        <v>-0.7562587061844805</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.512211971587735</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410274</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.25417925655825</v>
+        <v>-10.06103172114288</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9345177228580206</v>
+        <v>-0.8572587086918726</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.512211971587735</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.35855398758469</v>
+        <v>-10.16540645216932</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9829398060425754</v>
+        <v>-0.9056807918764274</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.616586702614181</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.41134014318502</v>
+        <v>-10.21819260776965</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.00293847844415</v>
+        <v>-0.9256794642780015</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.712262189196578</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.53737693655331</v>
+        <v>-10.34422940113794</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.050659467162351</v>
+        <v>-0.9734004529962026</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.687010566386836</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.48536142258449</v>
+        <v>-10.29221388716912</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.025862925888425</v>
+        <v>-0.9486039117222766</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.687010566386836</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.62703326430861</v>
+        <v>-10.43388572889324</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.084006889476814</v>
+        <v>-1.006747875310666</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.687010566386836</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.57744241988378</v>
+        <v>-10.38429488446841</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.049117141542009</v>
+        <v>-0.9718581273758606</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.637419721962002</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.56463502687901</v>
+        <v>-10.37148749146364</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.057045317986782</v>
+        <v>-0.9797863038206338</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.686275496970903</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615286</v>
+        <v>3.685161381615287</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.33878987415959</v>
+        <v>-10.14564233874422</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9571281838628081</v>
+        <v>-0.8798691696966601</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.64434882138374</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.214211217822</v>
+        <v>-10.02106368240663</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9061575767717129</v>
+        <v>-0.8288985626055649</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.64434882138374</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.71093553364622</v>
+        <v>3.710935533646221</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.26710650586629</v>
+        <v>-10.07395897045092</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9246819178273196</v>
+        <v>-0.8474229036611716</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.639393475295293</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.768951674611572</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.19497333057841</v>
+        <v>-10.00182579516304</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8900949434735308</v>
+        <v>-0.8128359293073828</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.639393475295293</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955331</v>
+        <v>3.728577929955332</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.12360693796876</v>
+        <v>-9.930459402553391</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8712856488235374</v>
+        <v>-0.794026634657389</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.568027082685645</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.03014790398354</v>
+        <v>-9.837000368568166</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8437855165423547</v>
+        <v>-0.7665265023762067</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.568027082685645</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436233</v>
+        <v>3.766317079436234</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.762906103115139</v>
+        <v>-9.569758567699768</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7387233566943694</v>
+        <v>-0.6614643425282214</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.568027082685645</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311953</v>
+        <v>3.784684521311954</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.664999064438648</v>
+        <v>-9.471851529023278</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6998608561972341</v>
+        <v>-0.6226018420310857</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.500041332825089</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097249</v>
+        <v>3.80082935409725</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.64104552346269</v>
+        <v>-9.44789798804732</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6896109336613572</v>
+        <v>-0.6123519194952092</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.476087791849131</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017777</v>
+        <v>3.789311112017778</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.376985585139893</v>
+        <v>-9.183838049724523</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5972472744939905</v>
+        <v>-0.5199882603278425</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.212027853526335</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.669905961635056</v>
+        <v>-8.476758426219686</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3172024587523565</v>
+        <v>-0.2399434445862085</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.212027853526335</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388733</v>
+        <v>3.839374447388735</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.629721663268866</v>
+        <v>-8.436574127853495</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.300785115518039</v>
+        <v>-0.223526101351891</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.171843555160144</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626479</v>
+        <v>3.856161751626481</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.466321792329502</v>
+        <v>-8.273174256914132</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2360583459215366</v>
+        <v>-0.1587993317553886</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.008443684220782</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291815</v>
+        <v>3.787330429291817</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.232840570099903</v>
+        <v>-8.039693034684532</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1347414281918446</v>
+        <v>-0.05748241402569665</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.774962461991183</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785791</v>
+        <v>3.801637122785793</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.083174179092389</v>
+        <v>-7.890026643677017</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07776708210179795</v>
+        <v>-0.0005080679356495033</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.682058970748648</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390431</v>
+        <v>3.763182248390433</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.950898705461502</v>
+        <v>-7.757751170046131</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02948940590241644</v>
+        <v>0.047769608263732</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.549783497117761</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105957</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.79516037290176</v>
+        <v>-7.602012837486389</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.03562098780911693</v>
+        <v>0.1128800019752654</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.394045164558019</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960991</v>
+        <v>3.753882571960992</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.538898534079141</v>
+        <v>-7.351025973773841</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1510320645618233</v>
+        <v>0.2261810886839433</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.394045164558019</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607649</v>
+        <v>3.692931855607651</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.644488523852246</v>
+        <v>-7.456615963546946</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.01917986094663737</v>
+        <v>0.05596916317548306</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.499635154331124</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987907</v>
+        <v>3.77042258398791</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.663223425970843</v>
+        <v>-7.475350865665543</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.02187052008301027</v>
+        <v>0.09701954420513026</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.505231163991255</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710817</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.515283384563244</v>
+        <v>-7.327410824257943</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.03883238604211758</v>
+        <v>0.03631663808000241</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.484910248082697</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.72356622940921</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.462313862309255</v>
+        <v>-7.274441302003955</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02635856339400044</v>
+        <v>0.04879046072811999</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.431940725828709</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098113</v>
+        <v>3.729969716098115</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.418765455538565</v>
+        <v>-7.230892895233264</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01589981278081742</v>
+        <v>0.05924921134130301</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.431940725828709</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493424</v>
+        <v>3.782922533493426</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.176617062084707</v>
+        <v>-6.988744501779406</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09542189898186892</v>
+        <v>0.1705709231039894</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.431940725828709</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82855148672282</v>
+        <v>3.828551486722822</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.068357924962185</v>
+        <v>-6.880485364656884</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1332576742900726</v>
+        <v>0.2084066984121931</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.431940725828709</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792051</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.945066790145054</v>
+        <v>-6.757194229839754</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1800722222275017</v>
+        <v>0.2552212463496222</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.308649591011578</v>
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919912</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.705588390497597</v>
+        <v>-6.73604503093631</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2835645603238097</v>
+        <v>0.2713819041483245</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.069171191364122</v>
+        <v>-1.287500392108135</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.324653626018123</v>
+        <v>2.193656105571716</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.748328408318098</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.461822948514153</v>
+        <v>-6.492279588952866</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3768514454642382</v>
+        <v>0.364668789288753</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.069171191364122</v>
+        <v>-1.287500392108135</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.320434334365174</v>
+        <v>2.189436813918766</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305753</v>
+        <v>3.824311233057531</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.360060128236858</v>
+        <v>-6.390516768675571</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4196808874951721</v>
+        <v>0.4074982313196869</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.055952122971693</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.330490089320647</v>
+        <v>2.199492568874239</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279189</v>
+        <v>3.826354974279191</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.110209734287784</v>
+        <v>-6.140666374726496</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.5123631200585042</v>
+        <v>0.500180463883019</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.055952122971693</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.323232164304349</v>
+        <v>2.192234643857941</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011502</v>
+        <v>3.835957987011504</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.934317641820352</v>
+        <v>-5.964774282259064</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5863190805661258</v>
+        <v>0.5741364243906406</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.055952122971693</v>
+        <v>-1.274281323715706</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.326831287824998</v>
+        <v>2.19583376737859</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392991</v>
+        <v>3.780933911392992</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.762871178797888</v>
+        <v>-5.793327819236601</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6682251718296648</v>
+        <v>0.6560425156541796</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.8845056599492299</v>
+        <v>-1.102834860693243</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.44302667169303</v>
+        <v>2.312029151246622</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632785</v>
+        <v>3.773765222632787</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.688581613059549</v>
+        <v>-5.719038253498262</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6969614757412974</v>
+        <v>0.6847788195658122</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8102160942108907</v>
+        <v>-1.028545294954904</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.48662088875233</v>
+        <v>2.355623368305922</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883078</v>
+        <v>3.76461787988308</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.624945870825615</v>
+        <v>-5.655402511264327</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7271105736891883</v>
+        <v>0.7149279175137035</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7465803519769562</v>
+        <v>-0.9649095527209691</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.529497135147008</v>
+        <v>2.3984996147006</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074788</v>
+        <v>3.79881477107479</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.513519111499694</v>
+        <v>-5.543975751938407</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7528755362033523</v>
+        <v>0.7406928800278672</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7465803519769562</v>
+        <v>-0.9649095527209691</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.510691393930804</v>
+        <v>2.379693873484396</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.7976948842423</v>
+        <v>3.797694884242302</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.273088614694834</v>
+        <v>-5.303545255133547</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8507908115501737</v>
+        <v>0.8386081553746885</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5061498551720959</v>
+        <v>-0.7244790559161088</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.656692768638597</v>
+        <v>2.52569524819219</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936769</v>
+        <v>3.821593509367692</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.200846046523639</v>
+        <v>-5.231302686962352</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8836171526534717</v>
+        <v>0.8714344964779865</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5061498551720959</v>
+        <v>-0.7244790559161088</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.660622082473417</v>
+        <v>2.52962456202701</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879971</v>
+        <v>3.822326997879973</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.147847724242252</v>
+        <v>-5.178304364680964</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9054950654833669</v>
+        <v>0.8933124093078817</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.450813596170157</v>
+        <v>-0.66914279691417</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.694502421791921</v>
+        <v>2.563504901345513</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502343</v>
+        <v>3.848616626502345</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.039042838762525</v>
+        <v>-5.069499479201237</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9460150908952514</v>
+        <v>0.9338324347197662</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.450813596170157</v>
+        <v>-0.66914279691417</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.691500493011914</v>
+        <v>2.560502972565506</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675945</v>
+        <v>3.818668951675947</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.819022040725514</v>
+        <v>-4.849478681164227</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.03560244712067</v>
+        <v>1.023419790945185</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3095937511021768</v>
+        <v>-0.5279229518461898</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.777811437063316</v>
+        <v>2.646813916616909</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539956</v>
+        <v>3.843274527539958</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.686154351662236</v>
+        <v>-4.716610992100949</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.104643705547804</v>
+        <v>1.092461049372319</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3095937511021768</v>
+        <v>-0.5279229518461898</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.79370561986514</v>
+        <v>2.662708099418732</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496265</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.565981268297738</v>
+        <v>-4.59643790873645</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.153858783333905</v>
+        <v>1.14167612715842</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1894206677376779</v>
+        <v>-0.4077498684816908</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.866955314324141</v>
+        <v>2.735957793877733</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577002</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.421309123198</v>
+        <v>-4.451765763636713</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.22181574393524</v>
+        <v>1.209633087759755</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.04474852263794044</v>
+        <v>-0.2630777233819534</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.963846703945423</v>
+        <v>2.832849183499015</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942107</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.481183950555693</v>
+        <v>-4.511640590994405</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.183903304393589</v>
+        <v>1.171720648218104</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1046233499956326</v>
+        <v>-0.3229525507396455</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.913959298932234</v>
+        <v>2.782961778485826</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674519</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.361363719644856</v>
+        <v>-4.391820360083568</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.247120565992132</v>
+        <v>1.234937909816647</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1046233499956326</v>
+        <v>-0.3229525507396455</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.929248468166442</v>
+        <v>2.798250947720035</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430698</v>
       </c>
       <c r="C1935" t="n">
         <v>2.992094879537234</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.363833426106662</v>
+        <v>-4.394290066545374</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.246205084780822</v>
+        <v>1.234022428605337</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1070930564574387</v>
+        <v>-0.3254222572014517</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.927839045662771</v>
+        <v>2.796841525216363</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743220196003607</v>
       </c>
       <c r="C1936" t="n">
         <v>3.003101802011936</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.432203612430672</v>
+        <v>-4.462660252869385</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.22986393272592</v>
+        <v>1.217681276550435</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.09781735742122377</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.944411387559202</v>
+        <v>2.813413867112794</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.714179139508375</v>
       </c>
       <c r="C1937" t="n">
         <v>2.993538510643827</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.445991665277718</v>
+        <v>-4.476448305716431</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.214785420218992</v>
+        <v>1.202602764043508</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.09781735742122377</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.934848096191093</v>
+        <v>2.803850575744685</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417708</v>
+        <v>3.71090673141771</v>
       </c>
       <c r="C1938" t="n">
         <v>2.818248075684214</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.476984824606424</v>
+        <v>-4.507441465045137</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.027097721527897</v>
+        <v>1.014915065352412</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.09781735742122377</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.75955766123148</v>
+        <v>2.628560140785072</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205905</v>
+        <v>3.746042526205906</v>
       </c>
       <c r="C1939" t="n">
         <v>2.822815307676002</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.301510564813954</v>
+        <v>-4.331967205252667</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.101854657436673</v>
+        <v>1.089672001261188</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.09781735742122377</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.764124893223268</v>
+        <v>2.63312737277686</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225451</v>
       </c>
       <c r="C1940" t="n">
         <v>2.798557336437209</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.412446817455203</v>
+        <v>-4.442903457893916</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.03322218514138</v>
+        <v>1.021039528965895</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.09781735742122377</v>
+        <v>-0.3161465581652367</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.739866921984475</v>
+        <v>2.608869401538067</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111298</v>
+        <v>3.7732102971113</v>
       </c>
       <c r="C1941" t="n">
         <v>2.801688721657114</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.378783271982921</v>
+        <v>-4.409239912421634</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.049818988550199</v>
+        <v>1.037636332374714</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.06415381194894193</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.76319643448775</v>
+        <v>2.632198914041342</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264168</v>
+        <v>3.78434395226417</v>
       </c>
       <c r="C1942" t="n">
         <v>2.811861108089247</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.318930652779198</v>
+        <v>-4.349387293217911</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.083932422663821</v>
+        <v>1.071749766488335</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.06415381194894193</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.773368820919882</v>
+        <v>2.642371300473474</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742304</v>
+        <v>3.786949957742306</v>
       </c>
       <c r="C1943" t="n">
         <v>2.806807378663107</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.23268718975282</v>
+        <v>-4.263143830191533</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.113376078448232</v>
+        <v>1.101193422272747</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.06415381194894193</v>
+        <v>-0.2824830126929549</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.768315091493742</v>
+        <v>2.637317571047335</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316051</v>
+        <v>3.752027499316053</v>
       </c>
       <c r="C1944" t="n">
         <v>2.798583154107633</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.2779940091518</v>
+        <v>-4.308450649590513</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.087029126133165</v>
+        <v>1.07484646995768</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1049639749581727</v>
+        <v>-0.3232931757021857</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.735604769132729</v>
+        <v>2.604607248686321</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803196</v>
+        <v>3.753571165803198</v>
       </c>
       <c r="C1945" t="n">
         <v>2.799135027140734</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.307027113854101</v>
+        <v>-4.337483754292814</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.075967757285347</v>
+        <v>1.063785101109862</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1049639749581727</v>
+        <v>-0.3232931757021857</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.736156642165831</v>
+        <v>2.605159121719423</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809503</v>
+        <v>3.733390600809505</v>
       </c>
       <c r="C1946" t="n">
         <v>2.7284077190321</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.214216632403241</v>
+        <v>-4.244673272841954</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.042364641757056</v>
+        <v>1.030181985581571</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.01215349350731337</v>
+        <v>-0.2304826942513263</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.721115622927712</v>
+        <v>2.590118102481304</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560431</v>
+        <v>3.748285816560432</v>
       </c>
       <c r="C1947" t="n">
         <v>2.730281194956701</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.258606101732669</v>
+        <v>-4.289062742171382</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.026482329949886</v>
+        <v>1.014299673774401</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.05654296283674104</v>
+        <v>-0.274872163580754</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.696355417254656</v>
+        <v>2.565357896808249</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472744</v>
+        <v>3.721077195472745</v>
       </c>
       <c r="C1948" t="n">
         <v>2.725356903468424</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.145934883496419</v>
+        <v>-4.176391523935131</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.066626525756109</v>
+        <v>1.054443869580624</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.05612825539950916</v>
+        <v>-0.1622009453445038</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.759033856708129</v>
+        <v>2.628036336261722</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798543</v>
+        <v>3.743047603798544</v>
       </c>
       <c r="C1949" t="n">
         <v>2.730848199299091</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.033557882313746</v>
+        <v>-4.064014522752458</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.117068622059845</v>
+        <v>1.10488596588436</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.05612825539950916</v>
+        <v>-0.1622009453445038</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.764525152538797</v>
+        <v>2.633527632092389</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498871</v>
+        <v>3.689597840498872</v>
       </c>
       <c r="C1950" t="n">
         <v>2.74234540106763</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.061338280215098</v>
+        <v>-4.091794920653811</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.117453664667843</v>
+        <v>1.105271008492358</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.0283478574981561</v>
+        <v>-0.1899813432458569</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.759354115566524</v>
+        <v>2.628356595120116</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705332</v>
+        <v>3.643069621705333</v>
       </c>
       <c r="C1951" t="n">
         <v>2.580701121068283</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.144339561240377</v>
+        <v>-4.17479620167909</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9226088722583852</v>
+        <v>0.9104262160829</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.009776972970982345</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.586567304850873</v>
+        <v>2.455569784404465</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729276</v>
+        <v>3.682716310729278</v>
       </c>
       <c r="C1952" t="n">
         <v>2.700850781787489</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.252953639683708</v>
+        <v>-4.283410280122421</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9993129016002582</v>
+        <v>0.9871302454247732</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.009776972970982345</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.706716965570079</v>
+        <v>2.575719445123671</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190775</v>
+        <v>3.733012441190777</v>
       </c>
       <c r="C1953" t="n">
         <v>2.715363807889812</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.217544601435566</v>
+        <v>-4.248001241874278</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.027989543001838</v>
+        <v>1.015806886826353</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.009776972970982345</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.721229991672402</v>
+        <v>2.590232471225994</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913432</v>
+        <v>3.741174069913434</v>
       </c>
       <c r="C1954" t="n">
         <v>2.712783249232181</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.179160938877414</v>
+        <v>-4.209617579316127</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.040762449367468</v>
+        <v>1.028579793191982</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.04816063552913352</v>
+        <v>-0.1701685652148794</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.741679630549661</v>
+        <v>2.610682110103253</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532493</v>
+        <v>3.751147197532495</v>
       </c>
       <c r="C1955" t="n">
         <v>2.709512278077483</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.002044608842248</v>
+        <v>-4.032501249280961</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.108338010226836</v>
+        <v>1.096155354051351</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.04816063552913352</v>
+        <v>-0.1701685652148794</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.738408659394963</v>
+        <v>2.607411138948556</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793911</v>
+        <v>3.741328448793912</v>
       </c>
       <c r="C1956" t="n">
         <v>2.710195669839396</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.047136853675794</v>
+        <v>-4.077593494114507</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.090984504055331</v>
+        <v>1.078801847879846</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.01373540764025627</v>
+        <v>-0.2320646083842692</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.701954425255243</v>
+        <v>2.570956904808835</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011243</v>
+        <v>3.750729377011245</v>
       </c>
       <c r="C1957" t="n">
         <v>2.70398264514581</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.867761432437026</v>
+        <v>-3.898218072875739</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.156521647857253</v>
+        <v>1.144338991681767</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1430413505304624</v>
+        <v>-0.07528785021355056</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.789807455464088</v>
+        <v>2.65880993501768</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982237</v>
+        <v>3.716991718982239</v>
       </c>
       <c r="C1958" t="n">
         <v>2.6847901004774</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.912775645957633</v>
+        <v>-3.943232286396345</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.1193234177806</v>
+        <v>1.107140761605115</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1126924552158578</v>
+        <v>-0.1056367455281552</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.752405573606915</v>
+        <v>2.621408053160507</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509546</v>
+        <v>3.737026608509548</v>
       </c>
       <c r="C1959" t="n">
         <v>2.690481662816346</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.179780156230068</v>
+        <v>-4.210236796668781</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.018213176010571</v>
+        <v>1.006030519835086</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.08167058282709078</v>
+        <v>-0.2999997835711037</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.641479313120092</v>
+        <v>2.510481792673684</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760817</v>
+        <v>3.702309454760819</v>
       </c>
       <c r="C1960" t="n">
         <v>2.689685584712847</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.280977937667241</v>
+        <v>-4.311434578105954</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9769379853322038</v>
+        <v>0.9647553291567186</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.15007939637241</v>
+        <v>-0.3684085971164229</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.599637946889402</v>
+        <v>2.468640426442994</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815462</v>
+        <v>3.705571661815464</v>
       </c>
       <c r="C1961" t="n">
         <v>2.687285546267164</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.274466971052928</v>
+        <v>-4.304923611491641</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9771423335322456</v>
+        <v>0.9649596773567604</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.15007939637241</v>
+        <v>-0.3684085971164229</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.597237908443718</v>
+        <v>2.466240387997311</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378108</v>
       </c>
       <c r="C1962" t="n">
         <v>2.683810265475409</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.255428843345631</v>
+        <v>-4.285885483784344</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9812823038234093</v>
+        <v>0.9690996476479243</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2082630077036045</v>
+        <v>-0.4265922084476175</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.558852460853247</v>
+        <v>2.427854940406839</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131258</v>
+        <v>3.731064473131259</v>
       </c>
       <c r="C1963" t="n">
         <v>2.86139213441409</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.286555474496249</v>
+        <v>-4.142363761164919</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.146413520301843</v>
+        <v>1.204090205634375</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2082630077036045</v>
+        <v>-0.4265922084476175</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.736434329791927</v>
+        <v>2.60543680934552</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067874</v>
+        <v>3.722447362067875</v>
       </c>
       <c r="C1964" t="n">
         <v>2.862225463400223</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.300422235830167</v>
+        <v>-4.156230522498837</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.141700144754409</v>
+        <v>1.199376830086941</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2461209244374274</v>
+        <v>-0.4644501251814404</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.714552908737767</v>
+        <v>2.583555388291359</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078913</v>
+        <v>3.787425580789131</v>
       </c>
       <c r="C1965" t="n">
         <v>2.868233993797149</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.255618064290237</v>
+        <v>-4.111426350958907</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.165630343767307</v>
+        <v>1.223307029099839</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2461209244374274</v>
+        <v>-0.4644501251814404</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.720561439134693</v>
+        <v>2.589563918688285</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519917</v>
+        <v>3.781501250519918</v>
       </c>
       <c r="C1966" t="n">
         <v>2.947386641589171</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.107875094055235</v>
+        <v>-3.963683380723905</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.30388017965333</v>
+        <v>1.361556864985862</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.07831356720254429</v>
+        <v>-0.2966427679465573</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.900398501267645</v>
+        <v>2.769400980821237</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181179</v>
+        <v>3.80224592918118</v>
       </c>
       <c r="C1967" t="n">
         <v>2.950180263120652</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.209889776586456</v>
+        <v>-4.065698063255126</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.265867928172322</v>
+        <v>1.323544613504854</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.07831356720254429</v>
+        <v>-0.2966427679465573</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.903192122799126</v>
+        <v>2.772194602352718</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394739</v>
+        <v>3.80560898539474</v>
       </c>
       <c r="C1968" t="n">
         <v>2.95084261151231</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.203737070533672</v>
+        <v>-4.059545357202341</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.268991358985094</v>
+        <v>1.326668044317626</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.07216086114976</v>
+        <v>-0.290490061893773</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.907546094822455</v>
+        <v>2.776548574376047</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890617</v>
+        <v>3.798239794890618</v>
       </c>
       <c r="C1969" t="n">
         <v>2.949923088252421</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.220546368684174</v>
+        <v>-4.076354655352843</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.261348116465004</v>
+        <v>1.319024801797536</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.08897015930026164</v>
+        <v>-0.3072993600442746</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.896540992672264</v>
+        <v>2.765543472225856</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798434</v>
+        <v>3.867362636798435</v>
       </c>
       <c r="C1970" t="n">
         <v>3.016258642049241</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.158248369908051</v>
+        <v>-4.014056656576721</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.352602869772274</v>
+        <v>1.410279555104806</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.08897015930026164</v>
+        <v>-0.2450013612681526</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.962876546469085</v>
+        <v>2.86925782528835</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992201</v>
+        <v>3.848729139992202</v>
       </c>
       <c r="C1971" t="n">
         <v>2.724839514438639</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.956458172242893</v>
+        <v>-3.812266458911563</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.141899821227735</v>
+        <v>1.199576506560267</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.1090480328688928</v>
+        <v>-0.04698316909899825</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.790268334159975</v>
+        <v>2.696649612979241</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852431</v>
+        <v>3.841444817852432</v>
       </c>
       <c r="C1972" t="n">
         <v>2.795129746760815</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.883080075154157</v>
+        <v>-3.738888361822827</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.241541292385405</v>
+        <v>1.299217977717937</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.1824261299576293</v>
+        <v>0.0263949279897383</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.904585424735393</v>
+        <v>2.810966703554658</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319556</v>
+        <v>3.819063300319557</v>
       </c>
       <c r="C1973" t="n">
         <v>2.809757482876858</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.980820619779131</v>
+        <v>-3.836628906447801</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.217072810651459</v>
+        <v>1.274749495983991</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.1665368518246491</v>
+        <v>0.01050564985675811</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.909679593971648</v>
+        <v>2.816060872790914</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.80829346370153</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.157158379902061</v>
+        <v>-4.012966666570731</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.145073687426958</v>
+        <v>1.20275037275949</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.009800908298280286</v>
+        <v>-0.1658321102661713</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.802412918722562</v>
+        <v>2.708794197541827</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397804</v>
+        <v>3.836411672397805</v>
       </c>
       <c r="C1975" t="n">
         <v>2.806785081741459</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.080736333470134</v>
+        <v>-3.936544620138804</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.174134124039658</v>
+        <v>1.23181080937219</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.009800908298280286</v>
+        <v>-0.1658321102661713</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.800904536762491</v>
+        <v>2.707285815581756</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316259</v>
+        <v>3.83351346031626</v>
       </c>
       <c r="C1976" t="n">
         <v>2.806647949176895</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.036363201831565</v>
+        <v>-3.892171488500235</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.191746244130521</v>
+        <v>1.249422929463053</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.03457222334028831</v>
+        <v>-0.1214589786276027</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.827391283181068</v>
+        <v>2.733772562000333</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105973</v>
+        <v>3.821562117105974</v>
       </c>
       <c r="C1977" t="n">
         <v>2.801041743315485</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.913528980944398</v>
+        <v>-3.769337267613068</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.235273726623979</v>
+        <v>1.292950411956511</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.03457222334028831</v>
+        <v>-0.1214589786276027</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.821785077319658</v>
+        <v>2.728166356138924</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190331</v>
+        <v>3.833011148190332</v>
       </c>
       <c r="C1978" t="n">
         <v>2.807423500343289</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.865873250383342</v>
+        <v>-3.721681537052012</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.260717775876205</v>
+        <v>1.318394461208737</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.08222795390134396</v>
+        <v>-0.07380324806654703</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.856760272684096</v>
+        <v>2.763141551503362</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569624</v>
+        <v>3.822678210569625</v>
       </c>
       <c r="C1979" t="n">
         <v>2.812315873718014</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.765355091884588</v>
+        <v>-3.621163378553257</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.305817412650432</v>
+        <v>1.363494097982964</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.1827461124000985</v>
+        <v>0.02671491043220753</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.921963541158074</v>
+        <v>2.828344819977339</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557299</v>
+        <v>3.8288088775573</v>
       </c>
       <c r="C1980" t="n">
         <v>2.799070546193887</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.826021682286977</v>
+        <v>-3.681829968955646</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.268305448965349</v>
+        <v>1.325982134297881</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.1010477956815649</v>
+        <v>-0.05498340628632614</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.859699223602826</v>
+        <v>2.766080502422091</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932774</v>
+        <v>3.816837033932775</v>
       </c>
       <c r="C1981" t="n">
         <v>2.803168248804515</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.781183280678579</v>
+        <v>-3.636991567347248</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.290338512219336</v>
+        <v>1.348015197551868</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.1055912286264343</v>
+        <v>-0.05043997334145667</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.866522985980376</v>
+        <v>2.772904264799641</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917058</v>
+        <v>3.817932354917059</v>
       </c>
       <c r="C1982" t="n">
         <v>2.807329188435593</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.881941916435577</v>
+        <v>-3.737750203104247</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.254195997547615</v>
+        <v>1.311872682880147</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.01676565989942891</v>
+        <v>-0.1392655420684621</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.817388584375251</v>
+        <v>2.723769863194516</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.81320879096343</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.837739079349677</v>
+        <v>-3.693547366018346</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.277756734909812</v>
+        <v>1.335433420242344</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.06096849698532936</v>
+        <v>-0.09506270498256164</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.849789889154628</v>
+        <v>2.756171167973894</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.811618791432678</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.87471810701312</v>
+        <v>-3.73052639368179</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.261375124313683</v>
+        <v>1.319051809646215</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.09794239877665989</v>
+        <v>-0.05808880319123111</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.870384230698674</v>
+        <v>2.77676550951794</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.862866556615717</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.89477618587796</v>
+        <v>-3.75058447254663</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.304599657950786</v>
+        <v>1.362276343283318</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.09794239877665989</v>
+        <v>-0.05808880319123111</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.921631995881714</v>
+        <v>2.828013274700979</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.861307261209971</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.85484551270007</v>
+        <v>-3.710653799368739</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.319012631816195</v>
+        <v>1.376689317148728</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.1378730719545502</v>
+        <v>-0.01815813001334077</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.944031104382701</v>
+        <v>2.850412383201967</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.856255489448241</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.803813419977542</v>
+        <v>-3.659621706646211</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.334373697143477</v>
+        <v>1.392050382476009</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.1889051646770782</v>
+        <v>0.03287396270918719</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.969598588254488</v>
+        <v>2.875979867073753</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.873442893540946</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.738589238850336</v>
+        <v>-3.594397525519006</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.377650773687064</v>
+        <v>1.435327459019596</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.2541293458042838</v>
+        <v>0.09809814383639281</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.025920501023516</v>
+        <v>2.932301779842781</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.869403865840226</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.701162218779202</v>
+        <v>-3.556970505447872</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.388582554014798</v>
+        <v>1.44625923934733</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.2593808838334655</v>
+        <v>0.1033496818655745</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.025032396140305</v>
+        <v>2.931413674959571</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.870660658171466</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.721273874813911</v>
+        <v>-3.577082161482581</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.381794683932155</v>
+        <v>1.439471369264687</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.2704082288308847</v>
+        <v>0.1143770268629937</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.032905595469997</v>
+        <v>2.939286874289263</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.031218429192677</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.667529060386706</v>
+        <v>-3.523337347055376</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.563850380724247</v>
+        <v>1.621527066056779</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.2804715382713466</v>
+        <v>0.1244403363034556</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.199501352155485</v>
+        <v>3.10588263097475</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.151331338410494</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.643737491780564</v>
+        <v>-3.499545778449233</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.693479917384521</v>
+        <v>1.751156602717054</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.3042631068774889</v>
+        <v>0.1482319049095979</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.333889202536988</v>
+        <v>3.240270481356253</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.143039314424353</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.617653407516756</v>
+        <v>-3.473461694185425</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.695621527103904</v>
+        <v>1.753298212436436</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.3042631068774889</v>
+        <v>0.1482319049095979</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.325597178550847</v>
+        <v>3.231978457370112</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.141232510008133</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.539522226667809</v>
+        <v>-3.395330513336479</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.725067195027262</v>
+        <v>1.782743880359794</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3784399177611735</v>
+        <v>0.2224087157932825</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.368296460664837</v>
+        <v>3.274677739484102</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959864</v>
+        <v>3.796264143959863</v>
       </c>
       <c r="C1995" t="n">
         <v>3.158786915734924</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.530629765274526</v>
+        <v>-3.386438051943196</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.746178585311366</v>
+        <v>1.803855270643898</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3784399177611735</v>
+        <v>0.2224087157932825</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.385850866391628</v>
+        <v>3.292232145210894</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.150641963139508</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.699105882244404</v>
+        <v>-3.554914168913073</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.670643185927999</v>
+        <v>1.728319871260531</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3504920820445927</v>
+        <v>0.1944608800767017</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.360937212366264</v>
+        <v>3.267318491185529</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782716</v>
+        <v>3.795574066782715</v>
       </c>
       <c r="C1997" t="n">
         <v>3.13191166032737</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.00130635338282</v>
+        <v>-2.85711464005149</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.931032694660495</v>
+        <v>1.988709379993026</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.280144022674182</v>
+        <v>0.124112820706291</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.299998073931879</v>
+        <v>3.206379352751145</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632646</v>
+        <v>3.784671345632645</v>
       </c>
       <c r="C1998" t="n">
         <v>3.122575682824274</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.978585249699668</v>
+        <v>-2.834393536368338</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.93078515863066</v>
+        <v>1.988461843963192</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.280144022674182</v>
+        <v>0.124112820706291</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.290662096428784</v>
+        <v>3.197043375248049</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777684</v>
+        <v>3.783205696777682</v>
       </c>
       <c r="C1999" t="n">
         <v>3.281481808675443</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.976860206409624</v>
+        <v>-2.832668493078294</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.090381301797847</v>
+        <v>2.148057987130379</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.2818690659642257</v>
+        <v>0.1258378639963347</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.450603248253979</v>
+        <v>3.356984527073244</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644423</v>
+        <v>3.779933725644421</v>
       </c>
       <c r="C2000" t="n">
         <v>3.31855963116909</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.131641213187879</v>
+        <v>-2.987449499856549</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.065546721580191</v>
+        <v>2.123223406912723</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.2485013919097496</v>
+        <v>0.09247018994185863</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.46766046631494</v>
+        <v>3.374041745134206</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979997</v>
+        <v>3.769443619799969</v>
       </c>
       <c r="C2001" t="n">
         <v>3.315234987158635</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.080205879803219</v>
+        <v>-2.936014166471889</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.0827962109236</v>
+        <v>2.140472896256132</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.2999367252944093</v>
+        <v>0.1439055233265183</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.495197022335281</v>
+        <v>3.401578301154546</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331125</v>
+        <v>3.766673496331124</v>
       </c>
       <c r="C2002" t="n">
         <v>3.325241140803377</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.053254655476731</v>
+        <v>-2.909062942145401</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.103582854298937</v>
+        <v>2.161259539631469</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.3148170713221284</v>
+        <v>0.1587858693542374</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.514131383596654</v>
+        <v>3.420512662415919</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784119</v>
+        <v>3.768052067784117</v>
       </c>
       <c r="C2003" t="n">
         <v>3.509344272948336</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.189207663533048</v>
+        <v>-3.045015950201718</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.23330478322137</v>
+        <v>2.290981468553902</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.3148170713221284</v>
+        <v>0.1587858693542374</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.698234515741614</v>
+        <v>3.604615794560879</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714432</v>
+        <v>3.74392550571443</v>
       </c>
       <c r="C2004" t="n">
         <v>3.50146096785133</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.21161578133792</v>
+        <v>-3.06742406800659</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.216458231002414</v>
+        <v>2.274134916334947</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.3148170713221284</v>
+        <v>0.1587858693542374</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.690351210644607</v>
+        <v>3.596732489463872</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155042</v>
+        <v>3.719118627155041</v>
       </c>
       <c r="C2005" t="n">
         <v>3.503514967400967</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.359621548817319</v>
+        <v>-3.215429835485989</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.159309923560292</v>
+        <v>2.216986608892824</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.228090062458587</v>
+        <v>0.07205886049069599</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.640369004876119</v>
+        <v>3.546750283695385</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161988</v>
+        <v>3.729452285161986</v>
       </c>
       <c r="C2006" t="n">
         <v>3.559768685122814</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.369062474705849</v>
+        <v>-3.224870761374519</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.211787270926727</v>
+        <v>2.269463956259259</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.3505171800019784</v>
+        <v>0.1944859780340874</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.770078993124002</v>
+        <v>3.676460271943267</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321645</v>
+        <v>3.714941193321643</v>
       </c>
       <c r="C2007" t="n">
         <v>3.562659779668115</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.367775711166293</v>
+        <v>-3.223583997834963</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.21519307088785</v>
+        <v>2.272869756220382</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.351803943541535</v>
+        <v>0.195772741573644</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.773742145793036</v>
+        <v>3.680123424612302</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347713</v>
+        <v>3.727898186347711</v>
       </c>
       <c r="C2008" t="n">
         <v>3.56077159256189</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.369332765155584</v>
+        <v>-3.225141051824254</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.212682062185909</v>
+        <v>2.270358747518441</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.351803943541535</v>
+        <v>0.195772741573644</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.771853958686811</v>
+        <v>3.678235237506077</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887757</v>
+        <v>3.710654104887755</v>
       </c>
       <c r="C2009" t="n">
         <v>3.555591822164752</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.376604650679049</v>
+        <v>-3.232412937347719</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.204593537579385</v>
+        <v>2.262270222911918</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.3445320580180702</v>
+        <v>0.1885008560501792</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.762311056975595</v>
+        <v>3.66869233579486</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343075</v>
+        <v>3.712897612343073</v>
       </c>
       <c r="C2010" t="n">
         <v>3.554025832374905</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.374763631620798</v>
+        <v>-3.230571918289467</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.203763955412839</v>
+        <v>2.26144064074537</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3458002846895387</v>
+        <v>0.1897690827216477</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.761506003188628</v>
+        <v>3.667887282007894</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647116</v>
+        <v>3.754911907647114</v>
       </c>
       <c r="C2011" t="n">
         <v>3.567099239240823</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.381672337120478</v>
+        <v>-3.237480623789148</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.214073880078885</v>
+        <v>2.271750565411417</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3458002846895387</v>
+        <v>0.1897690827216477</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.774579410054547</v>
+        <v>3.680960688873812</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763538</v>
+        <v>3.749896851763537</v>
       </c>
       <c r="C2012" t="n">
         <v>3.567099239240823</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.383233979935338</v>
+        <v>-3.239042266604008</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.213449222952941</v>
+        <v>2.271125908285473</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3458002846895387</v>
+        <v>0.1897690827216477</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.774579410054547</v>
+        <v>3.680960688873812</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392122</v>
+        <v>3.71583405539212</v>
       </c>
       <c r="C2013" t="n">
         <v>3.565623280367825</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.411134767044811</v>
+        <v>-3.266943053713481</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.200812949236154</v>
+        <v>2.258489634568686</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3112033605466039</v>
+        <v>0.1551721585787129</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.752345296695788</v>
+        <v>3.658726575515054</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172533</v>
+        <v>3.684909939172532</v>
       </c>
       <c r="C2014" t="n">
         <v>3.562387724345024</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.414167764557485</v>
+        <v>-3.269976051226155</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.196364194208283</v>
+        <v>2.254040879540815</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.30817036303393</v>
+        <v>0.152139161066039</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.747289942165382</v>
+        <v>3.653671220984648</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,45 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.409893696067393</v>
+        <v>3.619362241971084</v>
       </c>
       <c r="C2015" t="n">
         <v>3.629093683935528</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.715216614894124</v>
+        <v>-3.290037372502661</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.142650613664131</v>
+        <v>2.312722310620716</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.007121512697290777</v>
+        <v>0.132077839789532</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.633366591553902</v>
+        <v>3.708340387809247</v>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" s="2" t="n">
+        <v>45478</v>
+      </c>
+      <c r="B2016" t="n">
+        <v>3.830926303678913</v>
+      </c>
+      <c r="C2016" t="n">
+        <v>3.771538250367598</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>-3.290037372502661</v>
+      </c>
+      <c r="E2016" t="n">
+        <v>2.312722310620716</v>
+      </c>
+      <c r="F2016" t="n">
+        <v>0.132077839789532</v>
+      </c>
+      <c r="G2016" t="n">
+        <v>3.764602047353966</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240705.xlsx
+++ b/tame_output/ON/bt/strategyON_20240705.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,22 +849,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>48.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-662.0%</t>
+          <t>-681.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>-69.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>434.0%</t>
+          <t>448.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-490.6%</t>
+          <t>-521.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-265.2%</t>
+          <t>-272.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.4%</t>
+          <t>-40.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-41.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-144.9%</t>
+          <t>-157.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-183.0%</t>
+          <t>-209.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-210.8%</t>
+          <t>-205.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-69.6%</t>
+          <t>-86.3%</t>
         </is>
       </c>
     </row>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3792603279725552</v>
+        <v>-0.5724078633879268</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.974420164035016</v>
+        <v>2.897161149868867</v>
       </c>
       <c r="F1843" t="n">
         <v>1.367390796168583</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4610322284003069</v>
+        <v>-0.6541797638156785</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.931794129819154</v>
+        <v>2.854535115653005</v>
       </c>
       <c r="F1844" t="n">
         <v>1.394426369574719</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5282413362721845</v>
+        <v>-0.7213888716875563</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.909675803504105</v>
+        <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7358071206637964</v>
+        <v>-0.9289546560791682</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.8244742858667</v>
+        <v>2.747215271700552</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.153561144210633</v>
+        <v>-1.346708679626005</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.655299567953029</v>
+        <v>2.57804055378688</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.443692810816065</v>
+        <v>-1.636840346231436</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.539113117909778</v>
+        <v>2.461854103743629</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.651696869169142</v>
+        <v>-1.844844404584514</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.460803639122472</v>
+        <v>2.383544624956324</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.863109290057117</v>
+        <v>-2.056256825472489</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.37132012710527</v>
+        <v>2.294061112939122</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.22917801720177</v>
+        <v>-2.422325552617142</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.217976935553859</v>
+        <v>2.14071792138771</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.437668798653454</v>
+        <v>-2.630816334068826</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.154918912711953</v>
+        <v>2.077659898545804</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.684869983418676</v>
+        <v>-2.878017518834048</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.064137189214433</v>
+        <v>1.986878175048284</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.177255011442773</v>
+        <v>-3.370402546858144</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.868289570048526</v>
+        <v>1.791030555882378</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.562435402372846</v>
+        <v>-3.755582937788217</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.71275995248936</v>
+        <v>1.635500938323212</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.812306082387427</v>
+        <v>-4.005453617802798</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.614580803938144</v>
+        <v>1.537321789771996</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.018817859274448</v>
+        <v>-4.21196539468982</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.528082151839593</v>
+        <v>1.450823137673445</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.33816193435495</v>
+        <v>-4.531309469770322</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.402117448507652</v>
+        <v>1.324858434341504</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.769967727504738</v>
+        <v>-4.963115262920109</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.215728018715142</v>
+        <v>1.138469004548993</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.00466172163729</v>
+        <v>-5.197809257052661</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.110135196064211</v>
+        <v>1.032876181898063</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.340324368867742</v>
+        <v>-5.533471904283114</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9744507288279953</v>
+        <v>0.8971917146618469</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.703950613768056</v>
+        <v>-5.897098149183427</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8354877911021115</v>
+        <v>0.758228776935963</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.069077996406802</v>
+        <v>-6.262225531822174</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6886913530524441</v>
+        <v>0.6114323388862957</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.477666773587481</v>
+        <v>-6.670814309002852</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5240173861949318</v>
+        <v>0.4467583720287838</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.754242873903314</v>
+        <v>-6.947390409318684</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4085723785400592</v>
+        <v>0.3313133643739112</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.170634748190311</v>
+        <v>-7.363782283605682</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.240009679434138</v>
+        <v>0.1627506652679895</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.414906148917381</v>
+        <v>-7.608053684332751</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1525598098119891</v>
+        <v>0.07530079564584069</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.620157168154141</v>
+        <v>-7.813304703569512</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.06655896726298005</v>
+        <v>-0.01070004690316795</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.783737046338524</v>
+        <v>-7.976884581753895</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.0004680639557723687</v>
+        <v>-0.07772707812192037</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.080398388148723</v>
+        <v>-8.273545923564093</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1153536247506435</v>
+        <v>-0.1926126389167915</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.267118096458026</v>
+        <v>-8.460265631873396</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.1940678126087678</v>
+        <v>-0.2713268267749158</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.650119485200657</v>
+        <v>-8.843267020616027</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3473704694274042</v>
+        <v>-0.4246294835935522</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.831989276185691</v>
+        <v>-9.025136811601062</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4175468698499878</v>
+        <v>-0.4948058840161362</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.191519598689693</v>
+        <v>-9.384667134105063</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5560086955535386</v>
+        <v>-0.6332677097196866</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.241868662143915</v>
+        <v>-9.435016197559285</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.5682323009780497</v>
+        <v>-0.6454913151441981</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539466</v>
+        <v>3.501052558539465</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.339487939565311</v>
+        <v>-9.532635474980681</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6042382613248392</v>
+        <v>-0.6814972754909876</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937501</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.487014027570954</v>
+        <v>-9.680161562986324</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6603551402055241</v>
+        <v>-0.7376141543716725</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141704</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.691272202900818</v>
+        <v>-9.884419738316188</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7365452132188275</v>
+        <v>-0.8138042273849755</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729893</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.724925041409291</v>
+        <v>-9.918072576824661</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7455237941377808</v>
+        <v>-0.8227828083039288</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.41055738586864</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440636</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.651455209741842</v>
+        <v>-9.844602745157212</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7007641599773802</v>
+        <v>-0.7780231741435282</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.337087554201192</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.826579627128385</v>
+        <v>-10.01972716254376</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.7562587061844805</v>
+        <v>-0.8335177203506285</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.512211971587735</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410274</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.06103172114288</v>
+        <v>-10.25417925655825</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.8572587086918726</v>
+        <v>-0.9345177228580206</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.512211971587735</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.16540645216932</v>
+        <v>-10.35855398758469</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9056807918764274</v>
+        <v>-0.9829398060425754</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.616586702614181</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.21819260776965</v>
+        <v>-10.41134014318502</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9256794642780015</v>
+        <v>-1.00293847844415</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.712262189196578</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.34422940113794</v>
+        <v>-10.53737693655331</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9734004529962026</v>
+        <v>-1.050659467162351</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.687010566386836</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.29221388716912</v>
+        <v>-10.48536142258449</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9486039117222766</v>
+        <v>-1.025862925888425</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.687010566386836</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.43388572889324</v>
+        <v>-10.62703326430861</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.006747875310666</v>
+        <v>-1.084006889476814</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.687010566386836</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940722</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.38429488446841</v>
+        <v>-10.57744241988378</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9718581273758606</v>
+        <v>-1.049117141542009</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.637419721962002</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770583</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.37148749146364</v>
+        <v>-10.56463502687901</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.9797863038206338</v>
+        <v>-1.057045317986782</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.686275496970903</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615287</v>
+        <v>3.685161381615286</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.14564233874422</v>
+        <v>-10.33878987415959</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.8798691696966601</v>
+        <v>-0.9571281838628081</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.64434882138374</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.02106368240663</v>
+        <v>-10.214211217822</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8288985626055649</v>
+        <v>-0.9061575767717129</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.64434882138374</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646221</v>
+        <v>3.71093553364622</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.07395897045092</v>
+        <v>-10.26710650586629</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8474229036611716</v>
+        <v>-0.9246819178273196</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.639393475295293</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611572</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.00182579516304</v>
+        <v>-10.19497333057841</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8128359293073828</v>
+        <v>-0.8900949434735308</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.639393475295293</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955332</v>
+        <v>3.728577929955331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.930459402553391</v>
+        <v>-10.12360693796876</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.794026634657389</v>
+        <v>-0.8712856488235374</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.568027082685645</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.837000368568166</v>
+        <v>-10.03014790398354</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7665265023762067</v>
+        <v>-0.8437855165423547</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.568027082685645</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436234</v>
+        <v>3.766317079436233</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.569758567699768</v>
+        <v>-9.762906103115139</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6614643425282214</v>
+        <v>-0.7387233566943694</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.568027082685645</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311954</v>
+        <v>3.784684521311953</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.471851529023278</v>
+        <v>-9.664999064438648</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6226018420310857</v>
+        <v>-0.6998608561972341</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.500041332825089</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409725</v>
+        <v>3.800829354097249</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.44789798804732</v>
+        <v>-9.64104552346269</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6123519194952092</v>
+        <v>-0.6896109336613572</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.476087791849131</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017778</v>
+        <v>3.789311112017777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.183838049724523</v>
+        <v>-9.376985585139893</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5199882603278425</v>
+        <v>-0.5972472744939905</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.212027853526335</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.476758426219686</v>
+        <v>-8.669905961635056</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2399434445862085</v>
+        <v>-0.3172024587523565</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.212027853526335</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388735</v>
+        <v>3.839374447388733</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.436574127853495</v>
+        <v>-8.629721663268866</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.223526101351891</v>
+        <v>-0.300785115518039</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.171843555160144</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626481</v>
+        <v>3.856161751626479</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.273174256914132</v>
+        <v>-8.466321792329502</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1587993317553886</v>
+        <v>-0.2360583459215366</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.008443684220782</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291817</v>
+        <v>3.787330429291815</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.039693034684532</v>
+        <v>-8.232840570099903</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.05748241402569665</v>
+        <v>-0.1347414281918446</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.774962461991183</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785793</v>
+        <v>3.801637122785791</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.890026643677017</v>
+        <v>-8.083174179092389</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.0005080679356495033</v>
+        <v>-0.07776708210179795</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.682058970748648</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390433</v>
+        <v>3.763182248390431</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.757751170046131</v>
+        <v>-7.950898705461502</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.047769608263732</v>
+        <v>-0.02948940590241644</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.549783497117761</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105957</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.602012837486389</v>
+        <v>-7.79516037290176</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1128800019752654</v>
+        <v>0.03562098780911693</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.394045164558019</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960992</v>
+        <v>3.753882571960991</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.351025973773841</v>
+        <v>-7.546160574218179</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2261810886839433</v>
+        <v>0.1481272485062082</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.394045164558019</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607651</v>
+        <v>3.692931855607649</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.456615963546946</v>
+        <v>-7.651750563991284</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.05596916317548306</v>
+        <v>-0.02208467700225247</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.499635154331124</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.77042258398791</v>
+        <v>3.770422583987908</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.475350865665543</v>
+        <v>-7.670485466109881</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.09701954420513026</v>
+        <v>0.01896570402739517</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.505231163991255</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710817</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.327410824257943</v>
+        <v>-7.522545424702281</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.03631663808000241</v>
+        <v>-0.04173720209773268</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.484910248082697</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.72356622940921</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.274441302003955</v>
+        <v>-7.469575902448293</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.04879046072811999</v>
+        <v>-0.02926337944961555</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.431940725828709</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098115</v>
+        <v>3.729969716098113</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.230892895233264</v>
+        <v>-7.426027495677602</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.05924921134130301</v>
+        <v>-0.01880462883643252</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.431940725828709</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493426</v>
+        <v>3.782922533493424</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.988744501779406</v>
+        <v>-7.183879102223744</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1705709231039894</v>
+        <v>0.09251708292625382</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.431940725828709</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722822</v>
+        <v>3.82855148672282</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.880485364656884</v>
+        <v>-7.075619965101223</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.2084066984121931</v>
+        <v>0.1303528582344575</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.431940725828709</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792051</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.757194229839754</v>
+        <v>-6.952328830284092</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2552212463496222</v>
+        <v>0.1771674061718866</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.308649591011578</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919912</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.73604503093631</v>
+        <v>-6.931179631380648</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2713819041483245</v>
+        <v>0.1933280639705894</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.287500392108135</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318098</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.492279588952866</v>
+        <v>-6.687414189397204</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.364668789288753</v>
+        <v>0.2866149491110179</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.287500392108135</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057531</v>
+        <v>3.82431123305753</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.390516768675571</v>
+        <v>-6.585651369119909</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.4074982313196869</v>
+        <v>0.3294443911419518</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.274281323715706</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279191</v>
+        <v>3.826354974279189</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.140666374726496</v>
+        <v>-6.335800975170835</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.500180463883019</v>
+        <v>0.4221266237052839</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.274281323715706</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011504</v>
+        <v>3.835957987011502</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.964774282259064</v>
+        <v>-6.159908882703402</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5741364243906406</v>
+        <v>0.4960825842129055</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.274281323715706</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392992</v>
+        <v>3.780933911392991</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.793327819236601</v>
+        <v>-5.988462419680938</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6560425156541796</v>
+        <v>0.5779886754764449</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.102834860693243</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632787</v>
+        <v>3.773765222632785</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.719038253498262</v>
+        <v>-5.914172853942599</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6847788195658122</v>
+        <v>0.6067249793880776</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.028545294954904</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988308</v>
+        <v>3.764617879883078</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.655402511264327</v>
+        <v>-5.850537111708665</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7149279175137035</v>
+        <v>0.6368740773359685</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.9649095527209691</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107479</v>
+        <v>3.798814771074788</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.543975751938407</v>
+        <v>-5.739110352382744</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7406928800278672</v>
+        <v>0.6626390398501321</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.9649095527209691</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242302</v>
+        <v>3.7976948842423</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.303545255133547</v>
+        <v>-5.498679855577884</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8386081553746885</v>
+        <v>0.7605543151969538</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7244790559161088</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367692</v>
+        <v>3.82159350936769</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.231302686962352</v>
+        <v>-5.42643728740669</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8714344964779865</v>
+        <v>0.7933806563002519</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7244790559161088</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879973</v>
+        <v>3.822326997879971</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.178304364680964</v>
+        <v>-5.373438965125302</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8933124093078817</v>
+        <v>0.815258569130147</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.66914279691417</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502345</v>
+        <v>3.848616626502343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.069499479201237</v>
+        <v>-5.264634079645575</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9338324347197662</v>
+        <v>0.8557785945420311</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.66914279691417</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675947</v>
+        <v>3.818668951675945</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.849478681164227</v>
+        <v>-5.044613281608564</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.023419790945185</v>
+        <v>0.9453659507674494</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5279229518461898</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539958</v>
+        <v>3.843274527539956</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.716610992100949</v>
+        <v>-4.911745592545286</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.092461049372319</v>
+        <v>1.014407209194584</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5279229518461898</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496265</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.59643790873645</v>
+        <v>-4.791572509180788</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.14167612715842</v>
+        <v>1.063622286980685</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4077498684816908</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577002</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.451765763636713</v>
+        <v>-4.64690036408105</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.209633087759755</v>
+        <v>1.13157924758202</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.2630777233819534</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942107</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.511640590994405</v>
+        <v>-4.706775191438743</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.171720648218104</v>
+        <v>1.093666808040369</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3229525507396455</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674519</v>
+        <v>3.762647477674517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.391820360083568</v>
+        <v>-4.586954960527906</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.234937909816647</v>
+        <v>1.156884069638912</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3229525507396455</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430698</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.992094879537234</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.394290066545374</v>
+        <v>-4.589424666989712</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.234022428605337</v>
+        <v>1.155968588427602</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3254222572014517</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003607</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
         <v>3.003101802011936</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.462660252869385</v>
+        <v>-4.657794853313722</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.217681276550435</v>
+        <v>1.1396274363727</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3161465581652367</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508375</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
         <v>2.993538510643827</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.476448305716431</v>
+        <v>-4.671582906160769</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.202602764043508</v>
+        <v>1.124548923865773</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3161465581652367</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.71090673141771</v>
+        <v>3.710906731417708</v>
       </c>
       <c r="C1938" t="n">
         <v>2.818248075684214</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.507441465045137</v>
+        <v>-4.702576065489474</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.014915065352412</v>
+        <v>0.9368612251746773</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3161465581652367</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205906</v>
+        <v>3.746042526205905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.822815307676002</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.331967205252667</v>
+        <v>-4.527101805697004</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.089672001261188</v>
+        <v>1.011618161083453</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3161465581652367</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225451</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.798557336437209</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.442903457893916</v>
+        <v>-4.638038058338253</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.021039528965895</v>
+        <v>0.9429856887881605</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3161465581652367</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.7732102971113</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.801688721657114</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.409239912421634</v>
+        <v>-4.604374512865971</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.037636332374714</v>
+        <v>0.9595824921969789</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2824830126929549</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226417</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.811861108089247</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.349387293217911</v>
+        <v>-4.544521893662248</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.071749766488335</v>
+        <v>0.9936959263106004</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2824830126929549</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742306</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.806807378663107</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.263143830191533</v>
+        <v>-4.45827843063587</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.101193422272747</v>
+        <v>1.023139582095012</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2824830126929549</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316053</v>
+        <v>3.752027499316051</v>
       </c>
       <c r="C1944" t="n">
         <v>2.798583154107633</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.308450649590513</v>
+        <v>-4.50358525003485</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.07484646995768</v>
+        <v>0.9967926297799454</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3232931757021857</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803198</v>
+        <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
         <v>2.799135027140734</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.337483754292814</v>
+        <v>-4.532618354737151</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.063785101109862</v>
+        <v>0.9857312609321265</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3232931757021857</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809505</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.7284077190321</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.244673272841954</v>
+        <v>-4.439807873286291</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.030181985581571</v>
+        <v>0.9521281454038362</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2304826942513263</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560432</v>
+        <v>3.74828581656043</v>
       </c>
       <c r="C1947" t="n">
         <v>2.730281194956701</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.289062742171382</v>
+        <v>-4.484197342615719</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.014299673774401</v>
+        <v>0.9362458335966659</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.274872163580754</v>
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472745</v>
+        <v>3.721077195472743</v>
       </c>
       <c r="C1948" t="n">
         <v>2.725356903468424</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.176391523935131</v>
+        <v>-4.313430897279377</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.054443869580624</v>
+        <v>0.9996281202429256</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1622009453445038</v>
+        <v>-0.1041057182444122</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.628036336261722</v>
+        <v>2.662893472521777</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798544</v>
+        <v>3.743047603798543</v>
       </c>
       <c r="C1949" t="n">
         <v>2.730848199299091</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.064014522752458</v>
+        <v>-4.201053896096704</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.10488596588436</v>
+        <v>1.050070216546662</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1622009453445038</v>
+        <v>-0.1041057182444122</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.633527632092389</v>
+        <v>2.668384768352444</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498872</v>
+        <v>3.689597840498871</v>
       </c>
       <c r="C1950" t="n">
         <v>2.74234540106763</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.091794920653811</v>
+        <v>-4.228834293998057</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.105271008492358</v>
+        <v>1.05045525915466</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1899813432458569</v>
+        <v>-0.1318861161457653</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.628356595120116</v>
+        <v>2.663213731380171</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705333</v>
+        <v>3.643069621705331</v>
       </c>
       <c r="C1951" t="n">
         <v>2.580701121068283</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.17479620167909</v>
+        <v>-4.311835575023336</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9104262160829</v>
+        <v>0.8556104667452016</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.150457000672939</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.455569784404465</v>
+        <v>2.49042692066452</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729278</v>
+        <v>3.682716310729276</v>
       </c>
       <c r="C1952" t="n">
         <v>2.700850781787489</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.283410280122421</v>
+        <v>-4.420449653466667</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9871302454247732</v>
+        <v>0.9323144960870748</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.150457000672939</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.575719445123671</v>
+        <v>2.610576581383726</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190777</v>
+        <v>3.733012441190775</v>
       </c>
       <c r="C1953" t="n">
         <v>2.715363807889812</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.248001241874278</v>
+        <v>-4.385040615218524</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.015806886826353</v>
+        <v>0.9609911374886551</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2085522277730306</v>
+        <v>-0.150457000672939</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.590232471225994</v>
+        <v>2.625089607486049</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913434</v>
+        <v>3.741174069913432</v>
       </c>
       <c r="C1954" t="n">
         <v>2.712783249232181</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.209617579316127</v>
+        <v>-4.346656952660373</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.028579793191982</v>
+        <v>0.9737640438542841</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1701685652148794</v>
+        <v>-0.1120733381147879</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.610682110103253</v>
+        <v>2.645539246363308</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532495</v>
+        <v>3.751147197532493</v>
       </c>
       <c r="C1955" t="n">
         <v>2.709512278077483</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.032501249280961</v>
+        <v>-4.169540622625207</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.096155354051351</v>
+        <v>1.041339604713653</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1701685652148794</v>
+        <v>-0.1120733381147879</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.607411138948556</v>
+        <v>2.642268275208611</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793912</v>
+        <v>3.741328448793911</v>
       </c>
       <c r="C1956" t="n">
         <v>2.710195669839396</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.077593494114507</v>
+        <v>-4.214632867458753</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.078801847879846</v>
+        <v>1.023986098542148</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2320646083842692</v>
+        <v>-0.1739693812841777</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.570956904808835</v>
+        <v>2.60581404106889</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011245</v>
+        <v>3.750729377011243</v>
       </c>
       <c r="C1957" t="n">
         <v>2.70398264514581</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.898218072875739</v>
+        <v>-4.035257446219985</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.144338991681767</v>
+        <v>1.089523242344069</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.07528785021355056</v>
+        <v>-0.01719262311345898</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.65880993501768</v>
+        <v>2.693667071277735</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982239</v>
+        <v>3.716991718982237</v>
       </c>
       <c r="C1958" t="n">
         <v>2.6847901004774</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.943232286396345</v>
+        <v>-4.080271659740591</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.107140761605115</v>
+        <v>1.052325012267417</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1056367455281552</v>
+        <v>-0.04754151842806359</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.621408053160507</v>
+        <v>2.656265189420562</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509548</v>
+        <v>3.737026608509546</v>
       </c>
       <c r="C1959" t="n">
         <v>2.690481662816346</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.210236796668781</v>
+        <v>-4.347276170013026</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.006030519835086</v>
+        <v>0.9512147704973883</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2999997835711037</v>
+        <v>-0.2419045564710122</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.510481792673684</v>
+        <v>2.545338928933739</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760819</v>
+        <v>3.702309454760817</v>
       </c>
       <c r="C1960" t="n">
         <v>2.689685584712847</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.311434578105954</v>
+        <v>-4.448473951450199</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9647553291567186</v>
+        <v>0.9099395798190206</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3684085971164229</v>
+        <v>-0.3103133700163314</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.468640426442994</v>
+        <v>2.503497562703049</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815464</v>
+        <v>3.705571661815462</v>
       </c>
       <c r="C1961" t="n">
         <v>2.687285546267164</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.304923611491641</v>
+        <v>-4.441962984835886</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9649596773567604</v>
+        <v>0.9101439280190624</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3684085971164229</v>
+        <v>-0.3103133700163314</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.466240387997311</v>
+        <v>2.501097524257366</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378108</v>
+        <v>3.709510443378107</v>
       </c>
       <c r="C1962" t="n">
         <v>2.683810265475409</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.285885483784344</v>
+        <v>-4.422924857128589</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9690996476479243</v>
+        <v>0.9142838983102264</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4265922084476175</v>
+        <v>-0.3684969813475259</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.427854940406839</v>
+        <v>2.462712076666894</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131259</v>
+        <v>3.731064473131257</v>
       </c>
       <c r="C1963" t="n">
         <v>2.86139213441409</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.142363761164919</v>
+        <v>-4.454051488279207</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.204090205634375</v>
+        <v>1.079415114788659</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4265922084476175</v>
+        <v>-0.3684969813475259</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.60543680934552</v>
+        <v>2.640293945605575</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067875</v>
+        <v>3.722447362067873</v>
       </c>
       <c r="C1964" t="n">
         <v>2.862225463400223</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.156230522498837</v>
+        <v>-4.467918249613125</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.199376830086941</v>
+        <v>1.074701739241226</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4644501251814404</v>
+        <v>-0.4063548980813488</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.583555388291359</v>
+        <v>2.618412524551414</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789131</v>
+        <v>3.787425580789129</v>
       </c>
       <c r="C1965" t="n">
         <v>2.868233993797149</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.111426350958907</v>
+        <v>-4.423114078073195</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.223307029099839</v>
+        <v>1.098631938254124</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4644501251814404</v>
+        <v>-0.4063548980813488</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.589563918688285</v>
+        <v>2.62442105494834</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519918</v>
+        <v>3.781501250519916</v>
       </c>
       <c r="C1966" t="n">
         <v>2.947386641589171</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.963683380723905</v>
+        <v>-4.275371107838192</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.361556864985862</v>
+        <v>1.236881774140147</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2966427679465573</v>
+        <v>-0.2385475408464657</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.769400980821237</v>
+        <v>2.804258117081292</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918118</v>
+        <v>3.802245929181178</v>
       </c>
       <c r="C1967" t="n">
         <v>2.950180263120652</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.065698063255126</v>
+        <v>-4.377385790369414</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.323544613504854</v>
+        <v>1.198869522659139</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2966427679465573</v>
+        <v>-0.2385475408464657</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.772194602352718</v>
+        <v>2.807051738612773</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539474</v>
+        <v>3.805608985394739</v>
       </c>
       <c r="C1968" t="n">
         <v>2.95084261151231</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.059545357202341</v>
+        <v>-4.371233084316629</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.326668044317626</v>
+        <v>1.201992953471911</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.290490061893773</v>
+        <v>-0.2323948347936814</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.776548574376047</v>
+        <v>2.811405710636102</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890618</v>
+        <v>3.798239794890616</v>
       </c>
       <c r="C1969" t="n">
         <v>2.949923088252421</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.076354655352843</v>
+        <v>-4.388042382467131</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.319024801797536</v>
+        <v>1.194349710951821</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3072993600442746</v>
+        <v>-0.249204132944183</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.765543472225856</v>
+        <v>2.800400608485911</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798435</v>
+        <v>3.867362636798434</v>
       </c>
       <c r="C1970" t="n">
         <v>3.016258642049241</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.014056656576721</v>
+        <v>-4.325744383691009</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.410279555104806</v>
+        <v>1.28560446425909</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2450013612681526</v>
+        <v>-0.1869061341680611</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.86925782528835</v>
+        <v>2.904114961548405</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992202</v>
+        <v>3.848729139992201</v>
       </c>
       <c r="C1971" t="n">
         <v>2.724839514438639</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.812266458911563</v>
+        <v>-4.123954186025851</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.199576506560267</v>
+        <v>1.074901415714552</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.04698316909899825</v>
+        <v>0.01111205800109333</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.696649612979241</v>
+        <v>2.731506749239296</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852432</v>
+        <v>3.84144481785243</v>
       </c>
       <c r="C1972" t="n">
         <v>2.795129746760815</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.738888361822827</v>
+        <v>-4.050576088937115</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.299217977717937</v>
+        <v>1.174542886872221</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.0263949279897383</v>
+        <v>0.08449015508982988</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.810966703554658</v>
+        <v>2.845823839814713</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319557</v>
+        <v>3.819063300319555</v>
       </c>
       <c r="C1973" t="n">
         <v>2.809757482876858</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.836628906447801</v>
+        <v>-4.148316633562089</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.274749495983991</v>
+        <v>1.150074405138275</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.01050564985675811</v>
+        <v>0.06860087695684969</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.816060872790914</v>
+        <v>2.850918009050968</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489395</v>
+        <v>3.831819032489394</v>
       </c>
       <c r="C1974" t="n">
         <v>2.80829346370153</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.012966666570731</v>
+        <v>-4.324654393685019</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.20275037275949</v>
+        <v>1.078075281913775</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1658321102661713</v>
+        <v>-0.1077368831660797</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.708794197541827</v>
+        <v>2.743651333801882</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397805</v>
+        <v>3.836411672397803</v>
       </c>
       <c r="C1975" t="n">
         <v>2.806785081741459</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.936544620138804</v>
+        <v>-4.248232347253092</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.23181080937219</v>
+        <v>1.107135718526475</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1658321102661713</v>
+        <v>-0.1077368831660797</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.707285815581756</v>
+        <v>2.742142951841811</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031626</v>
+        <v>3.833513460316258</v>
       </c>
       <c r="C1976" t="n">
         <v>2.806647949176895</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.892171488500235</v>
+        <v>-4.203859215614523</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.249422929463053</v>
+        <v>1.124747838617338</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1214589786276027</v>
+        <v>-0.06336375152751111</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.733772562000333</v>
+        <v>2.768629698260388</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105974</v>
+        <v>3.821562117105972</v>
       </c>
       <c r="C1977" t="n">
         <v>2.801041743315485</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.769337267613068</v>
+        <v>-4.081024994727356</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.292950411956511</v>
+        <v>1.168275321110796</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1214589786276027</v>
+        <v>-0.06336375152751111</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.728166356138924</v>
+        <v>2.763023492398979</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190332</v>
+        <v>3.83301114819033</v>
       </c>
       <c r="C1978" t="n">
         <v>2.807423500343289</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.721681537052012</v>
+        <v>-4.0333692641663</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.318394461208737</v>
+        <v>1.193719370363022</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.07380324806654703</v>
+        <v>-0.01570802096645546</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.763141551503362</v>
+        <v>2.797998687763417</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569625</v>
+        <v>3.822678210569623</v>
       </c>
       <c r="C1979" t="n">
         <v>2.812315873718014</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.621163378553257</v>
+        <v>-3.932851105667545</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.363494097982964</v>
+        <v>1.238819007137249</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.02671491043220753</v>
+        <v>0.0848101375322991</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.828344819977339</v>
+        <v>2.863201956237394</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.8288088775573</v>
+        <v>3.828808877557298</v>
       </c>
       <c r="C1980" t="n">
         <v>2.799070546193887</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.681829968955646</v>
+        <v>-3.993517696069934</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.325982134297881</v>
+        <v>1.201307043452166</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.05498340628632614</v>
+        <v>0.003111820813765431</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.766080502422091</v>
+        <v>2.800937638682146</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932775</v>
+        <v>3.816837033932774</v>
       </c>
       <c r="C1981" t="n">
         <v>2.803168248804515</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.636991567347248</v>
+        <v>-3.948679294461536</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.348015197551868</v>
+        <v>1.223340106706153</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.05043997334145667</v>
+        <v>0.007655253758634906</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.772904264799641</v>
+        <v>2.807761401059696</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917059</v>
+        <v>3.817932354917058</v>
       </c>
       <c r="C1982" t="n">
         <v>2.807329188435593</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.737750203104247</v>
+        <v>-4.049437930218534</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.311872682880147</v>
+        <v>1.187197592034432</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1392655420684621</v>
+        <v>-0.08117031496837052</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.723769863194516</v>
+        <v>2.758626999454571</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405968</v>
+        <v>3.826684745405967</v>
       </c>
       <c r="C1983" t="n">
         <v>2.81320879096343</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.693547366018346</v>
+        <v>-4.005235093132634</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.335433420242344</v>
+        <v>1.210758329396629</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.09506270498256164</v>
+        <v>-0.03696747788247007</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.756171167973894</v>
+        <v>2.791028304233949</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265653</v>
+        <v>3.838199629265652</v>
       </c>
       <c r="C1984" t="n">
         <v>2.811618791432678</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.73052639368179</v>
+        <v>-4.042214120796077</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.319051809646215</v>
+        <v>1.1943767188005</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.05808880319123111</v>
+        <v>6.423908860464511e-06</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.77676550951794</v>
+        <v>2.811622645777994</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.862866556615717</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.75058447254663</v>
+        <v>-4.062272199660917</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.362276343283318</v>
+        <v>1.237601252437603</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.05808880319123111</v>
+        <v>6.423908860464511e-06</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.828013274700979</v>
+        <v>2.862870410961034</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132103</v>
+        <v>3.865338681321029</v>
       </c>
       <c r="C1986" t="n">
         <v>2.861307261209971</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.710653799368739</v>
+        <v>-4.022341526483027</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.376689317148728</v>
+        <v>1.252014226303013</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.01815813001334077</v>
+        <v>0.03993709708675081</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.850412383201967</v>
+        <v>2.885269519462021</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475147</v>
+        <v>3.864489842475146</v>
       </c>
       <c r="C1987" t="n">
         <v>2.856255489448241</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.659621706646211</v>
+        <v>-3.971309433760499</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.392050382476009</v>
+        <v>1.267375291630294</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.03287396270918719</v>
+        <v>0.09096918980927876</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.875979867073753</v>
+        <v>2.910837003333808</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404863</v>
+        <v>3.842547360404862</v>
       </c>
       <c r="C1988" t="n">
         <v>2.873442893540946</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.594397525519006</v>
+        <v>-3.906085252633293</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.435327459019596</v>
+        <v>1.310652368173881</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.09809814383639281</v>
+        <v>0.1561933709364844</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.932301779842781</v>
+        <v>2.967158916102836</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882567</v>
+        <v>3.840061186882566</v>
       </c>
       <c r="C1989" t="n">
         <v>2.869403865840226</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.556970505447872</v>
+        <v>-3.868658232562159</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.44625923934733</v>
+        <v>1.321584148501615</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1033496818655745</v>
+        <v>0.161444908965666</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.931413674959571</v>
+        <v>2.966270811219626</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.870660658171466</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.577082161482581</v>
+        <v>-3.888769888596868</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.439471369264687</v>
+        <v>1.314796278418972</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1143770268629937</v>
+        <v>0.1724722539630852</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.939286874289263</v>
+        <v>2.974144010549318</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.031218429192677</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.523337347055376</v>
+        <v>-3.835025074169663</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.621527066056779</v>
+        <v>1.496851975211065</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1244403363034556</v>
+        <v>0.1825355634035472</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.10588263097475</v>
+        <v>3.140739767234805</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.151331338410494</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.499545778449233</v>
+        <v>-3.81123350556352</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.751156602717054</v>
+        <v>1.626481511871339</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1482319049095979</v>
+        <v>0.2063271320096895</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.240270481356253</v>
+        <v>3.275127617616308</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.143039314424353</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.473461694185425</v>
+        <v>-3.785149421299713</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.753298212436436</v>
+        <v>1.628623121590721</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1482319049095979</v>
+        <v>0.2063271320096895</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.231978457370112</v>
+        <v>3.266835593630167</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.141232510008133</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.395330513336479</v>
+        <v>-3.707018240450766</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.782743880359794</v>
+        <v>1.658068789514079</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2224087157932825</v>
+        <v>0.280503942893374</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.274677739484102</v>
+        <v>3.309534875744157</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.158786915734924</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.386438051943196</v>
+        <v>-3.698125779057483</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.803855270643898</v>
+        <v>1.679180179798184</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2224087157932825</v>
+        <v>0.280503942893374</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.292232145210894</v>
+        <v>3.327089281470949</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.150641963139508</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.554914168913073</v>
+        <v>-3.86660189602736</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.728319871260531</v>
+        <v>1.603644780414816</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1944608800767017</v>
+        <v>0.2525561071767933</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.267318491185529</v>
+        <v>3.302175627445584</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.13191166032737</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.85711464005149</v>
+        <v>-3.168802367165777</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.988709379993026</v>
+        <v>1.864034289147312</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.124112820706291</v>
+        <v>0.1822080478063826</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.206379352751145</v>
+        <v>3.2412364890112</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.122575682824274</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.834393536368338</v>
+        <v>-3.146081263482625</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.988461843963192</v>
+        <v>1.863786753117477</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.124112820706291</v>
+        <v>0.1822080478063826</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.197043375248049</v>
+        <v>3.231900511508104</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.281481808675443</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.832668493078294</v>
+        <v>-3.144356220192581</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.148057987130379</v>
+        <v>2.023382896284664</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1258378639963347</v>
+        <v>0.1839330910964263</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.356984527073244</v>
+        <v>3.391841663333299</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.31855963116909</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.987449499856549</v>
+        <v>-3.299137226970836</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.123223406912723</v>
+        <v>1.998548316067009</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.09247018994185863</v>
+        <v>0.1505654170419502</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.374041745134206</v>
+        <v>3.40889888139426</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.315234987158635</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.936014166471889</v>
+        <v>-3.247701893586176</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.140472896256132</v>
+        <v>2.015797805410418</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.1439055233265183</v>
+        <v>0.2020007504266099</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.401578301154546</v>
+        <v>3.436435437414601</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.325241140803377</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.909062942145401</v>
+        <v>-3.220750669259688</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.161259539631469</v>
+        <v>2.036584448785754</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1587858693542374</v>
+        <v>0.216881096454329</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.420512662415919</v>
+        <v>3.455369798675974</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.509344272948336</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.045015950201718</v>
+        <v>-3.356703677316005</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.290981468553902</v>
+        <v>2.166306377708187</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1587858693542374</v>
+        <v>0.216881096454329</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.604615794560879</v>
+        <v>3.639472930820934</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.50146096785133</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.06742406800659</v>
+        <v>-3.379111795120877</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.274134916334947</v>
+        <v>2.149459825489232</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.1587858693542374</v>
+        <v>0.216881096454329</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.596732489463872</v>
+        <v>3.631589625723927</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.503514967400967</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.215429835485989</v>
+        <v>-3.527117562600276</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.216986608892824</v>
+        <v>2.092311518047109</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.07205886049069599</v>
+        <v>0.1301540875907876</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.546750283695385</v>
+        <v>3.58160741995544</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.559768685122814</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.224870761374519</v>
+        <v>-3.536558488488806</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.269463956259259</v>
+        <v>2.144788865413545</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.1944859780340874</v>
+        <v>0.252581205134179</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.676460271943267</v>
+        <v>3.711317408203322</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.562659779668115</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.223583997834963</v>
+        <v>-3.53527172494925</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.272869756220382</v>
+        <v>2.148194665374668</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.195772741573644</v>
+        <v>0.2538679686737356</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.680123424612302</v>
+        <v>3.714980560872357</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.56077159256189</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.225141051824254</v>
+        <v>-3.536828778938541</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.270358747518441</v>
+        <v>2.145683656672726</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.195772741573644</v>
+        <v>0.2538679686737356</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.678235237506077</v>
+        <v>3.713092373766132</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.555591822164752</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.232412937347719</v>
+        <v>-3.544100664462006</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.262270222911918</v>
+        <v>2.137595132066203</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.1885008560501792</v>
+        <v>0.2465960831502708</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.66869233579486</v>
+        <v>3.703549472054915</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.554025832374905</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.230571918289467</v>
+        <v>-3.542259645403754</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.26144064074537</v>
+        <v>2.136765549899656</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.1897690827216477</v>
+        <v>0.2478643098217392</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.667887282007894</v>
+        <v>3.702744418267949</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.567099239240823</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.237480623789148</v>
+        <v>-3.549168350903435</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.271750565411417</v>
+        <v>2.147075474565702</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.1897690827216477</v>
+        <v>0.2478643098217392</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.680960688873812</v>
+        <v>3.715817825133867</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.567099239240823</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.239042266604008</v>
+        <v>-3.550729993718295</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.271125908285473</v>
+        <v>2.146450817439758</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.1897690827216477</v>
+        <v>0.2478643098217392</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.680960688873812</v>
+        <v>3.715817825133867</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.565623280367825</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.266943053713481</v>
+        <v>-3.578630780827768</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.258489634568686</v>
+        <v>2.133814543722971</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.1551721585787129</v>
+        <v>0.2132673856788044</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.658726575515054</v>
+        <v>3.693583711775108</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.562387724345024</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.269976051226155</v>
+        <v>-3.581663778340442</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.254040879540815</v>
+        <v>2.1293657886951</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.152139161066039</v>
+        <v>0.2102343881661305</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.653671220984648</v>
+        <v>3.688528357244703</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971084</v>
+        <v>3.619362241971083</v>
       </c>
       <c r="C2015" t="n">
         <v>3.629093683935528</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.290037372502661</v>
+        <v>-3.601725099616949</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.312722310620716</v>
+        <v>2.188047219775001</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.132077839789532</v>
+        <v>0.1901730668896235</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.708340387809247</v>
+        <v>3.743197524069302</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.830926303678913</v>
+        <v>3.374999780900611</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.771538250367598</v>
+        <v>3.604603623794427</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.290037372502661</v>
+        <v>-3.601725099616949</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.312722310620716</v>
+        <v>2.188047219775001</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.132077839789532</v>
+        <v>0.1901730668896235</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.764602047353966</v>
+        <v>3.597667420780795</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240705.xlsx
+++ b/tame_output/ON/bt/strategyON_20240705.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>59.6%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,27 +844,27 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>79.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>122.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.1%</t>
+          <t>-67.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.0%</t>
+          <t>453.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-521.7%</t>
+          <t>-496.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-41.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.4%</t>
+          <t>-147.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-209.2%</t>
+          <t>-131.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-205.0%</t>
+          <t>-196.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-86.3%</t>
+          <t>-55.6%</t>
         </is>
       </c>
     </row>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760738</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539465</v>
+        <v>3.501052558539466</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937501</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141704</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729893</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440636</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410274</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.691571733940722</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770583</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615286</v>
+        <v>3.685161381615287</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.71093553364622</v>
+        <v>3.710935533646221</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.768951674611572</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955331</v>
+        <v>3.728577929955332</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436233</v>
+        <v>3.766317079436234</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311953</v>
+        <v>3.784684521311954</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097249</v>
+        <v>3.80082935409725</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017777</v>
+        <v>3.789311112017778</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388733</v>
+        <v>3.839374447388735</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626479</v>
+        <v>3.856161751626481</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291815</v>
+        <v>3.787330429291817</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785791</v>
+        <v>3.801637122785793</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390431</v>
+        <v>3.763182248390433</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105957</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960991</v>
+        <v>3.753882571960992</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607649</v>
+        <v>3.692931855607651</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987908</v>
+        <v>3.77042258398791</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710817</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.72356622940921</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098113</v>
+        <v>3.729969716098115</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493424</v>
+        <v>3.782922533493426</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82855148672282</v>
+        <v>3.828551486722822</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792051</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919912</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.748328408318098</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305753</v>
+        <v>3.824311233057531</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279189</v>
+        <v>3.826354974279191</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011502</v>
+        <v>3.835957987011504</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392991</v>
+        <v>3.780933911392992</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632785</v>
+        <v>3.773765222632787</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883078</v>
+        <v>3.76461787988308</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074788</v>
+        <v>3.79881477107479</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.7976948842423</v>
+        <v>3.797694884242302</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936769</v>
+        <v>3.821593509367692</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879971</v>
+        <v>3.822326997879973</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502343</v>
+        <v>3.848616626502345</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675945</v>
+        <v>3.818668951675947</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539956</v>
+        <v>3.843274527539958</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496265</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577002</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942107</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674517</v>
+        <v>3.762647477674519</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430698</v>
       </c>
       <c r="C1935" t="n">
         <v>2.992094879537234</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743220196003607</v>
       </c>
       <c r="C1936" t="n">
         <v>3.003101802011936</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.714179139508375</v>
       </c>
       <c r="C1937" t="n">
         <v>2.993538510643827</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417708</v>
+        <v>3.71090673141771</v>
       </c>
       <c r="C1938" t="n">
         <v>2.818248075684214</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205905</v>
+        <v>3.746042526205906</v>
       </c>
       <c r="C1939" t="n">
         <v>2.822815307676002</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225451</v>
       </c>
       <c r="C1940" t="n">
         <v>2.798557336437209</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111298</v>
+        <v>3.7732102971113</v>
       </c>
       <c r="C1941" t="n">
         <v>2.801688721657114</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264168</v>
+        <v>3.78434395226417</v>
       </c>
       <c r="C1942" t="n">
         <v>2.811861108089247</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742304</v>
+        <v>3.786949957742306</v>
       </c>
       <c r="C1943" t="n">
         <v>2.806807378663107</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316051</v>
+        <v>3.752027499316053</v>
       </c>
       <c r="C1944" t="n">
         <v>2.798583154107633</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803196</v>
+        <v>3.753571165803198</v>
       </c>
       <c r="C1945" t="n">
         <v>2.799135027140734</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809503</v>
+        <v>3.733390600809505</v>
       </c>
       <c r="C1946" t="n">
         <v>2.7284077190321</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.74828581656043</v>
+        <v>3.748285816560432</v>
       </c>
       <c r="C1947" t="n">
         <v>2.730281194956701</v>
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472743</v>
+        <v>3.721077195472745</v>
       </c>
       <c r="C1948" t="n">
         <v>2.725356903468424</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.313430897279377</v>
+        <v>-4.352748745685816</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9996281202429256</v>
+        <v>0.9839009808803501</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1041057182444122</v>
+        <v>-0.1434235666508515</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.662893472521777</v>
+        <v>2.639302763477913</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798543</v>
+        <v>3.743047603798544</v>
       </c>
       <c r="C1949" t="n">
         <v>2.730848199299091</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.201053896096704</v>
+        <v>-4.240371744503143</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.050070216546662</v>
+        <v>1.034343077184086</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1041057182444122</v>
+        <v>-0.1434235666508515</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.668384768352444</v>
+        <v>2.64479405930858</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498871</v>
+        <v>3.689597840498872</v>
       </c>
       <c r="C1950" t="n">
         <v>2.74234540106763</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.228834293998057</v>
+        <v>-4.268152142404496</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.05045525915466</v>
+        <v>1.034728119792084</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1318861161457653</v>
+        <v>-0.1712039645522045</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.663213731380171</v>
+        <v>2.639623022336308</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705331</v>
+        <v>3.643069621705333</v>
       </c>
       <c r="C1951" t="n">
         <v>2.580701121068283</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.311835575023336</v>
+        <v>-4.351153423429775</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8556104667452016</v>
+        <v>0.8398833273826261</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.150457000672939</v>
+        <v>-0.1897748490793783</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.49042692066452</v>
+        <v>2.466836211620657</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729276</v>
+        <v>3.682716310729278</v>
       </c>
       <c r="C1952" t="n">
         <v>2.700850781787489</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.420449653466667</v>
+        <v>-4.459767501873106</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9323144960870748</v>
+        <v>0.9165873567244993</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.150457000672939</v>
+        <v>-0.1897748490793783</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.610576581383726</v>
+        <v>2.586985872339862</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190775</v>
+        <v>3.733012441190777</v>
       </c>
       <c r="C1953" t="n">
         <v>2.715363807889812</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.385040615218524</v>
+        <v>-4.424358463624963</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9609911374886551</v>
+        <v>0.9452639981260793</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.150457000672939</v>
+        <v>-0.1897748490793783</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.625089607486049</v>
+        <v>2.601498898442185</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913432</v>
+        <v>3.741174069913434</v>
       </c>
       <c r="C1954" t="n">
         <v>2.712783249232181</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.346656952660373</v>
+        <v>-4.385974801066812</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9737640438542841</v>
+        <v>0.9580369044917085</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1120733381147879</v>
+        <v>-0.1513911865212271</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.645539246363308</v>
+        <v>2.621948537319445</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532493</v>
+        <v>3.751147197532495</v>
       </c>
       <c r="C1955" t="n">
         <v>2.709512278077483</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.169540622625207</v>
+        <v>-4.208858471031646</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.041339604713653</v>
+        <v>1.025612465351077</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1120733381147879</v>
+        <v>-0.1513911865212271</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.642268275208611</v>
+        <v>2.618677566164747</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793911</v>
+        <v>3.741328448793912</v>
       </c>
       <c r="C1956" t="n">
         <v>2.710195669839396</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.214632867458753</v>
+        <v>-4.253950715865192</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.023986098542148</v>
+        <v>1.008258959179572</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1739693812841777</v>
+        <v>-0.2132872296906169</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.60581404106889</v>
+        <v>2.582223332025026</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011243</v>
+        <v>3.750729377011245</v>
       </c>
       <c r="C1957" t="n">
         <v>2.70398264514581</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.035257446219985</v>
+        <v>-4.074575294626424</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.089523242344069</v>
+        <v>1.073796102981494</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.01719262311345898</v>
+        <v>-0.05651047151989824</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.693667071277735</v>
+        <v>2.670076362233872</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982237</v>
+        <v>3.716991718982239</v>
       </c>
       <c r="C1958" t="n">
         <v>2.6847901004774</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.080271659740591</v>
+        <v>-4.11958950814703</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.052325012267417</v>
+        <v>1.036597872904841</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.04754151842806359</v>
+        <v>-0.08685936683450285</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.656265189420562</v>
+        <v>2.632674480376699</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509546</v>
+        <v>3.737026608509548</v>
       </c>
       <c r="C1959" t="n">
         <v>2.690481662816346</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.347276170013026</v>
+        <v>-4.386594018419465</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9512147704973883</v>
+        <v>0.9354876311348128</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2419045564710122</v>
+        <v>-0.2812224048774514</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.545338928933739</v>
+        <v>2.521748219889875</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760817</v>
+        <v>3.702309454760819</v>
       </c>
       <c r="C1960" t="n">
         <v>2.689685584712847</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.448473951450199</v>
+        <v>-4.487791799856637</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9099395798190206</v>
+        <v>0.8942124404564451</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3103133700163314</v>
+        <v>-0.3496312184227706</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.503497562703049</v>
+        <v>2.479906853659185</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815462</v>
+        <v>3.705571661815464</v>
       </c>
       <c r="C1961" t="n">
         <v>2.687285546267164</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.441962984835886</v>
+        <v>-4.481280833242325</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9101439280190624</v>
+        <v>0.8944167886564869</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3103133700163314</v>
+        <v>-0.3496312184227706</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.501097524257366</v>
+        <v>2.477506815213502</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378108</v>
       </c>
       <c r="C1962" t="n">
         <v>2.683810265475409</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.422924857128589</v>
+        <v>-4.462242705535028</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9142838983102264</v>
+        <v>0.8985567589476506</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3684969813475259</v>
+        <v>-0.4078148297539652</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.462712076666894</v>
+        <v>2.43912136762303</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131257</v>
+        <v>3.731064473131259</v>
       </c>
       <c r="C1963" t="n">
         <v>2.86139213441409</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.454051488279207</v>
+        <v>-4.493369336685646</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.079415114788659</v>
+        <v>1.063687975426084</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3684969813475259</v>
+        <v>-0.4078148297539652</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.640293945605575</v>
+        <v>2.616703236561711</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067873</v>
+        <v>3.722447362067875</v>
       </c>
       <c r="C1964" t="n">
         <v>2.862225463400223</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.467918249613125</v>
+        <v>-4.507236098019564</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.074701739241226</v>
+        <v>1.05897459987865</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4063548980813488</v>
+        <v>-0.4456727464877881</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.618412524551414</v>
+        <v>2.59482181550755</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789129</v>
+        <v>3.787425580789131</v>
       </c>
       <c r="C1965" t="n">
         <v>2.868233993797149</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.423114078073195</v>
+        <v>-4.462431926479634</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.098631938254124</v>
+        <v>1.082904798891548</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4063548980813488</v>
+        <v>-0.4456727464877881</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.62442105494834</v>
+        <v>2.600830345904476</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519916</v>
+        <v>3.781501250519918</v>
       </c>
       <c r="C1966" t="n">
         <v>2.947386641589171</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.275371107838192</v>
+        <v>-4.314688956244631</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.236881774140147</v>
+        <v>1.221154634777571</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2385475408464657</v>
+        <v>-0.2778653892529049</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.804258117081292</v>
+        <v>2.780667408037428</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181178</v>
+        <v>3.80224592918118</v>
       </c>
       <c r="C1967" t="n">
         <v>2.950180263120652</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.377385790369414</v>
+        <v>-4.416703638775853</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.198869522659139</v>
+        <v>1.183142383296564</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2385475408464657</v>
+        <v>-0.2778653892529049</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.807051738612773</v>
+        <v>2.783461029568909</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394739</v>
+        <v>3.80560898539474</v>
       </c>
       <c r="C1968" t="n">
         <v>2.95084261151231</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.371233084316629</v>
+        <v>-4.410550932723068</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.201992953471911</v>
+        <v>1.186265814109336</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2323948347936814</v>
+        <v>-0.2717126832001207</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.811405710636102</v>
+        <v>2.787815001592238</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890616</v>
+        <v>3.798239794890618</v>
       </c>
       <c r="C1969" t="n">
         <v>2.949923088252421</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.388042382467131</v>
+        <v>-4.42736023087357</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.194349710951821</v>
+        <v>1.178622571589245</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.249204132944183</v>
+        <v>-0.2885219813506223</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.800400608485911</v>
+        <v>2.776809899442048</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798434</v>
+        <v>3.867362636798435</v>
       </c>
       <c r="C1970" t="n">
         <v>3.016258642049241</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.325744383691009</v>
+        <v>-4.365062232097448</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.28560446425909</v>
+        <v>1.269877324896515</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1869061341680611</v>
+        <v>-0.2885219813506223</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.904114961548405</v>
+        <v>2.843145453238868</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992201</v>
+        <v>3.848729139992202</v>
       </c>
       <c r="C1971" t="n">
         <v>2.724839514438639</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.123954186025851</v>
+        <v>-4.16327203443229</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.074901415714552</v>
+        <v>1.059174276351976</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.01111205800109333</v>
+        <v>-0.0905037891814679</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.731506749239296</v>
+        <v>2.670537240929759</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785243</v>
+        <v>3.841444817852432</v>
       </c>
       <c r="C1972" t="n">
         <v>2.795129746760815</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.050576088937115</v>
+        <v>-4.089893937343554</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.174542886872221</v>
+        <v>1.158815747509646</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.08449015508982988</v>
+        <v>-0.01712569209273135</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.845823839814713</v>
+        <v>2.784854331505176</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319555</v>
+        <v>3.819063300319557</v>
       </c>
       <c r="C1973" t="n">
         <v>2.809757482876858</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.148316633562089</v>
+        <v>-4.187634481968528</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.150074405138275</v>
+        <v>1.1343472657757</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.06860087695684969</v>
+        <v>-0.03301497022571154</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.850918009050968</v>
+        <v>2.789948500741432</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489394</v>
+        <v>3.831819032489395</v>
       </c>
       <c r="C1974" t="n">
         <v>2.80829346370153</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.324654393685019</v>
+        <v>-4.363972242091458</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.078075281913775</v>
+        <v>1.0623481425512</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1077368831660797</v>
+        <v>-0.2093527303486409</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.743651333801882</v>
+        <v>2.682681825492346</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397803</v>
+        <v>3.836411672397805</v>
       </c>
       <c r="C1975" t="n">
         <v>2.806785081741459</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.248232347253092</v>
+        <v>-4.287550195659531</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.107135718526475</v>
+        <v>1.091408579163899</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1077368831660797</v>
+        <v>-0.2093527303486409</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.742142951841811</v>
+        <v>2.681173443532274</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316258</v>
+        <v>3.83351346031626</v>
       </c>
       <c r="C1976" t="n">
         <v>2.806647949176895</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.203859215614523</v>
+        <v>-4.243177064020962</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.124747838617338</v>
+        <v>1.109020699254763</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.06336375152751111</v>
+        <v>-0.1649795987100723</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.768629698260388</v>
+        <v>2.707660189950852</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105972</v>
+        <v>3.821562117105974</v>
       </c>
       <c r="C1977" t="n">
         <v>2.801041743315485</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.081024994727356</v>
+        <v>-4.120342843133795</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.168275321110796</v>
+        <v>1.15254818174822</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.06336375152751111</v>
+        <v>-0.1649795987100723</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.763023492398979</v>
+        <v>2.702053984089442</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819033</v>
+        <v>3.833011148190332</v>
       </c>
       <c r="C1978" t="n">
         <v>2.807423500343289</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.0333692641663</v>
+        <v>-4.072687112572739</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.193719370363022</v>
+        <v>1.177992231000447</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.01570802096645546</v>
+        <v>-0.1173238681490167</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.797998687763417</v>
+        <v>2.73702917945388</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569623</v>
+        <v>3.822678210569625</v>
       </c>
       <c r="C1979" t="n">
         <v>2.812315873718014</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.932851105667545</v>
+        <v>-3.972168954073984</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.238819007137249</v>
+        <v>1.223091867774673</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.0848101375322991</v>
+        <v>-0.01680570965026212</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.863201956237394</v>
+        <v>2.802232447927857</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557298</v>
+        <v>3.8288088775573</v>
       </c>
       <c r="C1980" t="n">
         <v>2.799070546193887</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.993517696069934</v>
+        <v>-4.032835544476374</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.201307043452166</v>
+        <v>1.18557990408959</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.003111820813765431</v>
+        <v>-0.09850402636879579</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.800937638682146</v>
+        <v>2.739968130372609</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932774</v>
+        <v>3.816837033932775</v>
       </c>
       <c r="C1981" t="n">
         <v>2.803168248804515</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.948679294461536</v>
+        <v>-3.987997142867976</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.223340106706153</v>
+        <v>1.207612967343578</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.007655253758634906</v>
+        <v>-0.09396059342392632</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.807761401059696</v>
+        <v>2.74679189275016</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917058</v>
+        <v>3.817932354917059</v>
       </c>
       <c r="C1982" t="n">
         <v>2.807329188435593</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.049437930218534</v>
+        <v>-3.798385313605354</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.187197592034432</v>
+        <v>1.287618638679704</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.08117031496837052</v>
+        <v>0.004506253127211035</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.758626999454571</v>
+        <v>2.81003294031192</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405967</v>
+        <v>3.826684745405968</v>
       </c>
       <c r="C1983" t="n">
         <v>2.81320879096343</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.005235093132634</v>
+        <v>-3.754182476519454</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.210758329396629</v>
+        <v>1.311179376041901</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.03696747788247007</v>
+        <v>0.04870909021311148</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.791028304233949</v>
+        <v>2.842434245091297</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265652</v>
+        <v>3.838199629265653</v>
       </c>
       <c r="C1984" t="n">
         <v>2.811618791432678</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.042214120796077</v>
+        <v>-3.791161504182897</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.1943767188005</v>
+        <v>1.294797765445772</v>
       </c>
       <c r="F1984" t="n">
-        <v>6.423908860464511e-06</v>
+        <v>0.08568299200444202</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.811622645777994</v>
+        <v>2.863028586635343</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.862866556615717</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.062272199660917</v>
+        <v>-3.811219583047737</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.237601252437603</v>
+        <v>1.338022299082875</v>
       </c>
       <c r="F1985" t="n">
-        <v>6.423908860464511e-06</v>
+        <v>0.08568299200444202</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.862870410961034</v>
+        <v>2.914276351818383</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321029</v>
+        <v>3.86533868132103</v>
       </c>
       <c r="C1986" t="n">
         <v>2.861307261209971</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.022341526483027</v>
+        <v>-3.771288909869847</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.252014226303013</v>
+        <v>1.352435272948285</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.03993709708675081</v>
+        <v>0.1256136651823324</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.885269519462021</v>
+        <v>2.93667546031937</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475146</v>
+        <v>3.864489842475147</v>
       </c>
       <c r="C1987" t="n">
         <v>2.856255489448241</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.971309433760499</v>
+        <v>-3.720256817147319</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.267375291630294</v>
+        <v>1.367796338275566</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.09096918980927876</v>
+        <v>0.1766457579048603</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.910837003333808</v>
+        <v>2.962242944191157</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404862</v>
+        <v>3.842547360404863</v>
       </c>
       <c r="C1988" t="n">
         <v>2.873442893540946</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.906085252633293</v>
+        <v>-3.655032636020113</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.310652368173881</v>
+        <v>1.411073414819153</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1561933709364844</v>
+        <v>0.2418699390320659</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.967158916102836</v>
+        <v>3.018564856960186</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882566</v>
+        <v>3.840061186882567</v>
       </c>
       <c r="C1989" t="n">
         <v>2.869403865840226</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.868658232562159</v>
+        <v>-3.61760561594898</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.321584148501615</v>
+        <v>1.422005195146887</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.161444908965666</v>
+        <v>0.2471214770612476</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.966270811219626</v>
+        <v>3.017676752076975</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.870660658171466</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.888769888596868</v>
+        <v>-3.637717271983688</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.314796278418972</v>
+        <v>1.415217325064244</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1724722539630852</v>
+        <v>0.2581488220586668</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.974144010549318</v>
+        <v>3.025549951406667</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.031218429192677</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.835025074169663</v>
+        <v>-3.583972457556483</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.496851975211065</v>
+        <v>1.597273021856336</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1825355634035472</v>
+        <v>0.2682121314991288</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.140739767234805</v>
+        <v>3.192145708092154</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.151331338410494</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.81123350556352</v>
+        <v>-3.560180888950341</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.626481511871339</v>
+        <v>1.726902558516611</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.2063271320096895</v>
+        <v>0.292003700105271</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.275127617616308</v>
+        <v>3.326533558473657</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.143039314424353</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.785149421299713</v>
+        <v>-3.534096804686533</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.628623121590721</v>
+        <v>1.729044168235993</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.2063271320096895</v>
+        <v>0.292003700105271</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.266835593630167</v>
+        <v>3.318241534487516</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.141232510008133</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.707018240450766</v>
+        <v>-3.455965623837586</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.658068789514079</v>
+        <v>1.758489836159351</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.280503942893374</v>
+        <v>0.3661805109889556</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.309534875744157</v>
+        <v>3.360940816601506</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.158786915734924</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.698125779057483</v>
+        <v>-3.447073162444303</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.679180179798184</v>
+        <v>1.779601226443456</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.280503942893374</v>
+        <v>0.3661805109889556</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.327089281470949</v>
+        <v>3.378495222328298</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.150641963139508</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.86660189602736</v>
+        <v>-3.615549279414181</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.603644780414816</v>
+        <v>1.704065827060088</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2525561071767933</v>
+        <v>0.3382326752723748</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.302175627445584</v>
+        <v>3.353581568302933</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.13191166032737</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.168802367165777</v>
+        <v>-2.917749750552598</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.864034289147312</v>
+        <v>1.964455335792584</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1822080478063826</v>
+        <v>0.2678846159019641</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.2412364890112</v>
+        <v>3.292642429868549</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.122575682824274</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.146081263482625</v>
+        <v>-2.895028646869445</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.863786753117477</v>
+        <v>1.964207799762749</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1822080478063826</v>
+        <v>0.2678846159019641</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.231900511508104</v>
+        <v>3.283306452365453</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.281481808675443</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.144356220192581</v>
+        <v>-2.893303603579401</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.023382896284664</v>
+        <v>2.123803942929936</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1839330910964263</v>
+        <v>0.2696096591920079</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.391841663333299</v>
+        <v>3.443247604190648</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.31855963116909</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.299137226970836</v>
+        <v>-3.048084610357656</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.998548316067009</v>
+        <v>2.09896936271228</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1505654170419502</v>
+        <v>0.2362419851375318</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.40889888139426</v>
+        <v>3.460304822251609</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.315234987158635</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.247701893586176</v>
+        <v>-2.996649276972997</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.015797805410418</v>
+        <v>2.116218852055689</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.2020007504266099</v>
+        <v>0.2876773185221914</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.436435437414601</v>
+        <v>3.48784137827195</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.325241140803377</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.220750669259688</v>
+        <v>-2.969698052646509</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.036584448785754</v>
+        <v>2.137005495431026</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.216881096454329</v>
+        <v>0.3025576645499106</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.455369798675974</v>
+        <v>3.506775739533323</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.509344272948336</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.356703677316005</v>
+        <v>-3.105651060702825</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.166306377708187</v>
+        <v>2.266727424353459</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.216881096454329</v>
+        <v>0.3025576645499106</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.639472930820934</v>
+        <v>3.690878871678283</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.50146096785133</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.379111795120877</v>
+        <v>-3.128059178507697</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.149459825489232</v>
+        <v>2.249880872134503</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.216881096454329</v>
+        <v>0.3025576645499106</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.631589625723927</v>
+        <v>3.682995566581276</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.503514967400967</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.527117562600276</v>
+        <v>-3.276064945987097</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.092311518047109</v>
+        <v>2.192732564692381</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1301540875907876</v>
+        <v>0.2158306556863691</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.58160741995544</v>
+        <v>3.633013360812789</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.559768685122814</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.536558488488806</v>
+        <v>-3.285505871875626</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.144788865413545</v>
+        <v>2.245209912058816</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.252581205134179</v>
+        <v>0.3382577732297605</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.711317408203322</v>
+        <v>3.762723349060671</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.562659779668115</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.53527172494925</v>
+        <v>-3.28421910833607</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.148194665374668</v>
+        <v>2.24861571201994</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.2538679686737356</v>
+        <v>0.3395445367693171</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.714980560872357</v>
+        <v>3.766386501729706</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.56077159256189</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.536828778938541</v>
+        <v>-3.285776162325361</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.145683656672726</v>
+        <v>2.246104703317998</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.2538679686737356</v>
+        <v>0.3395445367693171</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.713092373766132</v>
+        <v>3.764498314623481</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.555591822164752</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.544100664462006</v>
+        <v>-3.293048047848826</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.137595132066203</v>
+        <v>2.238016178711475</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.2465960831502708</v>
+        <v>0.3322726512458524</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.703549472054915</v>
+        <v>3.754955412912264</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.554025832374905</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.542259645403754</v>
+        <v>-3.291207028790575</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.136765549899656</v>
+        <v>2.237186596544928</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.2478643098217392</v>
+        <v>0.3335408779173208</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.702744418267949</v>
+        <v>3.754150359125298</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.567099239240823</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.549168350903435</v>
+        <v>-3.298115734290255</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.147075474565702</v>
+        <v>2.247496521210974</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.2478643098217392</v>
+        <v>0.3335408779173208</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.715817825133867</v>
+        <v>3.767223765991216</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.567099239240823</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.550729993718295</v>
+        <v>-3.299677377105115</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.146450817439758</v>
+        <v>2.24687186408503</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.2478643098217392</v>
+        <v>0.3335408779173208</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.715817825133867</v>
+        <v>3.767223765991216</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.565623280367825</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.578630780827768</v>
+        <v>-3.327578164214588</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.133814543722971</v>
+        <v>2.234235590368243</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.2132673856788044</v>
+        <v>0.298943953774386</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.693583711775108</v>
+        <v>3.744989652632457</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.562387724345024</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.581663778340442</v>
+        <v>-3.330611161727262</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.1293657886951</v>
+        <v>2.229786835340372</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2102343881661305</v>
+        <v>0.2959109562617121</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.688528357244703</v>
+        <v>3.739934298102052</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.629093683935528</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.601725099616949</v>
+        <v>-3.350672483003769</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.188047219775001</v>
+        <v>2.288468266420273</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1901730668896235</v>
+        <v>0.2758496349852051</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.743197524069302</v>
+        <v>3.794603464926651</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.374999780900611</v>
+        <v>3.877238500390725</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.604603623794427</v>
+        <v>3.91133072868687</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.601725099616949</v>
+        <v>-3.350672483003769</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.188047219775001</v>
+        <v>2.288468266420273</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1901730668896235</v>
+        <v>0.2758496349852051</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.597667420780795</v>
+        <v>3.904394525673238</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240705.xlsx
+++ b/tame_output/ON/bt/strategyON_20240705.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.1%</t>
+          <t>-67.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.8%</t>
+          <t>453.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-496.6%</t>
+          <t>-501.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.9%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-147.4%</t>
+          <t>-149.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.4%</t>
+          <t>-59.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-196.4%</t>
+          <t>-199.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539466</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937501</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141704</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729893</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440636</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410274</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940722</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770583</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615287</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812106</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646221</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611572</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955332</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232417</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436234</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311954</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409725</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017778</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83325274783973</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388735</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626481</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291817</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785793</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390433</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105957</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960992</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607651</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.77042258398791</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710817</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.72356622940921</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098115</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493426</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722822</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792051</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919912</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318098</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057531</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279191</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011504</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392992</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632787</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988308</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107479</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242302</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367692</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879973</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502345</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675947</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539958</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496265</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577002</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942107</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674519</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430698</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.992094879537234</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003607</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.003101802011936</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508375</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.993538510643827</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.71090673141771</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.818248075684214</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205906</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.822815307676002</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225451</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.798557336437209</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.7732102971113</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.801688721657114</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226417</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.811861108089247</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742306</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.806807378663107</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316053</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.798583154107633</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803198</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.799135027140734</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809505</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.7284077190321</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560432</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.730281194956701</v>
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472745</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.725356903468424</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.352748745685816</v>
+        <v>-4.371526124379469</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9839009808803501</v>
+        <v>0.9763900294028889</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1434235666508515</v>
+        <v>-0.1622009453445038</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.639302763477913</v>
+        <v>2.628036336261722</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798544</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.730848199299091</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.240371744503143</v>
+        <v>-4.259149123196796</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.034343077184086</v>
+        <v>1.026832125706625</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1434235666508515</v>
+        <v>-0.1622009453445038</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.64479405930858</v>
+        <v>2.633527632092389</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498872</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.74234540106763</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.268152142404496</v>
+        <v>-4.286929521098148</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.034728119792084</v>
+        <v>1.027217168314623</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1712039645522045</v>
+        <v>-0.1899813432458569</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.639623022336308</v>
+        <v>2.628356595120116</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705333</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.580701121068283</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.351153423429775</v>
+        <v>-4.369930802123427</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8398833273826261</v>
+        <v>0.8323723759051651</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1897748490793783</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.466836211620657</v>
+        <v>2.455569784404465</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729278</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.700850781787489</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.459767501873106</v>
+        <v>-4.478544880566758</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9165873567244993</v>
+        <v>0.9090764052470384</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1897748490793783</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.586985872339862</v>
+        <v>2.575719445123671</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190777</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.715363807889812</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.424358463624963</v>
+        <v>-4.443135842318616</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9452639981260793</v>
+        <v>0.9377530466486184</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1897748490793783</v>
+        <v>-0.2085522277730306</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.601498898442185</v>
+        <v>2.590232471225994</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913434</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.712783249232181</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.385974801066812</v>
+        <v>-4.404752179760465</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9580369044917085</v>
+        <v>0.9505259530142476</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1513911865212271</v>
+        <v>-0.1701685652148794</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.621948537319445</v>
+        <v>2.610682110103253</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532495</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.709512278077483</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.208858471031646</v>
+        <v>-4.227635849725298</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.025612465351077</v>
+        <v>1.018101513873616</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1513911865212271</v>
+        <v>-0.1701685652148794</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.618677566164747</v>
+        <v>2.607411138948556</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793912</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.710195669839396</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.253950715865192</v>
+        <v>-4.272728094558844</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.008258959179572</v>
+        <v>1.000748007702111</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2132872296906169</v>
+        <v>-0.2320646083842692</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.582223332025026</v>
+        <v>2.570956904808835</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011245</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.70398264514581</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.074575294626424</v>
+        <v>-4.093352673320076</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.073796102981494</v>
+        <v>1.066285151504033</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.05651047151989824</v>
+        <v>-0.07528785021355056</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.670076362233872</v>
+        <v>2.65880993501768</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982239</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.6847901004774</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.11958950814703</v>
+        <v>-4.138366886840682</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.036597872904841</v>
+        <v>1.02908692142738</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.08685936683450285</v>
+        <v>-0.1056367455281552</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.632674480376699</v>
+        <v>2.621408053160507</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509548</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.690481662816346</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.386594018419465</v>
+        <v>-4.405371397113117</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9354876311348128</v>
+        <v>0.9279766796573519</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2812224048774514</v>
+        <v>-0.2999997835711037</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.521748219889875</v>
+        <v>2.510481792673684</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760819</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.689685584712847</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.487791799856637</v>
+        <v>-4.50656917855029</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8942124404564451</v>
+        <v>0.8867014889789842</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3496312184227706</v>
+        <v>-0.3684085971164229</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.479906853659185</v>
+        <v>2.468640426442994</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815464</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.687285546267164</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.481280833242325</v>
+        <v>-4.500058211935977</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8944167886564869</v>
+        <v>0.8869058371790259</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3496312184227706</v>
+        <v>-0.3684085971164229</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.477506815213502</v>
+        <v>2.466240387997311</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378108</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.683810265475409</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.462242705535028</v>
+        <v>-4.48102008422868</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8985567589476506</v>
+        <v>0.8910458074701897</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4078148297539652</v>
+        <v>-0.4265922084476175</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.43912136762303</v>
+        <v>2.427854940406839</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131259</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.86139213441409</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.493369336685646</v>
+        <v>-4.512146715379298</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.063687975426084</v>
+        <v>1.056177023948623</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4078148297539652</v>
+        <v>-0.4265922084476175</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.616703236561711</v>
+        <v>2.60543680934552</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067875</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.862225463400223</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.507236098019564</v>
+        <v>-4.526013476713216</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.05897459987865</v>
+        <v>1.051463648401189</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4456727464877881</v>
+        <v>-0.4644501251814404</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.59482181550755</v>
+        <v>2.583555388291359</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789131</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.868233993797149</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.462431926479634</v>
+        <v>-4.481209305173286</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.082904798891548</v>
+        <v>1.075393847414087</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4456727464877881</v>
+        <v>-0.4644501251814404</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.600830345904476</v>
+        <v>2.589563918688285</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519918</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.947386641589171</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.314688956244631</v>
+        <v>-4.333466334938284</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.221154634777571</v>
+        <v>1.21364368330011</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2778653892529049</v>
+        <v>-0.2966427679465573</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.780667408037428</v>
+        <v>2.769400980821237</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918118</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.950180263120652</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.416703638775853</v>
+        <v>-4.435481017469505</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.183142383296564</v>
+        <v>1.175631431819103</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2778653892529049</v>
+        <v>-0.2966427679465573</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.783461029568909</v>
+        <v>2.772194602352718</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539474</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.95084261151231</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.410550932723068</v>
+        <v>-4.429328311416721</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.186265814109336</v>
+        <v>1.178754862631875</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2717126832001207</v>
+        <v>-0.290490061893773</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.787815001592238</v>
+        <v>2.776548574376047</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890618</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.949923088252421</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.42736023087357</v>
+        <v>-4.446137609567223</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.178622571589245</v>
+        <v>1.171111620111784</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2885219813506223</v>
+        <v>-0.3072993600442746</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.776809899442048</v>
+        <v>2.765543472225856</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798435</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.016258642049241</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.365062232097448</v>
+        <v>-4.3838396107911</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.269877324896515</v>
+        <v>1.262366373419054</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2885219813506223</v>
+        <v>-0.3072993600442746</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.843145453238868</v>
+        <v>2.831879026022677</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992202</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.724839514438639</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.16327203443229</v>
+        <v>-4.182049413125942</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.059174276351976</v>
+        <v>1.051663324874515</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.0905037891814679</v>
+        <v>-0.1092811678751202</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.670537240929759</v>
+        <v>2.659270813713567</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852432</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.795129746760815</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.089893937343554</v>
+        <v>-4.108671316037206</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.158815747509646</v>
+        <v>1.151304796032185</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.01712569209273135</v>
+        <v>-0.03590307078638366</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.784854331505176</v>
+        <v>2.773587904288985</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319557</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.809757482876858</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.187634481968528</v>
+        <v>-4.206411860662181</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.1343472657757</v>
+        <v>1.126836314298239</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.03301497022571154</v>
+        <v>-0.05179234891936385</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.789948500741432</v>
+        <v>2.77868207352524</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489395</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.80829346370153</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.363972242091458</v>
+        <v>-4.38274962078511</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.0623481425512</v>
+        <v>1.054837191073739</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2093527303486409</v>
+        <v>-0.2281301090422932</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.682681825492346</v>
+        <v>2.671415398276154</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397805</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.806785081741459</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.287550195659531</v>
+        <v>-4.306327574353183</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.091408579163899</v>
+        <v>1.083897627686438</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2093527303486409</v>
+        <v>-0.2281301090422932</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.681173443532274</v>
+        <v>2.669907016316083</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031626</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.806647949176895</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.243177064020962</v>
+        <v>-4.261954442714615</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.109020699254763</v>
+        <v>1.101509747777302</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1649795987100723</v>
+        <v>-0.1837569774037247</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.707660189950852</v>
+        <v>2.69639376273466</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105974</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.801041743315485</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.120342843133795</v>
+        <v>-4.139120221827447</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.15254818174822</v>
+        <v>1.145037230270759</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1649795987100723</v>
+        <v>-0.1837569774037247</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.702053984089442</v>
+        <v>2.690787556873251</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190332</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.807423500343289</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.072687112572739</v>
+        <v>-4.091464491266391</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.177992231000447</v>
+        <v>1.170481279522986</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1173238681490167</v>
+        <v>-0.136101246842669</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.73702917945388</v>
+        <v>2.725762752237688</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569625</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.812315873718014</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.972168954073984</v>
+        <v>-3.990946332767637</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.223091867774673</v>
+        <v>1.215580916297212</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.01680570965026212</v>
+        <v>-0.03558308834391444</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.802232447927857</v>
+        <v>2.790966020711666</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.8288088775573</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.799070546193887</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.032835544476374</v>
+        <v>-4.051612923170026</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.18557990408959</v>
+        <v>1.178068952612129</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.09850402636879579</v>
+        <v>-0.1172814050624481</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.739968130372609</v>
+        <v>2.728701703156418</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932775</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.803168248804515</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.987997142867976</v>
+        <v>-4.006774521561628</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.207612967343578</v>
+        <v>1.200102015866117</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.09396059342392632</v>
+        <v>-0.1127379721175786</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.74679189275016</v>
+        <v>2.735525465533968</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917059</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.807329188435593</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.798385313605354</v>
+        <v>-3.843019775191809</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.287618638679704</v>
+        <v>1.269764854045122</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.004506253127211035</v>
+        <v>-0.02884904036386382</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.81003294031192</v>
+        <v>2.790019764217275</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405968</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.81320879096343</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.754182476519454</v>
+        <v>-3.798816938105908</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.311179376041901</v>
+        <v>1.293325591407319</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.04870909021311148</v>
+        <v>0.01535379672203663</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.842434245091297</v>
+        <v>2.822421068996653</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265653</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.811618791432678</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.791161504182897</v>
+        <v>-3.835795965769352</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.294797765445772</v>
+        <v>1.27694398081119</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.08568299200444202</v>
+        <v>0.05232769851336716</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.863028586635343</v>
+        <v>2.843015410540698</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284887</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.862866556615717</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.811219583047737</v>
+        <v>-3.855854044634192</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.338022299082875</v>
+        <v>1.320168514448293</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.08568299200444202</v>
+        <v>0.05232769851336716</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.914276351818383</v>
+        <v>2.894263175723738</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132103</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.861307261209971</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.771288909869847</v>
+        <v>-3.815923371456301</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.352435272948285</v>
+        <v>1.334581488313703</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.1256136651823324</v>
+        <v>0.0922583716912575</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.93667546031937</v>
+        <v>2.916662284224725</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475147</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.856255489448241</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.720256817147319</v>
+        <v>-3.764891278733773</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.367796338275566</v>
+        <v>1.349942553640984</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.1766457579048603</v>
+        <v>0.1432904644137855</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.962242944191157</v>
+        <v>2.942229768096512</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404863</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.873442893540946</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.655032636020113</v>
+        <v>-3.699667097606568</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.411073414819153</v>
+        <v>1.393219630184571</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.2418699390320659</v>
+        <v>0.2085146455409911</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.018564856960186</v>
+        <v>2.99855168086554</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882567</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.869403865840226</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.61760561594898</v>
+        <v>-3.662240077535434</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.422005195146887</v>
+        <v>1.404151410512305</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.2471214770612476</v>
+        <v>0.2137661835701727</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.017676752076975</v>
+        <v>2.99766357598233</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899267</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.870660658171466</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.637717271983688</v>
+        <v>-3.682351733570142</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.415217325064244</v>
+        <v>1.397363540429662</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.2581488220586668</v>
+        <v>0.2247935285675919</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.025549951406667</v>
+        <v>3.005536775312021</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636296</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>3.031218429192677</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.583972457556483</v>
+        <v>-3.628606919142937</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.597273021856336</v>
+        <v>1.579419237221755</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.2682121314991288</v>
+        <v>0.2348568380080539</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.192145708092154</v>
+        <v>3.17213253199751</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957634</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.151331338410494</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.560180888950341</v>
+        <v>-3.604815350536795</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.726902558516611</v>
+        <v>1.709048773882029</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.292003700105271</v>
+        <v>0.2586484066141962</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.326533558473657</v>
+        <v>3.306520382379012</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799876</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>3.143039314424353</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.534096804686533</v>
+        <v>-3.578731266272987</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.729044168235993</v>
+        <v>1.711190383601411</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.292003700105271</v>
+        <v>0.2586484066141962</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.318241534487516</v>
+        <v>3.298228358392871</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896934</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.141232510008133</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.455965623837586</v>
+        <v>-3.50060008542404</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.758489836159351</v>
+        <v>1.740636051524769</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3661805109889556</v>
+        <v>0.3328252174978807</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.360940816601506</v>
+        <v>3.340927640506862</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959863</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>3.158786915734924</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.447073162444303</v>
+        <v>-3.491707624030757</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.779601226443456</v>
+        <v>1.761747441808874</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3661805109889556</v>
+        <v>0.3328252174978807</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.378495222328298</v>
+        <v>3.358482046233653</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945373</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.150641963139508</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.615549279414181</v>
+        <v>-3.660183741000635</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.704065827060088</v>
+        <v>1.686212042425506</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3382326752723748</v>
+        <v>0.3048773817813</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.353581568302933</v>
+        <v>3.333568392208288</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782715</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>3.13191166032737</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.917749750552598</v>
+        <v>-2.962384212139052</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.964455335792584</v>
+        <v>1.946601551158002</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2678846159019641</v>
+        <v>0.2345293224108893</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.292642429868549</v>
+        <v>3.272629253773903</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632645</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.122575682824274</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.895028646869445</v>
+        <v>-2.939663108455899</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.964207799762749</v>
+        <v>1.946354015128168</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2678846159019641</v>
+        <v>0.2345293224108893</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.283306452365453</v>
+        <v>3.263293276270808</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777682</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.281481808675443</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.893303603579401</v>
+        <v>-2.937938065165855</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.123803942929936</v>
+        <v>2.105950158295354</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.2696096591920079</v>
+        <v>0.236254365700933</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.443247604190648</v>
+        <v>3.423234428096003</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644421</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.31855963116909</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.048084610357656</v>
+        <v>-3.09271907194411</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.09896936271228</v>
+        <v>2.081115578077698</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.2362419851375318</v>
+        <v>0.2028866916464569</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.460304822251609</v>
+        <v>3.440291646156964</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799969</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.315234987158635</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.996649276972997</v>
+        <v>-3.041283738559451</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.116218852055689</v>
+        <v>2.098365067421107</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.2876773185221914</v>
+        <v>0.2543220250311166</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.48784137827195</v>
+        <v>3.467828202177305</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331124</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.325241140803377</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.969698052646509</v>
+        <v>-3.014332514232963</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.137005495431026</v>
+        <v>2.119151710796444</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.3025576645499106</v>
+        <v>0.2692023710588357</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.506775739533323</v>
+        <v>3.486762563438679</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784117</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.509344272948336</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.105651060702825</v>
+        <v>-3.150285522289279</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.266727424353459</v>
+        <v>2.248873639718878</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.3025576645499106</v>
+        <v>0.2692023710588357</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.690878871678283</v>
+        <v>3.670865695583638</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571443</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.50146096785133</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.128059178507697</v>
+        <v>-3.172693640094151</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.249880872134503</v>
+        <v>2.232027087499922</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.3025576645499106</v>
+        <v>0.2692023710588357</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.682995566581276</v>
+        <v>3.662982390486631</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155041</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.503514967400967</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.276064945987097</v>
+        <v>-3.320699407573551</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.192732564692381</v>
+        <v>2.174878780057799</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.2158306556863691</v>
+        <v>0.1824753621952943</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.633013360812789</v>
+        <v>3.613000184718144</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161986</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.559768685122814</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.285505871875626</v>
+        <v>-3.330140333462081</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.245209912058816</v>
+        <v>2.227356127424234</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.3382577732297605</v>
+        <v>0.3049024797386857</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.762723349060671</v>
+        <v>3.742710172966026</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321643</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.562659779668115</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.28421910833607</v>
+        <v>-3.328853569922524</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.24861571201994</v>
+        <v>2.230761927385358</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.3395445367693171</v>
+        <v>0.3061892432782423</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.766386501729706</v>
+        <v>3.74637332563506</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347711</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.56077159256189</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.285776162325361</v>
+        <v>-3.330410623911816</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.246104703317998</v>
+        <v>2.228250918683417</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.3395445367693171</v>
+        <v>0.3061892432782423</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.764498314623481</v>
+        <v>3.744485138528836</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887755</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.555591822164752</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.293048047848826</v>
+        <v>-3.33768250943528</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.238016178711475</v>
+        <v>2.220162394076893</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.3322726512458524</v>
+        <v>0.2989173577547775</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.754955412912264</v>
+        <v>3.734942236817619</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343073</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.554025832374905</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.291207028790575</v>
+        <v>-3.335841490377029</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.237186596544928</v>
+        <v>2.219332811910346</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3335408779173208</v>
+        <v>0.3001855844262459</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.754150359125298</v>
+        <v>3.734137183030652</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647114</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.567099239240823</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.298115734290255</v>
+        <v>-3.34275019587671</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.247496521210974</v>
+        <v>2.229642736576392</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3335408779173208</v>
+        <v>0.3001855844262459</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.767223765991216</v>
+        <v>3.747210589896571</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763537</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.567099239240823</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.299677377105115</v>
+        <v>-3.344311838691569</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.24687186408503</v>
+        <v>2.229018079450448</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3335408779173208</v>
+        <v>0.3001855844262459</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.767223765991216</v>
+        <v>3.747210589896571</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.71583405539212</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.565623280367825</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.327578164214588</v>
+        <v>-3.372212625801042</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.234235590368243</v>
+        <v>2.216381805733661</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.298943953774386</v>
+        <v>0.2655886602833111</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.744989652632457</v>
+        <v>3.724976476537812</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172532</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.562387724345024</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.330611161727262</v>
+        <v>-3.375245623313716</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.229786835340372</v>
+        <v>2.21193305070579</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2959109562617121</v>
+        <v>0.2625556627706372</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.739934298102052</v>
+        <v>3.719921122007407</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971083</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.629093683935528</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.350672483003769</v>
+        <v>-3.395306944590223</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.288468266420273</v>
+        <v>2.270614481785691</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2758496349852051</v>
+        <v>0.2424943414941302</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.794603464926651</v>
+        <v>3.774590288832006</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,19 +47913,19 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.877238500390725</v>
+        <v>3.877238500390718</v>
       </c>
       <c r="C2016" t="n">
         <v>3.91133072868687</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.350672483003769</v>
+        <v>-3.395306944590223</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.288468266420273</v>
+        <v>2.270614481785691</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2758496349852051</v>
+        <v>0.2424943414941302</v>
       </c>
       <c r="G2016" t="n">
         <v>3.904394525673238</v>

--- a/tame_output/ON/bt/strategyON_20240705.xlsx
+++ b/tame_output/ON/bt/strategyON_20240705.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.8%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-681.4%</t>
+          <t>-673.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.3%</t>
+          <t>-69.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.6%</t>
+          <t>451.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-501.1%</t>
+          <t>-527.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-272.9%</t>
+          <t>-269.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-149.2%</t>
+          <t>-159.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-59.5%</t>
+          <t>-171.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-199.7%</t>
+          <t>-217.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-55.6%</t>
+          <t>-78.6%</t>
         </is>
       </c>
     </row>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7213888716875563</v>
+        <v>-0.641369400053315</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.832416789337956</v>
+        <v>2.864424577991652</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9289546560791682</v>
+        <v>-0.8489351844449269</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.747215271700552</v>
+        <v>2.779223060354248</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.346708679626005</v>
+        <v>-1.266689207991764</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.57804055378688</v>
+        <v>2.610048342440576</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.636840346231436</v>
+        <v>-1.556820874597195</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.461854103743629</v>
+        <v>2.493861892397326</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.844844404584514</v>
+        <v>-1.764824932950273</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.383544624956324</v>
+        <v>2.41555241361002</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.056256825472489</v>
+        <v>-1.976237353838248</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.294061112939122</v>
+        <v>2.326068901592818</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.422325552617142</v>
+        <v>-2.3423060809829</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.14071792138771</v>
+        <v>2.172725710041406</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.630816334068826</v>
+        <v>-2.550796862434585</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.077659898545804</v>
+        <v>2.109667687199501</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.878017518834048</v>
+        <v>-2.797998047199806</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.986878175048284</v>
+        <v>2.01888596370198</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.370402546858144</v>
+        <v>-3.290383075223903</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.791030555882378</v>
+        <v>1.823038344536074</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.755582937788217</v>
+        <v>-3.675563466153975</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.635500938323212</v>
+        <v>1.667508726976908</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.005453617802798</v>
+        <v>-3.925434146168557</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.537321789771996</v>
+        <v>1.569329578425692</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.21196539468982</v>
+        <v>-4.131945923055579</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.450823137673445</v>
+        <v>1.482830926327141</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.531309469770322</v>
+        <v>-4.451289998136081</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.324858434341504</v>
+        <v>1.3568662229952</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.963115262920109</v>
+        <v>-4.883095791285868</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.138469004548993</v>
+        <v>1.170476793202689</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.197809257052661</v>
+        <v>-5.11778978541842</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.032876181898063</v>
+        <v>1.064883970551759</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.533471904283114</v>
+        <v>-5.453452432648873</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8971917146618469</v>
+        <v>0.9291995033155431</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.897098149183427</v>
+        <v>-5.817078677549186</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.758228776935963</v>
+        <v>0.7902365655896597</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.262225531822174</v>
+        <v>-6.182206060187933</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6114323388862957</v>
+        <v>0.6434401275399924</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.670814309002852</v>
+        <v>-6.590794837368611</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4467583720287838</v>
+        <v>0.47876616068248</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.947390409318684</v>
+        <v>-6.867370937684443</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3313133643739112</v>
+        <v>0.3633211530276075</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.363782283605682</v>
+        <v>-7.283762811971441</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1627506652679895</v>
+        <v>0.1947584539216862</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.608053684332751</v>
+        <v>-7.52803421269851</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.07530079564584069</v>
+        <v>0.1073085842995374</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.813304703569512</v>
+        <v>-7.733285231935271</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.01070004690316795</v>
+        <v>0.0213077417505283</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.976884581753895</v>
+        <v>-7.896865110119654</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.07772707812192037</v>
+        <v>-0.04571928946822412</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.273545923564093</v>
+        <v>-8.193526451929852</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1926126389167915</v>
+        <v>-0.1606048502630952</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.460265631873396</v>
+        <v>-8.380246160239155</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2713268267749158</v>
+        <v>-0.2393190381212196</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.843267020616027</v>
+        <v>-8.763247548981786</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4246294835935522</v>
+        <v>-0.392621694939856</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.025136811601062</v>
+        <v>-8.945117339966821</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4948058840161362</v>
+        <v>-0.4627980953624395</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.384667134105063</v>
+        <v>-9.304647662470822</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6332677097196866</v>
+        <v>-0.6012599210659904</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.435016197559285</v>
+        <v>-9.354996725925044</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6454913151441981</v>
+        <v>-0.6134835264905014</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539465</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.532635474980681</v>
+        <v>-9.45261600334644</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6814972754909876</v>
+        <v>-0.6494894868372909</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.680161562986324</v>
+        <v>-9.600142091352083</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7376141543716725</v>
+        <v>-0.7056063657179759</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.884419738316188</v>
+        <v>-9.804400266681947</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8138042273849755</v>
+        <v>-0.7817964387312792</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.918072576824661</v>
+        <v>-9.83805310519042</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8227828083039288</v>
+        <v>-0.7907750196502326</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.41055738586864</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.844602745157212</v>
+        <v>-9.764583273522971</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7780231741435282</v>
+        <v>-0.7460153854898319</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.337087554201192</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.01972716254376</v>
+        <v>-9.939707690909515</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8335177203506285</v>
+        <v>-0.8015099316969323</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.512211971587735</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.25417925655825</v>
+        <v>-10.174159784924</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9345177228580206</v>
+        <v>-0.9025099342043243</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.512211971587735</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.35855398758469</v>
+        <v>-10.27853451595045</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9829398060425754</v>
+        <v>-0.9509320173888791</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.616586702614181</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.41134014318502</v>
+        <v>-10.33132067155078</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.00293847844415</v>
+        <v>-0.9709306897904533</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.712262189196578</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.53737693655331</v>
+        <v>-10.45735746491907</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.050659467162351</v>
+        <v>-1.018651678508654</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.687010566386836</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.48536142258449</v>
+        <v>-10.40534195095025</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.025862925888425</v>
+        <v>-0.9938551372347284</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.687010566386836</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.62703326430861</v>
+        <v>-10.54701379267437</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.084006889476814</v>
+        <v>-1.051999100823118</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.687010566386836</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940722</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.57744241988378</v>
+        <v>-10.49742294824954</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.049117141542009</v>
+        <v>-1.017109352888312</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.637419721962002</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770583</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.56463502687901</v>
+        <v>-10.48461555524477</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.057045317986782</v>
+        <v>-1.025037529333086</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.686275496970903</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615286</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.33878987415959</v>
+        <v>-10.25877040252535</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9571281838628081</v>
+        <v>-0.9251203952091118</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.64434882138374</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812106</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.214211217822</v>
+        <v>-10.13419174618776</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9061575767717129</v>
+        <v>-0.8741497881180167</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.64434882138374</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.71093553364622</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.26710650586629</v>
+        <v>-10.18708703423205</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9246819178273196</v>
+        <v>-0.8926741291736233</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.639393475295293</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.19497333057841</v>
+        <v>-10.11495385894417</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8900949434735308</v>
+        <v>-0.8580871548198346</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.639393475295293</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.12360693796876</v>
+        <v>-10.04358746633452</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8712856488235374</v>
+        <v>-0.8392778601698403</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.568027082685645</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232417</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.03014790398354</v>
+        <v>-9.950128432349295</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8437855165423547</v>
+        <v>-0.8117777278886584</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.568027082685645</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436233</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.762906103115139</v>
+        <v>-9.682886631480898</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7387233566943694</v>
+        <v>-0.7067155680406731</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.568027082685645</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311953</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.664999064438648</v>
+        <v>-9.584979592804407</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6998608561972341</v>
+        <v>-0.6678530675435375</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.500041332825089</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097249</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.64104552346269</v>
+        <v>-9.561026051828449</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6896109336613572</v>
+        <v>-0.6576031450076609</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.476087791849131</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.376985585139893</v>
+        <v>-9.296966113505652</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5972472744939905</v>
+        <v>-0.5652394858402943</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.212027853526335</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.83325274783973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.669905961635056</v>
+        <v>-8.589886490000815</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3172024587523565</v>
+        <v>-0.2851946700986603</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.212027853526335</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388733</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.629721663268866</v>
+        <v>-8.549702191634625</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.300785115518039</v>
+        <v>-0.2687773268643427</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.171843555160144</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626479</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.466321792329502</v>
+        <v>-8.386302320695261</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2360583459215366</v>
+        <v>-0.2040505572678404</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.008443684220782</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291815</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.232840570099903</v>
+        <v>-8.152821098465662</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1347414281918446</v>
+        <v>-0.1027336395381484</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.774962461991183</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785791</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.083174179092389</v>
+        <v>-8.003154707458147</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07776708210179795</v>
+        <v>-0.04575929344810126</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.682058970748648</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390431</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.950898705461502</v>
+        <v>-7.870879233827261</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02948940590241644</v>
+        <v>0.002518382751280246</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.549783497117761</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.79516037290176</v>
+        <v>-7.715140901267519</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.03562098780911693</v>
+        <v>0.06762877646281362</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.394045164558019</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960991</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.546160574218179</v>
+        <v>-7.466141102583938</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1481272485062082</v>
+        <v>0.1801350371599049</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.394045164558019</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607649</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.651750563991284</v>
+        <v>-7.571731092357043</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.02208467700225247</v>
+        <v>0.009923111651444216</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.499635154331124</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987907</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.670485466109881</v>
+        <v>-7.59046599447564</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.01896570402739517</v>
+        <v>0.05097349268109186</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.505231163991255</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.522545424702281</v>
+        <v>-7.44252595306804</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.04173720209773268</v>
+        <v>-0.009729413444035995</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.484910248082697</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.469575902448293</v>
+        <v>-7.389556430814052</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02926337944961555</v>
+        <v>0.002744409204081144</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.431940725828709</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098113</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.426027495677602</v>
+        <v>-7.346008024043361</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01880462883643252</v>
+        <v>0.01320315981726417</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.431940725828709</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493424</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.183879102223744</v>
+        <v>-7.103859630589503</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09251708292625382</v>
+        <v>0.1245248715799505</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.431940725828709</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.82855148672282</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.075619965101223</v>
+        <v>-6.995600493466982</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1303528582344575</v>
+        <v>0.1623606468881542</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.431940725828709</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.952328830284092</v>
+        <v>-6.872309358649851</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1771674061718866</v>
+        <v>0.2091751948255838</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.308649591011578</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.931179631380648</v>
+        <v>-6.851160159746407</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1933280639705894</v>
+        <v>0.2253358526242861</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.287500392108135</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318097</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.687414189397204</v>
+        <v>-6.595259474391562</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2866149491110179</v>
+        <v>0.3234768351132749</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.287500392108135</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.82431123305753</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.585651369119909</v>
+        <v>-6.493496654114267</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3294443911419518</v>
+        <v>0.3663062771442087</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.274281323715706</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279189</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.335800975170835</v>
+        <v>-6.243646260165193</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4221266237052839</v>
+        <v>0.4589885097075408</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.274281323715706</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011502</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.159908882703402</v>
+        <v>-6.06775416769776</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4960825842129055</v>
+        <v>0.5329444702151629</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.274281323715706</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392991</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.988462419680938</v>
+        <v>-5.896307704675296</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5779886754764449</v>
+        <v>0.6148505614787019</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.102834860693243</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632785</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.914172853942599</v>
+        <v>-5.822018138936957</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6067249793880776</v>
+        <v>0.6435868653903345</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.028545294954904</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883078</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.850537111708665</v>
+        <v>-5.758382396703023</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6368740773359685</v>
+        <v>0.6737359633382258</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.9649095527209691</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074788</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.739110352382744</v>
+        <v>-5.646955637377102</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6626390398501321</v>
+        <v>0.6995009258523894</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.9649095527209691</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.7976948842423</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.498679855577884</v>
+        <v>-5.406525140572242</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7605543151969538</v>
+        <v>0.7974162011992108</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7244790559161088</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.82159350936769</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.42643728740669</v>
+        <v>-5.334282572401047</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7933806563002519</v>
+        <v>0.8302425423025088</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7244790559161088</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879971</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.373438965125302</v>
+        <v>-5.28128425011966</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.815258569130147</v>
+        <v>0.852120455132404</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.66914279691417</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.264634079645575</v>
+        <v>-5.172479364639933</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8557785945420311</v>
+        <v>0.8926404805442885</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.66914279691417</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675945</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.044613281608564</v>
+        <v>-4.952458566602922</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9453659507674494</v>
+        <v>0.9822278367697068</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5279229518461898</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539956</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.911745592545286</v>
+        <v>-4.819590877539644</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.014407209194584</v>
+        <v>1.051269095196841</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5279229518461898</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.791572509180788</v>
+        <v>-4.699417794175146</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.063622286980685</v>
+        <v>1.100484172982942</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4077498684816908</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.64690036408105</v>
+        <v>-4.554745649075408</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.13157924758202</v>
+        <v>1.168441133584277</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.2630777233819534</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.706775191438743</v>
+        <v>-4.6146204764331</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.093666808040369</v>
+        <v>1.130528694042626</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3229525507396455</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.586954960527906</v>
+        <v>-4.494800245522264</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.156884069638912</v>
+        <v>1.19374595564117</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3229525507396455</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.992094879537234</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.589424666989712</v>
+        <v>-4.49726995198407</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.155968588427602</v>
+        <v>1.192830474429859</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3254222572014517</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
         <v>3.003101802011936</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.657794853313722</v>
+        <v>-4.56564013830808</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.1396274363727</v>
+        <v>1.176489322374957</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3161465581652367</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
         <v>2.993538510643827</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.671582906160769</v>
+        <v>-4.579428191155126</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.124548923865773</v>
+        <v>1.16141080986803</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3161465581652367</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417708</v>
       </c>
       <c r="C1938" t="n">
         <v>2.818248075684214</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.702576065489474</v>
+        <v>-4.610421350483832</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9368612251746773</v>
+        <v>0.9737231111769344</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3161465581652367</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.822815307676002</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.527101805697004</v>
+        <v>-4.434947090691362</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.011618161083453</v>
+        <v>1.04848004708571</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3161465581652367</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.798557336437209</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.638038058338253</v>
+        <v>-4.545883343332611</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9429856887881605</v>
+        <v>0.9798475747904176</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3161465581652367</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.801688721657114</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.604374512865971</v>
+        <v>-4.512219797860329</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9595824921969789</v>
+        <v>0.996444378199236</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2824830126929549</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.811861108089247</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.544521893662248</v>
+        <v>-4.452367178656606</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9936959263106004</v>
+        <v>1.030557812312858</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2824830126929549</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.806807378663107</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.45827843063587</v>
+        <v>-4.366123715630228</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.023139582095012</v>
+        <v>1.060001468097269</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2824830126929549</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316051</v>
       </c>
       <c r="C1944" t="n">
         <v>2.798583154107633</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.50358525003485</v>
+        <v>-4.411430535029208</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9967926297799454</v>
+        <v>1.033654515782203</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3232931757021857</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
         <v>2.799135027140734</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.532618354737151</v>
+        <v>-4.440463639731509</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9857312609321265</v>
+        <v>1.022593146934384</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3232931757021857</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.7284077190321</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.439807873286291</v>
+        <v>-4.347653158280649</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9521281454038362</v>
+        <v>0.9889900314060933</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2304826942513263</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.74828581656043</v>
       </c>
       <c r="C1947" t="n">
         <v>2.730281194956701</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.484197342615719</v>
+        <v>-4.392042627610077</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9362458335966659</v>
+        <v>0.9731077195989231</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.274872163580754</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472743</v>
       </c>
       <c r="C1948" t="n">
         <v>2.725356903468424</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.371526124379469</v>
+        <v>-4.279371409373827</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9763900294028889</v>
+        <v>1.013251915405146</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1622009453445038</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798543</v>
       </c>
       <c r="C1949" t="n">
         <v>2.730848199299091</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.259149123196796</v>
+        <v>-4.166994408191154</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.026832125706625</v>
+        <v>1.063694011708883</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1622009453445038</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498871</v>
       </c>
       <c r="C1950" t="n">
         <v>2.74234540106763</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.286929521098148</v>
+        <v>-4.194774806092506</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.027217168314623</v>
+        <v>1.064079054316881</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1899813432458569</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705331</v>
       </c>
       <c r="C1951" t="n">
         <v>2.580701121068283</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.369930802123427</v>
+        <v>-4.277776087117785</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8323723759051651</v>
+        <v>0.8692342619074223</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2085522277730306</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729275</v>
       </c>
       <c r="C1952" t="n">
         <v>2.700850781787489</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.478544880566758</v>
+        <v>-4.386390165561116</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9090764052470384</v>
+        <v>0.9459382912492955</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2085522277730306</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190774</v>
       </c>
       <c r="C1953" t="n">
         <v>2.715363807889812</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.443135842318616</v>
+        <v>-4.350981127312973</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9377530466486184</v>
+        <v>0.9746149326508755</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2085522277730306</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913431</v>
       </c>
       <c r="C1954" t="n">
         <v>2.712783249232181</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.404752179760465</v>
+        <v>-4.312597464754822</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9505259530142476</v>
+        <v>0.9873878390165047</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1701685652148794</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532492</v>
       </c>
       <c r="C1955" t="n">
         <v>2.709512278077483</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.227635849725298</v>
+        <v>-4.135481134719656</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.018101513873616</v>
+        <v>1.054963399875874</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1701685652148794</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.74132844879391</v>
       </c>
       <c r="C1956" t="n">
         <v>2.710195669839396</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.272728094558844</v>
+        <v>-4.180573379553202</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.000748007702111</v>
+        <v>1.037609893704368</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2320646083842692</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011242</v>
       </c>
       <c r="C1957" t="n">
         <v>2.70398264514581</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.093352673320076</v>
+        <v>-4.001197958314434</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.066285151504033</v>
+        <v>1.10314703750629</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.07528785021355056</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982237</v>
       </c>
       <c r="C1958" t="n">
         <v>2.6847901004774</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.138366886840682</v>
+        <v>-4.04621217183504</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.02908692142738</v>
+        <v>1.065948807429637</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1056367455281552</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509545</v>
       </c>
       <c r="C1959" t="n">
         <v>2.690481662816346</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.405371397113117</v>
+        <v>-4.313216682107475</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9279766796573519</v>
+        <v>0.964838565659609</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.2999997835711037</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760816</v>
       </c>
       <c r="C1960" t="n">
         <v>2.689685584712847</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.50656917855029</v>
+        <v>-4.414414463544648</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8867014889789842</v>
+        <v>0.9235633749812413</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3684085971164229</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.70557166181546</v>
       </c>
       <c r="C1961" t="n">
         <v>2.687285546267164</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.500058211935977</v>
+        <v>-4.407903496930335</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8869058371790259</v>
+        <v>0.9237677231812831</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3684085971164229</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378105</v>
       </c>
       <c r="C1962" t="n">
         <v>2.683810265475409</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.48102008422868</v>
+        <v>-4.388865369223038</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8910458074701897</v>
+        <v>0.9279076934724468</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4265922084476175</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131256</v>
       </c>
       <c r="C1963" t="n">
         <v>2.86139213441409</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.512146715379298</v>
+        <v>-4.419992000373656</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.056177023948623</v>
+        <v>1.09303890995088</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4265922084476175</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067872</v>
       </c>
       <c r="C1964" t="n">
         <v>2.862225463400223</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.526013476713216</v>
+        <v>-4.433858761707574</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.051463648401189</v>
+        <v>1.088325534403447</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4644501251814404</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789129</v>
       </c>
       <c r="C1965" t="n">
         <v>2.868233993797149</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.481209305173286</v>
+        <v>-4.389054590167644</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.075393847414087</v>
+        <v>1.112255733416344</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4644501251814404</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519915</v>
       </c>
       <c r="C1966" t="n">
         <v>2.947386641589171</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.333466334938284</v>
+        <v>-4.241311619932642</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.21364368330011</v>
+        <v>1.250505569302367</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2966427679465573</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181177</v>
       </c>
       <c r="C1967" t="n">
         <v>2.950180263120652</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.435481017469505</v>
+        <v>-4.343326302463863</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.175631431819103</v>
+        <v>1.21249331782136</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2966427679465573</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394738</v>
       </c>
       <c r="C1968" t="n">
         <v>2.95084261151231</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.429328311416721</v>
+        <v>-4.337173596411079</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.178754862631875</v>
+        <v>1.215616748634132</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.290490061893773</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890615</v>
       </c>
       <c r="C1969" t="n">
         <v>2.949923088252421</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.446137609567223</v>
+        <v>-4.353982894561581</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.171111620111784</v>
+        <v>1.207973506114041</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3072993600442746</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798433</v>
       </c>
       <c r="C1970" t="n">
         <v>3.016258642049241</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.3838396107911</v>
+        <v>-4.291684895785458</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.262366373419054</v>
+        <v>1.299228259421311</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3072993600442746</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.8487291399922</v>
       </c>
       <c r="C1971" t="n">
         <v>2.724839514438639</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.182049413125942</v>
+        <v>-4.0898946981203</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.051663324874515</v>
+        <v>1.088525210876772</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.1092811678751202</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852429</v>
       </c>
       <c r="C1972" t="n">
         <v>2.795129746760815</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.108671316037206</v>
+        <v>-4.016516601031564</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.151304796032185</v>
+        <v>1.188166682034442</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.03590307078638366</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319554</v>
       </c>
       <c r="C1973" t="n">
         <v>2.809757482876858</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.206411860662181</v>
+        <v>-4.114257145656539</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.126836314298239</v>
+        <v>1.163698200300496</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.05179234891936385</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489393</v>
       </c>
       <c r="C1974" t="n">
         <v>2.80829346370153</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.38274962078511</v>
+        <v>-4.290594905779468</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.054837191073739</v>
+        <v>1.091699077075996</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2281301090422932</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397802</v>
       </c>
       <c r="C1975" t="n">
         <v>2.806785081741459</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.306327574353183</v>
+        <v>-4.214172859347541</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.083897627686438</v>
+        <v>1.120759513688695</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2281301090422932</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316257</v>
       </c>
       <c r="C1976" t="n">
         <v>2.806647949176895</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.261954442714615</v>
+        <v>-4.169799727708972</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.101509747777302</v>
+        <v>1.138371633779559</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.1837569774037247</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105971</v>
       </c>
       <c r="C1977" t="n">
         <v>2.801041743315485</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.139120221827447</v>
+        <v>-4.046965506821805</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.145037230270759</v>
+        <v>1.181899116273016</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.1837569774037247</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190329</v>
       </c>
       <c r="C1978" t="n">
         <v>2.807423500343289</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.091464491266391</v>
+        <v>-3.999309776260749</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.170481279522986</v>
+        <v>1.207343165525243</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.136101246842669</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569622</v>
       </c>
       <c r="C1979" t="n">
         <v>2.812315873718014</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.990946332767637</v>
+        <v>-3.898791617761995</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.215580916297212</v>
+        <v>1.25244280229947</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.03558308834391444</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557297</v>
       </c>
       <c r="C1980" t="n">
         <v>2.799070546193887</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.051612923170026</v>
+        <v>-3.959458208164384</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.178068952612129</v>
+        <v>1.214930838614386</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.1172814050624481</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932773</v>
       </c>
       <c r="C1981" t="n">
         <v>2.803168248804515</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.006774521561628</v>
+        <v>-3.914619806555986</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.200102015866117</v>
+        <v>1.236963901868374</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.1127379721175786</v>
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917057</v>
       </c>
       <c r="C1982" t="n">
         <v>2.807329188435593</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.843019775191809</v>
+        <v>-4.015378442312984</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.269764854045122</v>
+        <v>1.200821387196653</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.02884904036386382</v>
+        <v>-0.2015635408445841</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.790019764217275</v>
+        <v>2.686391063928843</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405966</v>
       </c>
       <c r="C1983" t="n">
         <v>2.81320879096343</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.798816938105908</v>
+        <v>-3.971175605227083</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.293325591407319</v>
+        <v>1.22438212455885</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.01535379672203663</v>
+        <v>-0.1573607037586836</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.822421068996653</v>
+        <v>2.71879236870822</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265652</v>
       </c>
       <c r="C1984" t="n">
         <v>2.811618791432678</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.835795965769352</v>
+        <v>-4.008154632890527</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.27694398081119</v>
+        <v>1.20800051396272</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.05232769851336716</v>
+        <v>-0.1203868019673531</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.843015410540698</v>
+        <v>2.739386710252266</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284886</v>
       </c>
       <c r="C1985" t="n">
         <v>2.862866556615717</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.855854044634192</v>
+        <v>-4.028212711755367</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.320168514448293</v>
+        <v>1.251225047599824</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.05232769851336716</v>
+        <v>-0.1203868019673531</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.894263175723738</v>
+        <v>2.790634475435306</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321028</v>
       </c>
       <c r="C1986" t="n">
         <v>2.861307261209971</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.815923371456301</v>
+        <v>-3.988282038577477</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.334581488313703</v>
+        <v>1.265638021465233</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.0922583716912575</v>
+        <v>-0.08045612878946273</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.916662284224725</v>
+        <v>2.813033583936293</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475145</v>
       </c>
       <c r="C1987" t="n">
         <v>2.856255489448241</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.764891278733773</v>
+        <v>-3.937249945854949</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.349942553640984</v>
+        <v>1.280999086792515</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.1432904644137855</v>
+        <v>-0.02942403606693478</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.942229768096512</v>
+        <v>2.83860106780808</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404861</v>
       </c>
       <c r="C1988" t="n">
         <v>2.873442893540946</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.699667097606568</v>
+        <v>-3.872025764727743</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.393219630184571</v>
+        <v>1.324276163336102</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.2085146455409911</v>
+        <v>0.03580014506027085</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.99855168086554</v>
+        <v>2.894922980577108</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882565</v>
       </c>
       <c r="C1989" t="n">
         <v>2.869403865840226</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.662240077535434</v>
+        <v>-3.834598744656609</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.404151410512305</v>
+        <v>1.335207943663836</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.2137661835701727</v>
+        <v>0.04105168308945251</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.99766357598233</v>
+        <v>2.894034875693898</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992669</v>
       </c>
       <c r="C1990" t="n">
         <v>2.870660658171466</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.682351733570142</v>
+        <v>-3.854710400691318</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.397363540429662</v>
+        <v>1.328420073581193</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.2247935285675919</v>
+        <v>0.0520790280868717</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.005536775312021</v>
+        <v>2.90190807502359</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636294</v>
       </c>
       <c r="C1991" t="n">
         <v>3.031218429192677</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.628606919142937</v>
+        <v>-3.800965586264113</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.579419237221755</v>
+        <v>1.510475770373285</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.2348568380080539</v>
+        <v>0.06214233752733367</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.17213253199751</v>
+        <v>3.068503831709077</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957632</v>
       </c>
       <c r="C1992" t="n">
         <v>3.151331338410494</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.604815350536795</v>
+        <v>-3.777174017657971</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.709048773882029</v>
+        <v>1.640105307033559</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.2586484066141962</v>
+        <v>0.08593390613347596</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.306520382379012</v>
+        <v>3.20289168209058</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
         <v>3.143039314424353</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.578731266272987</v>
+        <v>-3.751089933394163</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.711190383601411</v>
+        <v>1.642246916752941</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.2586484066141962</v>
+        <v>0.08593390613347596</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.298228358392871</v>
+        <v>3.194599658104439</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896932</v>
       </c>
       <c r="C1994" t="n">
         <v>3.141232510008133</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.50060008542404</v>
+        <v>-3.672958752545216</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.740636051524769</v>
+        <v>1.6716925846763</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3328252174978807</v>
+        <v>0.1601107170171605</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.340927640506862</v>
+        <v>3.237298940218429</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959863</v>
       </c>
       <c r="C1995" t="n">
         <v>3.158786915734924</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.491707624030757</v>
+        <v>-3.664066291151933</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.761747441808874</v>
+        <v>1.692803974960404</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3328252174978807</v>
+        <v>0.1601107170171605</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.358482046233653</v>
+        <v>3.254853345945221</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945372</v>
       </c>
       <c r="C1996" t="n">
         <v>3.150641963139508</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.660183741000635</v>
+        <v>-3.832542408121811</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.686212042425506</v>
+        <v>1.617268575577037</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3048773817813</v>
+        <v>0.1321628813005797</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.333568392208288</v>
+        <v>3.229939691919856</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782715</v>
       </c>
       <c r="C1997" t="n">
         <v>3.13191166032737</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.962384212139052</v>
+        <v>-3.134742879260227</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.946601551158002</v>
+        <v>1.877658084309532</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2345293224108893</v>
+        <v>0.06181482193016902</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.272629253773903</v>
+        <v>3.169000553485471</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632645</v>
       </c>
       <c r="C1998" t="n">
         <v>3.122575682824274</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.939663108455899</v>
+        <v>-3.112021775577075</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.946354015128168</v>
+        <v>1.877410548279698</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2345293224108893</v>
+        <v>0.06181482193016902</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.263293276270808</v>
+        <v>3.159664575982376</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777682</v>
       </c>
       <c r="C1999" t="n">
         <v>3.281481808675443</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.937938065165855</v>
+        <v>-3.110296732287031</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.105950158295354</v>
+        <v>2.037006691446885</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.236254365700933</v>
+        <v>0.06353986522021277</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.423234428096003</v>
+        <v>3.319605727807571</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644421</v>
       </c>
       <c r="C2000" t="n">
         <v>3.31855963116909</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.09271907194411</v>
+        <v>-3.265077739065286</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.081115578077698</v>
+        <v>2.012172111229229</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.2028866916464569</v>
+        <v>0.03017219116573666</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.440291646156964</v>
+        <v>3.336662945868532</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799969</v>
       </c>
       <c r="C2001" t="n">
         <v>3.315234987158635</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.041283738559451</v>
+        <v>-3.213642405680627</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.098365067421107</v>
+        <v>2.029421600572638</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.2543220250311166</v>
+        <v>0.08160752455039633</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.467828202177305</v>
+        <v>3.364199501888873</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331124</v>
       </c>
       <c r="C2002" t="n">
         <v>3.325241140803377</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.014332514232963</v>
+        <v>-3.186691181354139</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.119151710796444</v>
+        <v>2.050208243947975</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2692023710588357</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.486762563438679</v>
+        <v>3.383133863150246</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784117</v>
       </c>
       <c r="C2003" t="n">
         <v>3.509344272948336</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.150285522289279</v>
+        <v>-3.322644189410455</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.248873639718878</v>
+        <v>2.179930172870408</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2692023710588357</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.670865695583638</v>
+        <v>3.567236995295206</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.74392550571443</v>
       </c>
       <c r="C2004" t="n">
         <v>3.50146096785133</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.172693640094151</v>
+        <v>-3.345052307215327</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.232027087499922</v>
+        <v>2.163083620651452</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2692023710588357</v>
+        <v>0.09648787057811548</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.662982390486631</v>
+        <v>3.559353690198199</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155041</v>
       </c>
       <c r="C2005" t="n">
         <v>3.503514967400967</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.320699407573551</v>
+        <v>-3.493058074694726</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.174878780057799</v>
+        <v>2.10593531320933</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1824753621952943</v>
+        <v>0.009760861714574021</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.613000184718144</v>
+        <v>3.509371484429712</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161986</v>
       </c>
       <c r="C2006" t="n">
         <v>3.559768685122814</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.330140333462081</v>
+        <v>-3.502499000583256</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.227356127424234</v>
+        <v>2.158412660575765</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.3049024797386857</v>
+        <v>0.1321879792579654</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.742710172966026</v>
+        <v>3.639081472677594</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321643</v>
       </c>
       <c r="C2007" t="n">
         <v>3.562659779668115</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.328853569922524</v>
+        <v>-3.5012122370437</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.230761927385358</v>
+        <v>2.161818460536888</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.3061892432782423</v>
+        <v>0.133474742797522</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.74637332563506</v>
+        <v>3.642744625346628</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347711</v>
       </c>
       <c r="C2008" t="n">
         <v>3.56077159256189</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.330410623911816</v>
+        <v>-3.502769291032991</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.228250918683417</v>
+        <v>2.159307451834947</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.3061892432782423</v>
+        <v>0.133474742797522</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.744485138528836</v>
+        <v>3.640856438240403</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887755</v>
       </c>
       <c r="C2009" t="n">
         <v>3.555591822164752</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.33768250943528</v>
+        <v>-3.510041176556456</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.220162394076893</v>
+        <v>2.151218927228423</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.2989173577547775</v>
+        <v>0.1262028572740573</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.734942236817619</v>
+        <v>3.631313536529187</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343073</v>
       </c>
       <c r="C2010" t="n">
         <v>3.554025832374905</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.335841490377029</v>
+        <v>-3.508200157498205</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.219332811910346</v>
+        <v>2.150389345061877</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3001855844262459</v>
+        <v>0.1274710839455257</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.734137183030652</v>
+        <v>3.63050848274222</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647114</v>
       </c>
       <c r="C2011" t="n">
         <v>3.567099239240823</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.34275019587671</v>
+        <v>-3.515108862997885</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.229642736576392</v>
+        <v>2.160699269727923</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3001855844262459</v>
+        <v>0.1274710839455257</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.747210589896571</v>
+        <v>3.643581889608139</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763537</v>
       </c>
       <c r="C2012" t="n">
         <v>3.567099239240823</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.344311838691569</v>
+        <v>-3.516670505812745</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.229018079450448</v>
+        <v>2.160074612601979</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3001855844262459</v>
+        <v>0.1274710839455257</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.747210589896571</v>
+        <v>3.643581889608139</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.71583405539212</v>
       </c>
       <c r="C2013" t="n">
         <v>3.565623280367825</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.372212625801042</v>
+        <v>-3.544571292922218</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.216381805733661</v>
+        <v>2.147438338885192</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.2655886602833111</v>
+        <v>0.09287415980259089</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.724976476537812</v>
+        <v>3.62134777624938</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172532</v>
       </c>
       <c r="C2014" t="n">
         <v>3.562387724345024</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.375245623313716</v>
+        <v>-3.547604290434892</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.21193305070579</v>
+        <v>2.142989583857321</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2625556627706372</v>
+        <v>0.08984116228991701</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.719921122007407</v>
+        <v>3.616292421718974</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971084</v>
       </c>
       <c r="C2015" t="n">
         <v>3.629093683935528</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.395306944590223</v>
+        <v>-3.567665611711399</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.270614481785691</v>
+        <v>2.201671014937222</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2424943414941302</v>
+        <v>0.06977984101341</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.774590288832006</v>
+        <v>3.670961588543574</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.877238500390718</v>
+        <v>3.556003981668339</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.91133072868687</v>
+        <v>3.632745047394486</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.395306944590223</v>
+        <v>-3.660057393966329</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.270614481785691</v>
+        <v>2.168365665494208</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2424943414941302</v>
+        <v>0.06977984101341</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.904394525673238</v>
+        <v>3.674612952002533</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240705.xlsx
+++ b/tame_output/ON/bt/strategyON_20240705.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-673.4%</t>
+          <t>-678.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-69.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.5%</t>
+          <t>450.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-527.6%</t>
+          <t>-533.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-269.7%</t>
+          <t>-271.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-39.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-159.4%</t>
+          <t>-161.7%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.641369400053315</v>
+        <v>-0.6882239671337554</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.864424577991652</v>
+        <v>2.845682751159476</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.8489351844449269</v>
+        <v>-0.8957897515253673</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.779223060354248</v>
+        <v>2.760481233522072</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.266689207991764</v>
+        <v>-1.313543775072204</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.610048342440576</v>
+        <v>2.5913065156084</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.556820874597195</v>
+        <v>-1.603675441677636</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.493861892397326</v>
+        <v>2.47512006556515</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.764824932950273</v>
+        <v>-1.811679500030713</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.41555241361002</v>
+        <v>2.396810586777844</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.976237353838248</v>
+        <v>-2.023091920918688</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.326068901592818</v>
+        <v>2.307327074760642</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.3423060809829</v>
+        <v>-2.389160648063341</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.172725710041406</v>
+        <v>2.15398388320923</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.550796862434585</v>
+        <v>-2.597651429515025</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.109667687199501</v>
+        <v>2.090925860367324</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.797998047199806</v>
+        <v>-2.844852614280247</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.01888596370198</v>
+        <v>2.000144136869805</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.290383075223903</v>
+        <v>-3.337237642304343</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.823038344536074</v>
+        <v>1.804296517703898</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.675563466153975</v>
+        <v>-3.722418033234416</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.667508726976908</v>
+        <v>1.648766900144732</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.925434146168557</v>
+        <v>-3.972288713248997</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.569329578425692</v>
+        <v>1.550587751593516</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.131945923055579</v>
+        <v>-4.178800490136019</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.482830926327141</v>
+        <v>1.464089099494965</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.451289998136081</v>
+        <v>-4.498144565216521</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.3568662229952</v>
+        <v>1.338124396163024</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.883095791285868</v>
+        <v>-4.929950358366308</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.170476793202689</v>
+        <v>1.151734966370513</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.11778978541842</v>
+        <v>-5.16464435249886</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.064883970551759</v>
+        <v>1.046142143719583</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.453452432648873</v>
+        <v>-5.500306999729313</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9291995033155431</v>
+        <v>0.9104576764833672</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.817078677549186</v>
+        <v>-5.863933244629626</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7902365655896597</v>
+        <v>0.7714947387574833</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.182206060187933</v>
+        <v>-6.229060627268373</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6434401275399924</v>
+        <v>0.624698300707816</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.590794837368611</v>
+        <v>-6.637649404449052</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.47876616068248</v>
+        <v>0.4600243338503036</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.867370937684443</v>
+        <v>-6.914225504764884</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3633211530276075</v>
+        <v>0.3445793261954311</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.283762811971441</v>
+        <v>-7.330617379051882</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1947584539216862</v>
+        <v>0.1760166270895098</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.52803421269851</v>
+        <v>-7.574888779778951</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1073085842995374</v>
+        <v>0.08856675746736098</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.733285231935271</v>
+        <v>-7.780139799015712</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.0213077417505283</v>
+        <v>0.002565914918351897</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.896865110119654</v>
+        <v>-7.943719677200095</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.04571928946822412</v>
+        <v>-0.06446111630040052</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.193526451929852</v>
+        <v>-8.240381019010293</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1606048502630952</v>
+        <v>-0.1793466770952716</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.380246160239155</v>
+        <v>-8.427100727319596</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2393190381212196</v>
+        <v>-0.258060864953396</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.763247548981786</v>
+        <v>-8.810102116062227</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.392621694939856</v>
+        <v>-0.4113635217720324</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.945117339966821</v>
+        <v>-8.991971907047262</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4627980953624395</v>
+        <v>-0.4815399221946159</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.304647662470822</v>
+        <v>-9.351502229551263</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6012599210659904</v>
+        <v>-0.6200017478981668</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.354996725925044</v>
+        <v>-9.401851293005485</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6134835264905014</v>
+        <v>-0.6322253533226778</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539465</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.45261600334644</v>
+        <v>-9.499470570426881</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6494894868372909</v>
+        <v>-0.6682313136694673</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.600142091352083</v>
+        <v>-9.646996658432524</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7056063657179759</v>
+        <v>-0.7243481925501523</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.804400266681947</v>
+        <v>-9.851254833762388</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7817964387312792</v>
+        <v>-0.8005382655634556</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.83805310519042</v>
+        <v>-9.884907672270861</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7907750196502326</v>
+        <v>-0.809516846482409</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.41055738586864</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.764583273522971</v>
+        <v>-9.811437840603412</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7460153854898319</v>
+        <v>-0.7647572123220083</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.337087554201192</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.939707690909515</v>
+        <v>-9.986562257989956</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8015099316969323</v>
+        <v>-0.8202517585291087</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.512211971587735</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.174159784924</v>
+        <v>-10.22101435200445</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9025099342043243</v>
+        <v>-0.9212517610365007</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.512211971587735</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.27853451595045</v>
+        <v>-10.32538908303089</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9509320173888791</v>
+        <v>-0.9696738442210555</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.616586702614181</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.33132067155078</v>
+        <v>-10.37817523863122</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9709306897904533</v>
+        <v>-0.9896725166226297</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.712262189196578</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.45735746491907</v>
+        <v>-10.50421203199951</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.018651678508654</v>
+        <v>-1.037393505340831</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.687010566386836</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.40534195095025</v>
+        <v>-10.45219651803069</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9938551372347284</v>
+        <v>-1.012596964066905</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.687010566386836</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.54701379267437</v>
+        <v>-10.59386835975481</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.051999100823118</v>
+        <v>-1.070740927655295</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.687010566386836</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940722</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.49742294824954</v>
+        <v>-10.54427751532998</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.017109352888312</v>
+        <v>-1.035851179720489</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.637419721962002</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770583</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.48461555524477</v>
+        <v>-10.53147012232521</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.025037529333086</v>
+        <v>-1.043779356165262</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.686275496970903</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615286</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.25877040252535</v>
+        <v>-10.30562496960579</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9251203952091118</v>
+        <v>-0.9438622220412882</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.64434882138374</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812106</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.13419174618776</v>
+        <v>-10.1810463132682</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8741497881180167</v>
+        <v>-0.8928916149501931</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.64434882138374</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.71093553364622</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.18708703423205</v>
+        <v>-10.23394160131249</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8926741291736233</v>
+        <v>-0.9114159560057997</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.639393475295293</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.11495385894417</v>
+        <v>-10.16180842602461</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8580871548198346</v>
+        <v>-0.876828981652011</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.639393475295293</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955331</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.04358746633452</v>
+        <v>-10.09044203341496</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8392778601698403</v>
+        <v>-0.8580196870020167</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.568027082685645</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232417</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.950128432349295</v>
+        <v>-9.996982999429736</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8117777278886584</v>
+        <v>-0.8305195547208348</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.568027082685645</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436233</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.682886631480898</v>
+        <v>-9.729741198561339</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7067155680406731</v>
+        <v>-0.7254573948728495</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.568027082685645</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311953</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.584979592804407</v>
+        <v>-9.631834159884848</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6678530675435375</v>
+        <v>-0.6865948943757139</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.500041332825089</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097249</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.561026051828449</v>
+        <v>-9.60788061890889</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6576031450076609</v>
+        <v>-0.6763449718398373</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.476087791849131</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017777</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.296966113505652</v>
+        <v>-9.343820680586093</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5652394858402943</v>
+        <v>-0.5839813126724707</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.212027853526335</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83325274783973</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.589886490000815</v>
+        <v>-8.636741057081256</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2851946700986603</v>
+        <v>-0.3039364969308367</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.212027853526335</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388733</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.549702191634625</v>
+        <v>-8.596556758715066</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2687773268643427</v>
+        <v>-0.2875191536965191</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.171843555160144</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626479</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.386302320695261</v>
+        <v>-8.433156887775702</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2040505572678404</v>
+        <v>-0.2227923841000168</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.008443684220782</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291815</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.152821098465662</v>
+        <v>-8.199675665546103</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1027336395381484</v>
+        <v>-0.1214754663703248</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.774962461991183</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785791</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.003154707458147</v>
+        <v>-8.050009274538588</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.04575929344810126</v>
+        <v>-0.0645011202802781</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.682058970748648</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390431</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.870879233827261</v>
+        <v>-7.917733800907702</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.002518382751280246</v>
+        <v>-0.0162234440808966</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.549783497117761</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.715140901267519</v>
+        <v>-7.76199546834796</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.06762877646281362</v>
+        <v>0.04888694963063678</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.394045164558019</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960991</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.466141102583938</v>
+        <v>-7.512995669664379</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1801350371599049</v>
+        <v>0.161393210327728</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.394045164558019</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607649</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.571731092357043</v>
+        <v>-7.618585659437484</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.009923111651444216</v>
+        <v>-0.008818715180732184</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.499635154331124</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987907</v>
+        <v>3.770422583987904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.59046599447564</v>
+        <v>-7.637320561556081</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.05097349268109186</v>
+        <v>0.03223166584891501</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.505231163991255</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.44252595306804</v>
+        <v>-7.489380520148481</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.009729413444035995</v>
+        <v>-0.02847124027621284</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.484910248082697</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.389556430814052</v>
+        <v>-7.436410997894493</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.002744409204081144</v>
+        <v>-0.01599741762809526</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.431940725828709</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098113</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.346008024043361</v>
+        <v>-7.392862591123802</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.01320315981726417</v>
+        <v>-0.005538667014912235</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.431940725828709</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493424</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.103859630589503</v>
+        <v>-7.150714197669944</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1245248715799505</v>
+        <v>0.1057830447477741</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.431940725828709</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82855148672282</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.995600493466982</v>
+        <v>-7.042455060547423</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1623606468881542</v>
+        <v>0.1436188200559778</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.431940725828709</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.872309358649851</v>
+        <v>-6.919163925730292</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2091751948255838</v>
+        <v>0.1904333679934069</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.308649591011578</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.851160159746407</v>
+        <v>-6.898014726826848</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2253358526242861</v>
+        <v>0.2065940257921093</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.287500392108135</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318097</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.595259474391562</v>
+        <v>-6.654249284843404</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3234768351132749</v>
+        <v>0.2998809109325378</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.287500392108135</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82431123305753</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.493496654114267</v>
+        <v>-6.552486464566109</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3663062771442087</v>
+        <v>0.3427103529634716</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.274281323715706</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279189</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.243646260165193</v>
+        <v>-6.302636070617035</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4589885097075408</v>
+        <v>0.4353925855268037</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.274281323715706</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011502</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.06775416769776</v>
+        <v>-6.126743978149602</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5329444702151629</v>
+        <v>0.5093485460344258</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.274281323715706</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392991</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.896307704675296</v>
+        <v>-5.955297515127138</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6148505614787019</v>
+        <v>0.5912546372979648</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.102834860693243</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632785</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.822018138936957</v>
+        <v>-5.881007949388799</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6435868653903345</v>
+        <v>0.6199909412095974</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.028545294954904</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883078</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.758382396703023</v>
+        <v>-5.817372207154865</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6737359633382258</v>
+        <v>0.6501400391574883</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.9649095527209691</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074788</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.646955637377102</v>
+        <v>-5.705945447828944</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6995009258523894</v>
+        <v>0.6759050016716524</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.9649095527209691</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.7976948842423</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.406525140572242</v>
+        <v>-5.465514951024084</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7974162011992108</v>
+        <v>0.7738202770184737</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7244790559161088</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936769</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.334282572401047</v>
+        <v>-5.393272382852889</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8302425423025088</v>
+        <v>0.8066466181217717</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7244790559161088</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879971</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.28128425011966</v>
+        <v>-5.340274060571502</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.852120455132404</v>
+        <v>0.8285245309516669</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.66914279691417</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502343</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.172479364639933</v>
+        <v>-5.231469175091775</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8926404805442885</v>
+        <v>0.8690445563635514</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.66914279691417</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675945</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.952458566602922</v>
+        <v>-5.011448377054764</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9822278367697068</v>
+        <v>0.9586319125889697</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5279229518461898</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539956</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.819590877539644</v>
+        <v>-4.878580687991486</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.051269095196841</v>
+        <v>1.027673171016104</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5279229518461898</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.699417794175146</v>
+        <v>-4.758407604626988</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.100484172982942</v>
+        <v>1.076888248802205</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4077498684816908</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.554745649075408</v>
+        <v>-4.61373545952725</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.168441133584277</v>
+        <v>1.14484520940354</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.2630777233819534</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.6146204764331</v>
+        <v>-4.673610286884943</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.130528694042626</v>
+        <v>1.106932769861889</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3229525507396455</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.494800245522264</v>
+        <v>-4.553790055974106</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.19374595564117</v>
+        <v>1.170150031460432</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3229525507396455</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.992094879537234</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.49726995198407</v>
+        <v>-4.556259762435912</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.192830474429859</v>
+        <v>1.169234550249122</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3254222572014517</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.003101802011936</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.56564013830808</v>
+        <v>-4.624629948759922</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.176489322374957</v>
+        <v>1.15289339819422</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3161465581652367</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.993538510643827</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.579428191155126</v>
+        <v>-4.638418001606968</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.16141080986803</v>
+        <v>1.137814885687292</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3161465581652367</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417708</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.818248075684214</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.610421350483832</v>
+        <v>-4.669411160935674</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9737231111769344</v>
+        <v>0.9501271869961974</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3161465581652367</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205905</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.822815307676002</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.434947090691362</v>
+        <v>-4.493936901143204</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.04848004708571</v>
+        <v>1.024884122904973</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3161465581652367</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.798557336437209</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.545883343332611</v>
+        <v>-4.604873153784453</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9798475747904176</v>
+        <v>0.9562516506096803</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3161465581652367</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111298</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.801688721657114</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.512219797860329</v>
+        <v>-4.571209608312171</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.996444378199236</v>
+        <v>0.9728484540184987</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2824830126929549</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264168</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.811861108089247</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.452367178656606</v>
+        <v>-4.511356989108448</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.030557812312858</v>
+        <v>1.006961888132121</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2824830126929549</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742304</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.806807378663107</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.366123715630228</v>
+        <v>-4.42511352608207</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.060001468097269</v>
+        <v>1.036405543916532</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2824830126929549</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316051</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.798583154107633</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.411430535029208</v>
+        <v>-4.47042034548105</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.033654515782203</v>
+        <v>1.010058591601465</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3232931757021857</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803196</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.799135027140734</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.440463639731509</v>
+        <v>-4.499453450183351</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.022593146934384</v>
+        <v>0.9989972227536466</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3232931757021857</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809503</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.7284077190321</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.347653158280649</v>
+        <v>-4.406642968732491</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9889900314060933</v>
+        <v>0.965394107225356</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2304826942513263</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.74828581656043</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.730281194956701</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.392042627610077</v>
+        <v>-4.451032438061919</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9731077195989231</v>
+        <v>0.949511795418186</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.274872163580754</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472743</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.725356903468424</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.279371409373827</v>
+        <v>-4.338361219825669</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.013251915405146</v>
+        <v>0.9896559912244089</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1622009453445038</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798543</v>
+        <v>3.743047603798538</v>
       </c>
       <c r="C1949" t="n">
         <v>2.730848199299091</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.166994408191154</v>
+        <v>-4.225984218642996</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.063694011708883</v>
+        <v>1.040098087528145</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1622009453445038</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498871</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.74234540106763</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.194774806092506</v>
+        <v>-4.253764616544348</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.064079054316881</v>
+        <v>1.040483130136143</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1899813432458569</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705331</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.580701121068283</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.277776087117785</v>
+        <v>-4.336765897569627</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8692342619074223</v>
+        <v>0.8456383377266852</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2085522277730306</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729275</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.700850781787489</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.386390165561116</v>
+        <v>-4.445379976012958</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9459382912492955</v>
+        <v>0.9223423670685582</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2085522277730306</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190774</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.715363807889812</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.350981127312973</v>
+        <v>-4.409970937764816</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9746149326508755</v>
+        <v>0.9510190084701384</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2085522277730306</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913431</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.712783249232181</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.312597464754822</v>
+        <v>-4.371587275206664</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9873878390165047</v>
+        <v>0.9637919148357676</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1701685652148794</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532492</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.709512278077483</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.135481134719656</v>
+        <v>-4.194470945171498</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.054963399875874</v>
+        <v>1.031367475695136</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1701685652148794</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.74132844879391</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.710195669839396</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.180573379553202</v>
+        <v>-4.239563190005044</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.037609893704368</v>
+        <v>1.014013969523631</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2320646083842692</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011242</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.70398264514581</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.001197958314434</v>
+        <v>-4.060187768766276</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.10314703750629</v>
+        <v>1.079551113325553</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.07528785021355056</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982237</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.6847901004774</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.04621217183504</v>
+        <v>-4.105201982286882</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.065948807429637</v>
+        <v>1.0423528832489</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1056367455281552</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509545</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.690481662816346</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.313216682107475</v>
+        <v>-4.372206492559317</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.964838565659609</v>
+        <v>0.9412426414788717</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.2999997835711037</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760816</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.689685584712847</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.414414463544648</v>
+        <v>-4.47340427399649</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9235633749812413</v>
+        <v>0.8999674508005042</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3684085971164229</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70557166181546</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.687285546267164</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.407903496930335</v>
+        <v>-4.466893307382177</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9237677231812831</v>
+        <v>0.900171799000546</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3684085971164229</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378105</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.683810265475409</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.388865369223038</v>
+        <v>-4.44785517967488</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9279076934724468</v>
+        <v>0.9043117692917098</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4265922084476175</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131256</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.86139213441409</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.419992000373656</v>
+        <v>-4.478981810825498</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.09303890995088</v>
+        <v>1.069442985770143</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4265922084476175</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067872</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.862225463400223</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.433858761707574</v>
+        <v>-4.492848572159416</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.088325534403447</v>
+        <v>1.064729610222709</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4644501251814404</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789129</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.868233993797149</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.389054590167644</v>
+        <v>-4.448044400619486</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.112255733416344</v>
+        <v>1.088659809235607</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4644501251814404</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519915</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.947386641589171</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.241311619932642</v>
+        <v>-4.300301430384484</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.250505569302367</v>
+        <v>1.22690964512163</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2966427679465573</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181177</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.950180263120652</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.343326302463863</v>
+        <v>-4.402316112915705</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.21249331782136</v>
+        <v>1.188897393640623</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2966427679465573</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394738</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.95084261151231</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.337173596411079</v>
+        <v>-4.396163406862921</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.215616748634132</v>
+        <v>1.192020824453395</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.290490061893773</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890615</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.949923088252421</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.353982894561581</v>
+        <v>-4.412972705013423</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.207973506114041</v>
+        <v>1.184377581933304</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3072993600442746</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798433</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.016258642049241</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.291684895785458</v>
+        <v>-4.3506747062373</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.299228259421311</v>
+        <v>1.275632335240574</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3072993600442746</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.8487291399922</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.724839514438639</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.0898946981203</v>
+        <v>-4.148884508572142</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.088525210876772</v>
+        <v>1.064929286696035</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.1092811678751202</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852429</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.795129746760815</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.016516601031564</v>
+        <v>-4.075506411483406</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.188166682034442</v>
+        <v>1.164570757853705</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.03590307078638366</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319554</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.809757482876858</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.114257145656539</v>
+        <v>-4.173246956108381</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.163698200300496</v>
+        <v>1.140102276119759</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.05179234891936385</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489393</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.80829346370153</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.290594905779468</v>
+        <v>-4.34958471623131</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.091699077075996</v>
+        <v>1.068103152895259</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2281301090422932</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397802</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.806785081741459</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.214172859347541</v>
+        <v>-4.273162669799383</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.120759513688695</v>
+        <v>1.097163589507958</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2281301090422932</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316257</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.806647949176895</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.169799727708972</v>
+        <v>-4.228789538160814</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.138371633779559</v>
+        <v>1.114775709598822</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.1837569774037247</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105971</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.801041743315485</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.046965506821805</v>
+        <v>-4.105955317273647</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.181899116273016</v>
+        <v>1.158303192092279</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.1837569774037247</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190329</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.807423500343289</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.999309776260749</v>
+        <v>-4.058299586712591</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.207343165525243</v>
+        <v>1.183747241344506</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.136101246842669</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569622</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.812315873718014</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.898791617761995</v>
+        <v>-3.957781428213837</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.25244280229947</v>
+        <v>1.228846878118732</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.03558308834391444</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557297</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.799070546193887</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.959458208164384</v>
+        <v>-4.018448018616226</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.214930838614386</v>
+        <v>1.191334914433649</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.1172814050624481</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932773</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.803168248804515</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.914619806555986</v>
+        <v>-3.973609617007828</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.236963901868374</v>
+        <v>1.213367977687636</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.1127379721175786</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917057</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.807329188435593</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.015378442312984</v>
+        <v>-4.074368252764827</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.200821387196653</v>
+        <v>1.177225463015915</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.2015635408445841</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405966</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.81320879096343</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.971175605227083</v>
+        <v>-4.030165415678926</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.22438212455885</v>
+        <v>1.200786200378112</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.1573607037586836</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265652</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.811618791432678</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.008154632890527</v>
+        <v>-4.06714444334237</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.20800051396272</v>
+        <v>1.184404589781983</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.1203868019673531</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284886</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.862866556615717</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.028212711755367</v>
+        <v>-4.08720252220721</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.251225047599824</v>
+        <v>1.227629123419086</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.1203868019673531</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321028</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.861307261209971</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.988282038577477</v>
+        <v>-4.04727184902932</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.265638021465233</v>
+        <v>1.242042097284495</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.08045612878946273</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475145</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.856255489448241</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.937249945854949</v>
+        <v>-3.996239756306792</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.280999086792515</v>
+        <v>1.257403162611777</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.02942403606693478</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404861</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.873442893540946</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.872025764727743</v>
+        <v>-3.931015575179586</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.324276163336102</v>
+        <v>1.300680239155364</v>
       </c>
       <c r="F1988" t="n">
         <v>0.03580014506027085</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882565</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.869403865840226</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.834598744656609</v>
+        <v>-3.893588555108452</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.335207943663836</v>
+        <v>1.311612019483098</v>
       </c>
       <c r="F1989" t="n">
         <v>0.04105168308945251</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992669</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.870660658171466</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.854710400691318</v>
+        <v>-3.913700211143161</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.328420073581193</v>
+        <v>1.304824149400455</v>
       </c>
       <c r="F1990" t="n">
         <v>0.0520790280868717</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636294</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>3.031218429192677</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.800965586264113</v>
+        <v>-3.859955396715956</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.510475770373285</v>
+        <v>1.486879846192547</v>
       </c>
       <c r="F1991" t="n">
         <v>0.06214233752733367</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957632</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.151331338410494</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.777174017657971</v>
+        <v>-3.836163828109814</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.640105307033559</v>
+        <v>1.616509382852821</v>
       </c>
       <c r="F1992" t="n">
         <v>0.08593390613347596</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>3.143039314424353</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.751089933394163</v>
+        <v>-3.810079743846006</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.642246916752941</v>
+        <v>1.618650992572204</v>
       </c>
       <c r="F1993" t="n">
         <v>0.08593390613347596</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896932</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.141232510008133</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.672958752545216</v>
+        <v>-3.731948562997059</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.6716925846763</v>
+        <v>1.648096660495562</v>
       </c>
       <c r="F1994" t="n">
         <v>0.1601107170171605</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959863</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>3.158786915734924</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.664066291151933</v>
+        <v>-3.723056101603776</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.692803974960404</v>
+        <v>1.669208050779666</v>
       </c>
       <c r="F1995" t="n">
         <v>0.1601107170171605</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945372</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.150641963139508</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.832542408121811</v>
+        <v>-3.891532218573654</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.617268575577037</v>
+        <v>1.593672651396299</v>
       </c>
       <c r="F1996" t="n">
         <v>0.1321628813005797</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782715</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>3.13191166032737</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.134742879260227</v>
+        <v>-3.19373268971207</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.877658084309532</v>
+        <v>1.854062160128794</v>
       </c>
       <c r="F1997" t="n">
         <v>0.06181482193016902</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632645</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.122575682824274</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.112021775577075</v>
+        <v>-3.171011586028918</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.877410548279698</v>
+        <v>1.85381462409896</v>
       </c>
       <c r="F1998" t="n">
         <v>0.06181482193016902</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777682</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.281481808675443</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.110296732287031</v>
+        <v>-3.169286542738874</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.037006691446885</v>
+        <v>2.013410767266147</v>
       </c>
       <c r="F1999" t="n">
         <v>0.06353986522021277</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644421</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.31855963116909</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.265077739065286</v>
+        <v>-3.324067549517129</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.012172111229229</v>
+        <v>1.988576187048491</v>
       </c>
       <c r="F2000" t="n">
         <v>0.03017219116573666</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799969</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.315234987158635</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.213642405680627</v>
+        <v>-3.272632216132469</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.029421600572638</v>
+        <v>2.0058256763919</v>
       </c>
       <c r="F2001" t="n">
         <v>0.08160752455039633</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331124</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.325241140803377</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.186691181354139</v>
+        <v>-3.245680991805981</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.050208243947975</v>
+        <v>2.026612319767237</v>
       </c>
       <c r="F2002" t="n">
         <v>0.09648787057811548</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784117</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.509344272948336</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.322644189410455</v>
+        <v>-3.381633999862298</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.179930172870408</v>
+        <v>2.15633424868967</v>
       </c>
       <c r="F2003" t="n">
         <v>0.09648787057811548</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571443</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.50146096785133</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.345052307215327</v>
+        <v>-3.40404211766717</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.163083620651452</v>
+        <v>2.139487696470714</v>
       </c>
       <c r="F2004" t="n">
         <v>0.09648787057811548</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155041</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.503514967400967</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.493058074694726</v>
+        <v>-3.552047885146569</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.10593531320933</v>
+        <v>2.082339389028592</v>
       </c>
       <c r="F2005" t="n">
         <v>0.009760861714574021</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161986</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.559768685122814</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.502499000583256</v>
+        <v>-3.561488811035099</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.158412660575765</v>
+        <v>2.134816736395027</v>
       </c>
       <c r="F2006" t="n">
         <v>0.1321879792579654</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321643</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.562659779668115</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.5012122370437</v>
+        <v>-3.560202047495543</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.161818460536888</v>
+        <v>2.13822253635615</v>
       </c>
       <c r="F2007" t="n">
         <v>0.133474742797522</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347711</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.56077159256189</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.502769291032991</v>
+        <v>-3.561759101484834</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.159307451834947</v>
+        <v>2.135711527654209</v>
       </c>
       <c r="F2008" t="n">
         <v>0.133474742797522</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887755</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.555591822164752</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.510041176556456</v>
+        <v>-3.569030987008299</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.151218927228423</v>
+        <v>2.127623003047685</v>
       </c>
       <c r="F2009" t="n">
         <v>0.1262028572740573</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343073</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.554025832374905</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.508200157498205</v>
+        <v>-3.567189967950048</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.150389345061877</v>
+        <v>2.126793420881139</v>
       </c>
       <c r="F2010" t="n">
         <v>0.1274710839455257</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647114</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.567099239240823</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.515108862997885</v>
+        <v>-3.574098673449728</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.160699269727923</v>
+        <v>2.137103345547185</v>
       </c>
       <c r="F2011" t="n">
         <v>0.1274710839455257</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763537</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.567099239240823</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.516670505812745</v>
+        <v>-3.575660316264588</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.160074612601979</v>
+        <v>2.136478688421241</v>
       </c>
       <c r="F2012" t="n">
         <v>0.1274710839455257</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.71583405539212</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.565623280367825</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.544571292922218</v>
+        <v>-3.603561103374061</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.147438338885192</v>
+        <v>2.123842414704454</v>
       </c>
       <c r="F2013" t="n">
         <v>0.09287415980259089</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172532</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.562387724345024</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.547604290434892</v>
+        <v>-3.606594100886735</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.142989583857321</v>
+        <v>2.119393659676583</v>
       </c>
       <c r="F2014" t="n">
         <v>0.08984116228991701</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971084</v>
+        <v>3.619362241971078</v>
       </c>
       <c r="C2015" t="n">
         <v>3.629093683935528</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.567665611711399</v>
+        <v>-3.626655422163242</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.201671014937222</v>
+        <v>2.178075090756484</v>
       </c>
       <c r="F2015" t="n">
         <v>0.06977984101341</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.556003981668339</v>
+        <v>3.556003981668333</v>
       </c>
       <c r="C2016" t="n">
         <v>3.632745047394486</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.660057393966329</v>
+        <v>-3.719116582115555</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.168365665494208</v>
+        <v>2.144741990234517</v>
       </c>
       <c r="F2016" t="n">
         <v>0.06977984101341</v>
